--- a/outputs/ozon/ozon_unitka_po_ostatkam_2026-08-05.xlsx
+++ b/outputs/ozon/ozon_unitka_po_ostatkam_2026-08-05.xlsx
@@ -1120,10 +1120,9 @@
       <c r="J14" s="30" t="n">
         <v>343.82</v>
       </c>
-      <c r="K14" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K14" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L14" s="32">
         <f>J14+K14</f>
@@ -1140,18 +1139,18 @@
         <v>67</v>
       </c>
       <c r="P14" s="34">
-        <f>G14*</f>
+        <f>G14*$G$8</f>
         <v/>
       </c>
       <c r="Q14" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R14" s="34">
-        <f>G14*</f>
+        <f>G14*$G$4</f>
         <v/>
       </c>
       <c r="S14" s="34">
-        <f>I14*</f>
+        <f>I14*$G$3</f>
         <v/>
       </c>
       <c r="T14" s="36" t="n">
@@ -1168,11 +1167,11 @@
         <v>0.63</v>
       </c>
       <c r="X14" s="34">
-        <f>**W14</f>
+        <f>$G$6*$G$7*W14</f>
         <v/>
       </c>
       <c r="Y14" s="32">
-        <f>W14*(+0)</f>
+        <f>W14*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z14" s="33" t="n">
@@ -1214,7 +1213,7 @@
         <v/>
       </c>
       <c r="AJ14" s="34">
-        <f>(O14+Q14+V14+X14+Y14+L14)/(1-(M14++(1-H14)*++Z14+AB14))</f>
+        <f>(O14+Q14+V14+X14+Y14+L14)/(1-(M14+$G$4+(1-H14)*$G$3+$G$8+Z14+AB14))</f>
         <v/>
       </c>
     </row>
@@ -1458,10 +1457,9 @@
       <c r="J20" s="30" t="n">
         <v>151.13</v>
       </c>
-      <c r="K20" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K20" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L20" s="32">
         <f>J20+K20</f>
@@ -1478,18 +1476,18 @@
         <v>67</v>
       </c>
       <c r="P20" s="34">
-        <f>G20*</f>
+        <f>G20*$G$8</f>
         <v/>
       </c>
       <c r="Q20" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R20" s="34">
-        <f>G20*</f>
+        <f>G20*$G$4</f>
         <v/>
       </c>
       <c r="S20" s="34">
-        <f>I20*</f>
+        <f>I20*$G$3</f>
         <v/>
       </c>
       <c r="T20" s="36" t="n">
@@ -1506,11 +1504,11 @@
         <v>0.68</v>
       </c>
       <c r="X20" s="34">
-        <f>**W20</f>
+        <f>$G$6*$G$7*W20</f>
         <v/>
       </c>
       <c r="Y20" s="32">
-        <f>W20*(+0)</f>
+        <f>W20*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z20" s="33" t="n">
@@ -1552,7 +1550,7 @@
         <v/>
       </c>
       <c r="AJ20" s="34">
-        <f>(O20+Q20+V20+X20+Y20+L20)/(1-(M20++(1-H20)*++Z20+AB20))</f>
+        <f>(O20+Q20+V20+X20+Y20+L20)/(1-(M20+$G$4+(1-H20)*$G$3+$G$8+Z20+AB20))</f>
         <v/>
       </c>
     </row>
@@ -1910,7 +1908,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G29" s="27">
-        <f>(1.25*L29+O29+Q29+V29+X29+Y29)/(1-M29---(1-H29)*-Z29-AB29)</f>
+        <f>(1.25*L29+O29+Q29+V29+X29+Y29)/(1-M29-$G$8-$G$4-(1-H29)*$G$3-Z29-AB29)</f>
         <v/>
       </c>
       <c r="H29" s="28" t="n">
@@ -1923,10 +1921,9 @@
       <c r="J29" s="30" t="n">
         <v>637.89</v>
       </c>
-      <c r="K29" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K29" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L29" s="32">
         <f>J29+K29</f>
@@ -1943,18 +1940,18 @@
         <v>63</v>
       </c>
       <c r="P29" s="34">
-        <f>G29*</f>
+        <f>G29*$G$8</f>
         <v/>
       </c>
       <c r="Q29" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R29" s="34">
-        <f>G29*</f>
+        <f>G29*$G$4</f>
         <v/>
       </c>
       <c r="S29" s="34">
-        <f>I29*</f>
+        <f>I29*$G$3</f>
         <v/>
       </c>
       <c r="T29" s="36" t="n">
@@ -1971,11 +1968,11 @@
         <v>0.33</v>
       </c>
       <c r="X29" s="34">
-        <f>**W29</f>
+        <f>$G$6*$G$7*W29</f>
         <v/>
       </c>
       <c r="Y29" s="32">
-        <f>W29*(+0)</f>
+        <f>W29*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z29" s="33" t="n">
@@ -2017,7 +2014,7 @@
         <v/>
       </c>
       <c r="AJ29" s="34">
-        <f>(O29+Q29+V29+X29+Y29+L29)/(1-(M29++(1-H29)*++Z29+AB29))</f>
+        <f>(O29+Q29+V29+X29+Y29+L29)/(1-(M29+$G$4+(1-H29)*$G$3+$G$8+Z29+AB29))</f>
         <v/>
       </c>
     </row>
@@ -2123,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="27">
-        <f>(1.25*L32+O32+Q32+V32+X32+Y32)/(1-M32---(1-H32)*-Z32-AB32)</f>
+        <f>(1.25*L32+O32+Q32+V32+X32+Y32)/(1-M32-$G$8-$G$4-(1-H32)*$G$3-Z32-AB32)</f>
         <v/>
       </c>
       <c r="H32" s="28" t="n">
@@ -2136,10 +2133,9 @@
       <c r="J32" s="30" t="n">
         <v>142.13</v>
       </c>
-      <c r="K32" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K32" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L32" s="32">
         <f>J32+K32</f>
@@ -2156,18 +2152,18 @@
         <v>67</v>
       </c>
       <c r="P32" s="34">
-        <f>G32*</f>
+        <f>G32*$G$8</f>
         <v/>
       </c>
       <c r="Q32" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R32" s="34">
-        <f>G32*</f>
+        <f>G32*$G$4</f>
         <v/>
       </c>
       <c r="S32" s="34">
-        <f>I32*</f>
+        <f>I32*$G$3</f>
         <v/>
       </c>
       <c r="T32" s="36" t="n">
@@ -2184,11 +2180,11 @@
         <v>0.42</v>
       </c>
       <c r="X32" s="34">
-        <f>**W32</f>
+        <f>$G$6*$G$7*W32</f>
         <v/>
       </c>
       <c r="Y32" s="32">
-        <f>W32*(+0)</f>
+        <f>W32*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z32" s="33" t="n">
@@ -2230,7 +2226,7 @@
         <v/>
       </c>
       <c r="AJ32" s="34">
-        <f>(O32+Q32+V32+X32+Y32+L32)/(1-(M32++(1-H32)*++Z32+AB32))</f>
+        <f>(O32+Q32+V32+X32+Y32+L32)/(1-(M32+$G$4+(1-H32)*$G$3+$G$8+Z32+AB32))</f>
         <v/>
       </c>
     </row>
@@ -2378,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="27">
-        <f>(1.25*L36+O36+Q36+V36+X36+Y36)/(1-M36---(1-H36)*-Z36-AB36)</f>
+        <f>(1.25*L36+O36+Q36+V36+X36+Y36)/(1-M36-$G$8-$G$4-(1-H36)*$G$3-Z36-AB36)</f>
         <v/>
       </c>
       <c r="H36" s="28" t="n">
@@ -2391,10 +2387,9 @@
       <c r="J36" s="30" t="n">
         <v>242.23</v>
       </c>
-      <c r="K36" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K36" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L36" s="32">
         <f>J36+K36</f>
@@ -2411,18 +2406,18 @@
         <v>67</v>
       </c>
       <c r="P36" s="34">
-        <f>G36*</f>
+        <f>G36*$G$8</f>
         <v/>
       </c>
       <c r="Q36" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R36" s="34">
-        <f>G36*</f>
+        <f>G36*$G$4</f>
         <v/>
       </c>
       <c r="S36" s="34">
-        <f>I36*</f>
+        <f>I36*$G$3</f>
         <v/>
       </c>
       <c r="T36" s="36" t="n">
@@ -2439,11 +2434,11 @@
         <v>0.46</v>
       </c>
       <c r="X36" s="34">
-        <f>**W36</f>
+        <f>$G$6*$G$7*W36</f>
         <v/>
       </c>
       <c r="Y36" s="32">
-        <f>W36*(+0)</f>
+        <f>W36*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z36" s="33" t="n">
@@ -2485,7 +2480,7 @@
         <v/>
       </c>
       <c r="AJ36" s="34">
-        <f>(O36+Q36+V36+X36+Y36+L36)/(1-(M36++(1-H36)*++Z36+AB36))</f>
+        <f>(O36+Q36+V36+X36+Y36+L36)/(1-(M36+$G$4+(1-H36)*$G$3+$G$8+Z36+AB36))</f>
         <v/>
       </c>
     </row>
@@ -2589,7 +2584,7 @@
       <c r="E39" s="27" t="n"/>
       <c r="F39" s="27" t="n"/>
       <c r="G39" s="27">
-        <f>(1.25*L39+O39+Q39+V39+X39+Y39)/(1-M39---(1-H39)*-Z39-AB39)</f>
+        <f>(1.25*L39+O39+Q39+V39+X39+Y39)/(1-M39-$G$8-$G$4-(1-H39)*$G$3-Z39-AB39)</f>
         <v/>
       </c>
       <c r="H39" s="28" t="n">
@@ -2602,10 +2597,9 @@
       <c r="J39" s="30" t="n">
         <v>447.64</v>
       </c>
-      <c r="K39" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K39" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L39" s="32">
         <f>J39+K39</f>
@@ -2622,18 +2616,18 @@
         <v>63</v>
       </c>
       <c r="P39" s="34">
-        <f>G39*</f>
+        <f>G39*$G$8</f>
         <v/>
       </c>
       <c r="Q39" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R39" s="34">
-        <f>G39*</f>
+        <f>G39*$G$4</f>
         <v/>
       </c>
       <c r="S39" s="34">
-        <f>I39*</f>
+        <f>I39*$G$3</f>
         <v/>
       </c>
       <c r="T39" s="36" t="n">
@@ -2650,11 +2644,11 @@
         <v>0.3</v>
       </c>
       <c r="X39" s="34">
-        <f>**W39</f>
+        <f>$G$6*$G$7*W39</f>
         <v/>
       </c>
       <c r="Y39" s="32">
-        <f>W39*(+0)</f>
+        <f>W39*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z39" s="33" t="n">
@@ -2696,7 +2690,7 @@
         <v/>
       </c>
       <c r="AJ39" s="34">
-        <f>(O39+Q39+V39+X39+Y39+L39)/(1-(M39++(1-H39)*++Z39+AB39))</f>
+        <f>(O39+Q39+V39+X39+Y39+L39)/(1-(M39+$G$4+(1-H39)*$G$3+$G$8+Z39+AB39))</f>
         <v/>
       </c>
     </row>
@@ -2772,10 +2766,9 @@
       <c r="J41" s="30" t="n">
         <v>602.1799999999999</v>
       </c>
-      <c r="K41" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K41" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L41" s="32">
         <f>J41+K41</f>
@@ -2792,18 +2785,18 @@
         <v>67</v>
       </c>
       <c r="P41" s="34">
-        <f>G41*</f>
+        <f>G41*$G$8</f>
         <v/>
       </c>
       <c r="Q41" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R41" s="34">
-        <f>G41*</f>
+        <f>G41*$G$4</f>
         <v/>
       </c>
       <c r="S41" s="34">
-        <f>I41*</f>
+        <f>I41*$G$3</f>
         <v/>
       </c>
       <c r="T41" s="36" t="n">
@@ -2820,11 +2813,11 @@
         <v>0.58</v>
       </c>
       <c r="X41" s="34">
-        <f>**W41</f>
+        <f>$G$6*$G$7*W41</f>
         <v/>
       </c>
       <c r="Y41" s="32">
-        <f>W41*(+0)</f>
+        <f>W41*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z41" s="33" t="n">
@@ -2866,7 +2859,7 @@
         <v/>
       </c>
       <c r="AJ41" s="34">
-        <f>(O41+Q41+V41+X41+Y41+L41)/(1-(M41++(1-H41)*++Z41+AB41))</f>
+        <f>(O41+Q41+V41+X41+Y41+L41)/(1-(M41+$G$4+(1-H41)*$G$3+$G$8+Z41+AB41))</f>
         <v/>
       </c>
     </row>
@@ -3030,10 +3023,9 @@
       <c r="J45" s="30" t="n">
         <v>161.3</v>
       </c>
-      <c r="K45" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K45" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L45" s="32">
         <f>J45+K45</f>
@@ -3050,18 +3042,18 @@
         <v>67</v>
       </c>
       <c r="P45" s="34">
-        <f>G45*</f>
+        <f>G45*$G$8</f>
         <v/>
       </c>
       <c r="Q45" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R45" s="34">
-        <f>G45*</f>
+        <f>G45*$G$4</f>
         <v/>
       </c>
       <c r="S45" s="34">
-        <f>I45*</f>
+        <f>I45*$G$3</f>
         <v/>
       </c>
       <c r="T45" s="36" t="n">
@@ -3078,11 +3070,11 @@
         <v>0.72</v>
       </c>
       <c r="X45" s="34">
-        <f>**W45</f>
+        <f>$G$6*$G$7*W45</f>
         <v/>
       </c>
       <c r="Y45" s="32">
-        <f>W45*(+0)</f>
+        <f>W45*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z45" s="33" t="n">
@@ -3124,7 +3116,7 @@
         <v/>
       </c>
       <c r="AJ45" s="34">
-        <f>(O45+Q45+V45+X45+Y45+L45)/(1-(M45++(1-H45)*++Z45+AB45))</f>
+        <f>(O45+Q45+V45+X45+Y45+L45)/(1-(M45+$G$4+(1-H45)*$G$3+$G$8+Z45+AB45))</f>
         <v/>
       </c>
     </row>
@@ -3146,7 +3138,7 @@
         <v>20</v>
       </c>
       <c r="G46" s="27">
-        <f>(1.25*L46+O46+Q46+V46+X46+Y46)/(1-M46---(1-H46)*-Z46-AB46)</f>
+        <f>(1.25*L46+O46+Q46+V46+X46+Y46)/(1-M46-$G$8-$G$4-(1-H46)*$G$3-Z46-AB46)</f>
         <v/>
       </c>
       <c r="H46" s="28" t="n">
@@ -3159,10 +3151,9 @@
       <c r="J46" s="47" t="n">
         <v>183.88</v>
       </c>
-      <c r="K46" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K46" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L46" s="32">
         <f>J46+K46</f>
@@ -3179,18 +3170,18 @@
         <v>67</v>
       </c>
       <c r="P46" s="34">
-        <f>G46*</f>
+        <f>G46*$G$8</f>
         <v/>
       </c>
       <c r="Q46" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R46" s="34">
-        <f>G46*</f>
+        <f>G46*$G$4</f>
         <v/>
       </c>
       <c r="S46" s="34">
-        <f>I46*</f>
+        <f>I46*$G$3</f>
         <v/>
       </c>
       <c r="T46" s="36" t="n">
@@ -3207,11 +3198,11 @@
         <v>0.72</v>
       </c>
       <c r="X46" s="34">
-        <f>**W46</f>
+        <f>$G$6*$G$7*W46</f>
         <v/>
       </c>
       <c r="Y46" s="32">
-        <f>W46*(+0)</f>
+        <f>W46*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z46" s="33" t="n">
@@ -3253,7 +3244,7 @@
         <v/>
       </c>
       <c r="AJ46" s="34">
-        <f>(O46+Q46+V46+X46+Y46+L46)/(1-(M46++(1-H46)*++Z46+AB46))</f>
+        <f>(O46+Q46+V46+X46+Y46+L46)/(1-(M46+$G$4+(1-H46)*$G$3+$G$8+Z46+AB46))</f>
         <v/>
       </c>
     </row>
@@ -3287,10 +3278,9 @@
       <c r="J47" s="47" t="n">
         <v>216.45</v>
       </c>
-      <c r="K47" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K47" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L47" s="32">
         <f>J47+K47</f>
@@ -3307,18 +3297,18 @@
         <v>67</v>
       </c>
       <c r="P47" s="34">
-        <f>G47*</f>
+        <f>G47*$G$8</f>
         <v/>
       </c>
       <c r="Q47" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R47" s="34">
-        <f>G47*</f>
+        <f>G47*$G$4</f>
         <v/>
       </c>
       <c r="S47" s="34">
-        <f>I47*</f>
+        <f>I47*$G$3</f>
         <v/>
       </c>
       <c r="T47" s="36" t="n">
@@ -3335,11 +3325,11 @@
         <v>0.4</v>
       </c>
       <c r="X47" s="34">
-        <f>**W47</f>
+        <f>$G$6*$G$7*W47</f>
         <v/>
       </c>
       <c r="Y47" s="32">
-        <f>W47*(+0)</f>
+        <f>W47*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z47" s="33" t="n">
@@ -3381,7 +3371,7 @@
         <v/>
       </c>
       <c r="AJ47" s="34">
-        <f>(O47+Q47+V47+X47+Y47+L47)/(1-(M47++(1-H47)*++Z47+AB47))</f>
+        <f>(O47+Q47+V47+X47+Y47+L47)/(1-(M47+$G$4+(1-H47)*$G$3+$G$8+Z47+AB47))</f>
         <v/>
       </c>
     </row>
@@ -3415,10 +3405,9 @@
       <c r="J48" s="49" t="n">
         <v>242.88</v>
       </c>
-      <c r="K48" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K48" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L48" s="32">
         <f>J48+K48</f>
@@ -3435,18 +3424,18 @@
         <v>67</v>
       </c>
       <c r="P48" s="34">
-        <f>G48*</f>
+        <f>G48*$G$8</f>
         <v/>
       </c>
       <c r="Q48" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R48" s="34">
-        <f>G48*</f>
+        <f>G48*$G$4</f>
         <v/>
       </c>
       <c r="S48" s="34">
-        <f>I48*</f>
+        <f>I48*$G$3</f>
         <v/>
       </c>
       <c r="T48" s="36" t="n">
@@ -3463,11 +3452,11 @@
         <v>0.4</v>
       </c>
       <c r="X48" s="34">
-        <f>**W48</f>
+        <f>$G$6*$G$7*W48</f>
         <v/>
       </c>
       <c r="Y48" s="32">
-        <f>W48*(+0)</f>
+        <f>W48*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z48" s="33" t="n">
@@ -3509,7 +3498,7 @@
         <v/>
       </c>
       <c r="AJ48" s="34">
-        <f>(O48+Q48+V48+X48+Y48+L48)/(1-(M48++(1-H48)*++Z48+AB48))</f>
+        <f>(O48+Q48+V48+X48+Y48+L48)/(1-(M48+$G$4+(1-H48)*$G$3+$G$8+Z48+AB48))</f>
         <v/>
       </c>
     </row>
@@ -3585,10 +3574,9 @@
       <c r="J50" s="47" t="n">
         <v>245.65</v>
       </c>
-      <c r="K50" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K50" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L50" s="32">
         <f>J50+K50</f>
@@ -3605,18 +3593,18 @@
         <v>67</v>
       </c>
       <c r="P50" s="34">
-        <f>G50*</f>
+        <f>G50*$G$8</f>
         <v/>
       </c>
       <c r="Q50" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R50" s="34">
-        <f>G50*</f>
+        <f>G50*$G$4</f>
         <v/>
       </c>
       <c r="S50" s="34">
-        <f>I50*</f>
+        <f>I50*$G$3</f>
         <v/>
       </c>
       <c r="T50" s="36" t="n">
@@ -3633,11 +3621,11 @@
         <v>0.4</v>
       </c>
       <c r="X50" s="34">
-        <f>**W50</f>
+        <f>$G$6*$G$7*W50</f>
         <v/>
       </c>
       <c r="Y50" s="32">
-        <f>W50*(+0)</f>
+        <f>W50*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z50" s="33" t="n">
@@ -3679,7 +3667,7 @@
         <v/>
       </c>
       <c r="AJ50" s="34">
-        <f>(O50+Q50+V50+X50+Y50+L50)/(1-(M50++(1-H50)*++Z50+AB50))</f>
+        <f>(O50+Q50+V50+X50+Y50+L50)/(1-(M50+$G$4+(1-H50)*$G$3+$G$8+Z50+AB50))</f>
         <v/>
       </c>
     </row>
@@ -3713,10 +3701,9 @@
       <c r="J51" s="49" t="n">
         <v>270.81</v>
       </c>
-      <c r="K51" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K51" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L51" s="32">
         <f>J51+K51</f>
@@ -3733,18 +3720,18 @@
         <v>67</v>
       </c>
       <c r="P51" s="34">
-        <f>G51*</f>
+        <f>G51*$G$8</f>
         <v/>
       </c>
       <c r="Q51" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R51" s="34">
-        <f>G51*</f>
+        <f>G51*$G$4</f>
         <v/>
       </c>
       <c r="S51" s="34">
-        <f>I51*</f>
+        <f>I51*$G$3</f>
         <v/>
       </c>
       <c r="T51" s="36" t="n">
@@ -3761,11 +3748,11 @@
         <v>0.4</v>
       </c>
       <c r="X51" s="34">
-        <f>**W51</f>
+        <f>$G$6*$G$7*W51</f>
         <v/>
       </c>
       <c r="Y51" s="32">
-        <f>W51*(+0)</f>
+        <f>W51*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z51" s="33" t="n">
@@ -3807,7 +3794,7 @@
         <v/>
       </c>
       <c r="AJ51" s="34">
-        <f>(O51+Q51+V51+X51+Y51+L51)/(1-(M51++(1-H51)*++Z51+AB51))</f>
+        <f>(O51+Q51+V51+X51+Y51+L51)/(1-(M51+$G$4+(1-H51)*$G$3+$G$8+Z51+AB51))</f>
         <v/>
       </c>
     </row>
@@ -3841,10 +3828,9 @@
       <c r="J52" s="49" t="n">
         <v>238.13</v>
       </c>
-      <c r="K52" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K52" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L52" s="32">
         <f>J52+K52</f>
@@ -3861,18 +3847,18 @@
         <v>67</v>
       </c>
       <c r="P52" s="34">
-        <f>G52*</f>
+        <f>G52*$G$8</f>
         <v/>
       </c>
       <c r="Q52" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R52" s="34">
-        <f>G52*</f>
+        <f>G52*$G$4</f>
         <v/>
       </c>
       <c r="S52" s="34">
-        <f>I52*</f>
+        <f>I52*$G$3</f>
         <v/>
       </c>
       <c r="T52" s="36" t="n">
@@ -3889,11 +3875,11 @@
         <v>0.4</v>
       </c>
       <c r="X52" s="34">
-        <f>**W52</f>
+        <f>$G$6*$G$7*W52</f>
         <v/>
       </c>
       <c r="Y52" s="32">
-        <f>W52*(+0)</f>
+        <f>W52*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z52" s="33" t="n">
@@ -3935,7 +3921,7 @@
         <v/>
       </c>
       <c r="AJ52" s="34">
-        <f>(O52+Q52+V52+X52+Y52+L52)/(1-(M52++(1-H52)*++Z52+AB52))</f>
+        <f>(O52+Q52+V52+X52+Y52+L52)/(1-(M52+$G$4+(1-H52)*$G$3+$G$8+Z52+AB52))</f>
         <v/>
       </c>
     </row>
@@ -3969,10 +3955,9 @@
       <c r="J53" s="50" t="n">
         <v>223.35</v>
       </c>
-      <c r="K53" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K53" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L53" s="32">
         <f>J53+K53</f>
@@ -3989,18 +3974,18 @@
         <v>67</v>
       </c>
       <c r="P53" s="34">
-        <f>G53*</f>
+        <f>G53*$G$8</f>
         <v/>
       </c>
       <c r="Q53" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R53" s="34">
-        <f>G53*</f>
+        <f>G53*$G$4</f>
         <v/>
       </c>
       <c r="S53" s="34">
-        <f>I53*</f>
+        <f>I53*$G$3</f>
         <v/>
       </c>
       <c r="T53" s="36" t="n">
@@ -4017,11 +4002,11 @@
         <v>0.4</v>
       </c>
       <c r="X53" s="34">
-        <f>**W53</f>
+        <f>$G$6*$G$7*W53</f>
         <v/>
       </c>
       <c r="Y53" s="32">
-        <f>W53*(+0)</f>
+        <f>W53*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z53" s="33" t="n">
@@ -4063,7 +4048,7 @@
         <v/>
       </c>
       <c r="AJ53" s="34">
-        <f>(O53+Q53+V53+X53+Y53+L53)/(1-(M53++(1-H53)*++Z53+AB53))</f>
+        <f>(O53+Q53+V53+X53+Y53+L53)/(1-(M53+$G$4+(1-H53)*$G$3+$G$8+Z53+AB53))</f>
         <v/>
       </c>
     </row>
@@ -4097,10 +4082,9 @@
       <c r="J54" s="49" t="n">
         <v>335.9</v>
       </c>
-      <c r="K54" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K54" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L54" s="32">
         <f>J54+K54</f>
@@ -4117,18 +4101,18 @@
         <v>67</v>
       </c>
       <c r="P54" s="34">
-        <f>G54*</f>
+        <f>G54*$G$8</f>
         <v/>
       </c>
       <c r="Q54" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R54" s="34">
-        <f>G54*</f>
+        <f>G54*$G$4</f>
         <v/>
       </c>
       <c r="S54" s="34">
-        <f>I54*</f>
+        <f>I54*$G$3</f>
         <v/>
       </c>
       <c r="T54" s="36" t="n">
@@ -4145,11 +4129,11 @@
         <v>0.4</v>
       </c>
       <c r="X54" s="34">
-        <f>**W54</f>
+        <f>$G$6*$G$7*W54</f>
         <v/>
       </c>
       <c r="Y54" s="32">
-        <f>W54*(+0)</f>
+        <f>W54*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z54" s="33" t="n">
@@ -4191,7 +4175,7 @@
         <v/>
       </c>
       <c r="AJ54" s="34">
-        <f>(O54+Q54+V54+X54+Y54+L54)/(1-(M54++(1-H54)*++Z54+AB54))</f>
+        <f>(O54+Q54+V54+X54+Y54+L54)/(1-(M54+$G$4+(1-H54)*$G$3+$G$8+Z54+AB54))</f>
         <v/>
       </c>
     </row>
@@ -4213,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="27">
-        <f>(1.25*L55+O55+Q55+V55+X55+Y55)/(1-M55---(1-H55)*-Z55-AB55)</f>
+        <f>(1.25*L55+O55+Q55+V55+X55+Y55)/(1-M55-$G$8-$G$4-(1-H55)*$G$3-Z55-AB55)</f>
         <v/>
       </c>
       <c r="H55" s="28" t="n">
@@ -4226,10 +4210,9 @@
       <c r="J55" s="49" t="n">
         <v>304.77</v>
       </c>
-      <c r="K55" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K55" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L55" s="32">
         <f>J55+K55</f>
@@ -4246,18 +4229,18 @@
         <v>67</v>
       </c>
       <c r="P55" s="34">
-        <f>G55*</f>
+        <f>G55*$G$8</f>
         <v/>
       </c>
       <c r="Q55" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R55" s="34">
-        <f>G55*</f>
+        <f>G55*$G$4</f>
         <v/>
       </c>
       <c r="S55" s="34">
-        <f>I55*</f>
+        <f>I55*$G$3</f>
         <v/>
       </c>
       <c r="T55" s="36" t="n">
@@ -4274,11 +4257,11 @@
         <v>0.4</v>
       </c>
       <c r="X55" s="34">
-        <f>**W55</f>
+        <f>$G$6*$G$7*W55</f>
         <v/>
       </c>
       <c r="Y55" s="32">
-        <f>W55*(+0)</f>
+        <f>W55*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z55" s="33" t="n">
@@ -4320,7 +4303,7 @@
         <v/>
       </c>
       <c r="AJ55" s="34">
-        <f>(O55+Q55+V55+X55+Y55+L55)/(1-(M55++(1-H55)*++Z55+AB55))</f>
+        <f>(O55+Q55+V55+X55+Y55+L55)/(1-(M55+$G$4+(1-H55)*$G$3+$G$8+Z55+AB55))</f>
         <v/>
       </c>
     </row>
@@ -4504,7 +4487,7 @@
       <c r="E60" s="27" t="n"/>
       <c r="F60" s="27" t="n"/>
       <c r="G60" s="27">
-        <f>(1.25*L60+O60+Q60+V60+X60+Y60)/(1-M60---(1-H60)*-Z60-AB60)</f>
+        <f>(1.25*L60+O60+Q60+V60+X60+Y60)/(1-M60-$G$8-$G$4-(1-H60)*$G$3-Z60-AB60)</f>
         <v/>
       </c>
       <c r="H60" s="28" t="n">
@@ -4517,10 +4500,9 @@
       <c r="J60" s="49" t="n">
         <v>183.24</v>
       </c>
-      <c r="K60" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K60" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L60" s="32">
         <f>J60+K60</f>
@@ -4537,18 +4519,18 @@
         <v>56</v>
       </c>
       <c r="P60" s="34">
-        <f>G60*</f>
+        <f>G60*$G$8</f>
         <v/>
       </c>
       <c r="Q60" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R60" s="34">
-        <f>G60*</f>
+        <f>G60*$G$4</f>
         <v/>
       </c>
       <c r="S60" s="34">
-        <f>I60*</f>
+        <f>I60*$G$3</f>
         <v/>
       </c>
       <c r="T60" s="36" t="n">
@@ -4565,11 +4547,11 @@
         <v>0.05</v>
       </c>
       <c r="X60" s="34">
-        <f>**W60</f>
+        <f>$G$6*$G$7*W60</f>
         <v/>
       </c>
       <c r="Y60" s="32">
-        <f>W60*(+0)</f>
+        <f>W60*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z60" s="33" t="n">
@@ -4611,7 +4593,7 @@
         <v/>
       </c>
       <c r="AJ60" s="34">
-        <f>(O60+Q60+V60+X60+Y60+L60)/(1-(M60++(1-H60)*++Z60+AB60))</f>
+        <f>(O60+Q60+V60+X60+Y60+L60)/(1-(M60+$G$4+(1-H60)*$G$3+$G$8+Z60+AB60))</f>
         <v/>
       </c>
     </row>
@@ -4669,7 +4651,7 @@
       <c r="E62" s="27" t="n"/>
       <c r="F62" s="27" t="n"/>
       <c r="G62" s="27">
-        <f>(1.25*L62+O62+Q62+V62+X62+Y62)/(1-M62---(1-H62)*-Z62-AB62)</f>
+        <f>(1.25*L62+O62+Q62+V62+X62+Y62)/(1-M62-$G$8-$G$4-(1-H62)*$G$3-Z62-AB62)</f>
         <v/>
       </c>
       <c r="H62" s="28" t="n">
@@ -4682,10 +4664,9 @@
       <c r="J62" s="49" t="n">
         <v>183.24</v>
       </c>
-      <c r="K62" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K62" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L62" s="32">
         <f>J62+K62</f>
@@ -4702,18 +4683,18 @@
         <v>56</v>
       </c>
       <c r="P62" s="34">
-        <f>G62*</f>
+        <f>G62*$G$8</f>
         <v/>
       </c>
       <c r="Q62" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R62" s="34">
-        <f>G62*</f>
+        <f>G62*$G$4</f>
         <v/>
       </c>
       <c r="S62" s="34">
-        <f>I62*</f>
+        <f>I62*$G$3</f>
         <v/>
       </c>
       <c r="T62" s="36" t="n">
@@ -4730,11 +4711,11 @@
         <v>0.05</v>
       </c>
       <c r="X62" s="34">
-        <f>**W62</f>
+        <f>$G$6*$G$7*W62</f>
         <v/>
       </c>
       <c r="Y62" s="32">
-        <f>W62*(+0)</f>
+        <f>W62*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z62" s="33" t="n">
@@ -4776,7 +4757,7 @@
         <v/>
       </c>
       <c r="AJ62" s="34">
-        <f>(O62+Q62+V62+X62+Y62+L62)/(1-(M62++(1-H62)*++Z62+AB62))</f>
+        <f>(O62+Q62+V62+X62+Y62+L62)/(1-(M62+$G$4+(1-H62)*$G$3+$G$8+Z62+AB62))</f>
         <v/>
       </c>
     </row>
@@ -4834,7 +4815,7 @@
       <c r="E64" s="27" t="n"/>
       <c r="F64" s="27" t="n"/>
       <c r="G64" s="27">
-        <f>(1.25*L64+O64+Q64+V64+X64+Y64)/(1-M64---(1-H64)*-Z64-AB64)</f>
+        <f>(1.25*L64+O64+Q64+V64+X64+Y64)/(1-M64-$G$8-$G$4-(1-H64)*$G$3-Z64-AB64)</f>
         <v/>
       </c>
       <c r="H64" s="28" t="n">
@@ -4847,10 +4828,9 @@
       <c r="J64" s="49" t="n">
         <v>183.24</v>
       </c>
-      <c r="K64" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K64" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L64" s="32">
         <f>J64+K64</f>
@@ -4867,18 +4847,18 @@
         <v>56</v>
       </c>
       <c r="P64" s="34">
-        <f>G64*</f>
+        <f>G64*$G$8</f>
         <v/>
       </c>
       <c r="Q64" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R64" s="34">
-        <f>G64*</f>
+        <f>G64*$G$4</f>
         <v/>
       </c>
       <c r="S64" s="34">
-        <f>I64*</f>
+        <f>I64*$G$3</f>
         <v/>
       </c>
       <c r="T64" s="36" t="n">
@@ -4895,11 +4875,11 @@
         <v>0.05</v>
       </c>
       <c r="X64" s="34">
-        <f>**W64</f>
+        <f>$G$6*$G$7*W64</f>
         <v/>
       </c>
       <c r="Y64" s="32">
-        <f>W64*(+0)</f>
+        <f>W64*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z64" s="33" t="n">
@@ -4941,7 +4921,7 @@
         <v/>
       </c>
       <c r="AJ64" s="34">
-        <f>(O64+Q64+V64+X64+Y64+L64)/(1-(M64++(1-H64)*++Z64+AB64))</f>
+        <f>(O64+Q64+V64+X64+Y64+L64)/(1-(M64+$G$4+(1-H64)*$G$3+$G$8+Z64+AB64))</f>
         <v/>
       </c>
     </row>
@@ -5041,7 +5021,7 @@
       <c r="E67" s="27" t="n"/>
       <c r="F67" s="27" t="n"/>
       <c r="G67" s="27">
-        <f>(1.25*L67+O67+Q67+V67+X67+Y67)/(1-M67---(1-H67)*-Z67-AB67)</f>
+        <f>(1.25*L67+O67+Q67+V67+X67+Y67)/(1-M67-$G$8-$G$4-(1-H67)*$G$3-Z67-AB67)</f>
         <v/>
       </c>
       <c r="H67" s="28" t="n">
@@ -5054,10 +5034,9 @@
       <c r="J67" s="49" t="n">
         <v>189.27</v>
       </c>
-      <c r="K67" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K67" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L67" s="32">
         <f>J67+K67</f>
@@ -5074,18 +5053,18 @@
         <v>63</v>
       </c>
       <c r="P67" s="34">
-        <f>G67*</f>
+        <f>G67*$G$8</f>
         <v/>
       </c>
       <c r="Q67" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R67" s="34">
-        <f>G67*</f>
+        <f>G67*$G$4</f>
         <v/>
       </c>
       <c r="S67" s="34">
-        <f>I67*</f>
+        <f>I67*$G$3</f>
         <v/>
       </c>
       <c r="T67" s="36" t="n">
@@ -5102,11 +5081,11 @@
         <v>0.28</v>
       </c>
       <c r="X67" s="34">
-        <f>**W67</f>
+        <f>$G$6*$G$7*W67</f>
         <v/>
       </c>
       <c r="Y67" s="32">
-        <f>W67*(+0)</f>
+        <f>W67*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z67" s="33" t="n">
@@ -5148,7 +5127,7 @@
         <v/>
       </c>
       <c r="AJ67" s="34">
-        <f>(O67+Q67+V67+X67+Y67+L67)/(1-(M67++(1-H67)*++Z67+AB67))</f>
+        <f>(O67+Q67+V67+X67+Y67+L67)/(1-(M67+$G$4+(1-H67)*$G$3+$G$8+Z67+AB67))</f>
         <v/>
       </c>
     </row>
@@ -5308,10 +5287,9 @@
       <c r="J71" s="30" t="n">
         <v>361.03</v>
       </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K71" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L71" s="32">
         <f>J71+K71</f>
@@ -5328,18 +5306,18 @@
         <v>67</v>
       </c>
       <c r="P71" s="34">
-        <f>G71*</f>
+        <f>G71*$G$8</f>
         <v/>
       </c>
       <c r="Q71" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R71" s="34">
-        <f>G71*</f>
+        <f>G71*$G$4</f>
         <v/>
       </c>
       <c r="S71" s="34">
-        <f>I71*</f>
+        <f>I71*$G$3</f>
         <v/>
       </c>
       <c r="T71" s="36" t="n">
@@ -5356,11 +5334,11 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="X71" s="34">
-        <f>**W71</f>
+        <f>$G$6*$G$7*W71</f>
         <v/>
       </c>
       <c r="Y71" s="32">
-        <f>W71*(+0)</f>
+        <f>W71*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z71" s="33" t="n">
@@ -5402,7 +5380,7 @@
         <v/>
       </c>
       <c r="AJ71" s="34">
-        <f>(O71+Q71+V71+X71+Y71+L71)/(1-(M71++(1-H71)*++Z71+AB71))</f>
+        <f>(O71+Q71+V71+X71+Y71+L71)/(1-(M71+$G$4+(1-H71)*$G$3+$G$8+Z71+AB71))</f>
         <v/>
       </c>
     </row>
@@ -5478,10 +5456,9 @@
       <c r="J73" s="30" t="n">
         <v>292.89</v>
       </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K73" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L73" s="32">
         <f>J73+K73</f>
@@ -5498,18 +5475,18 @@
         <v>67</v>
       </c>
       <c r="P73" s="34">
-        <f>G73*</f>
+        <f>G73*$G$8</f>
         <v/>
       </c>
       <c r="Q73" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R73" s="34">
-        <f>G73*</f>
+        <f>G73*$G$4</f>
         <v/>
       </c>
       <c r="S73" s="34">
-        <f>I73*</f>
+        <f>I73*$G$3</f>
         <v/>
       </c>
       <c r="T73" s="36" t="n">
@@ -5526,11 +5503,11 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="X73" s="34">
-        <f>**W73</f>
+        <f>$G$6*$G$7*W73</f>
         <v/>
       </c>
       <c r="Y73" s="32">
-        <f>W73*(+0)</f>
+        <f>W73*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z73" s="33" t="n">
@@ -5572,7 +5549,7 @@
         <v/>
       </c>
       <c r="AJ73" s="34">
-        <f>(O73+Q73+V73+X73+Y73+L73)/(1-(M73++(1-H73)*++Z73+AB73))</f>
+        <f>(O73+Q73+V73+X73+Y73+L73)/(1-(M73+$G$4+(1-H73)*$G$3+$G$8+Z73+AB73))</f>
         <v/>
       </c>
     </row>
@@ -5606,10 +5583,9 @@
       <c r="J74" s="30" t="n">
         <v>389.99</v>
       </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K74" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L74" s="32">
         <f>J74+K74</f>
@@ -5626,18 +5602,18 @@
         <v>72</v>
       </c>
       <c r="P74" s="34">
-        <f>G74*</f>
+        <f>G74*$G$8</f>
         <v/>
       </c>
       <c r="Q74" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R74" s="34">
-        <f>G74*</f>
+        <f>G74*$G$4</f>
         <v/>
       </c>
       <c r="S74" s="34">
-        <f>I74*</f>
+        <f>I74*$G$3</f>
         <v/>
       </c>
       <c r="T74" s="36" t="n">
@@ -5654,11 +5630,11 @@
         <v>1.15</v>
       </c>
       <c r="X74" s="34">
-        <f>**W74</f>
+        <f>$G$6*$G$7*W74</f>
         <v/>
       </c>
       <c r="Y74" s="32">
-        <f>W74*(+0)</f>
+        <f>W74*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z74" s="33" t="n">
@@ -5700,7 +5676,7 @@
         <v/>
       </c>
       <c r="AJ74" s="34">
-        <f>(O74+Q74+V74+X74+Y74+L74)/(1-(M74++(1-H74)*++Z74+AB74))</f>
+        <f>(O74+Q74+V74+X74+Y74+L74)/(1-(M74+$G$4+(1-H74)*$G$3+$G$8+Z74+AB74))</f>
         <v/>
       </c>
     </row>
@@ -5780,10 +5756,9 @@
       <c r="J76" s="30" t="n">
         <v>347.76</v>
       </c>
-      <c r="K76" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K76" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L76" s="32">
         <f>J76+K76</f>
@@ -5800,18 +5775,18 @@
         <v>67</v>
       </c>
       <c r="P76" s="34">
-        <f>G76*</f>
+        <f>G76*$G$8</f>
         <v/>
       </c>
       <c r="Q76" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R76" s="34">
-        <f>G76*</f>
+        <f>G76*$G$4</f>
         <v/>
       </c>
       <c r="S76" s="34">
-        <f>I76*</f>
+        <f>I76*$G$3</f>
         <v/>
       </c>
       <c r="T76" s="36" t="n">
@@ -5828,11 +5803,11 @@
         <v>0.832</v>
       </c>
       <c r="X76" s="34">
-        <f>**W76</f>
+        <f>$G$6*$G$7*W76</f>
         <v/>
       </c>
       <c r="Y76" s="32">
-        <f>W76*(+0)</f>
+        <f>W76*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z76" s="33" t="n">
@@ -5874,7 +5849,7 @@
         <v/>
       </c>
       <c r="AJ76" s="34">
-        <f>(O76+Q76+V76+X76+Y76+L76)/(1-(M76++(1-H76)*++Z76+AB76))</f>
+        <f>(O76+Q76+V76+X76+Y76+L76)/(1-(M76+$G$4+(1-H76)*$G$3+$G$8+Z76+AB76))</f>
         <v/>
       </c>
     </row>
@@ -5912,10 +5887,9 @@
       <c r="J77" s="30" t="n">
         <v>396.72</v>
       </c>
-      <c r="K77" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K77" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L77" s="32">
         <f>J77+K77</f>
@@ -5932,18 +5906,18 @@
         <v>75</v>
       </c>
       <c r="P77" s="34">
-        <f>G77*</f>
+        <f>G77*$G$8</f>
         <v/>
       </c>
       <c r="Q77" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R77" s="34">
-        <f>G77*</f>
+        <f>G77*$G$4</f>
         <v/>
       </c>
       <c r="S77" s="34">
-        <f>I77*</f>
+        <f>I77*$G$3</f>
         <v/>
       </c>
       <c r="T77" s="36" t="n">
@@ -5960,11 +5934,11 @@
         <v>1.89</v>
       </c>
       <c r="X77" s="34">
-        <f>**W77</f>
+        <f>$G$6*$G$7*W77</f>
         <v/>
       </c>
       <c r="Y77" s="32">
-        <f>W77*(+0)</f>
+        <f>W77*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z77" s="33" t="n">
@@ -6006,7 +5980,7 @@
         <v/>
       </c>
       <c r="AJ77" s="34">
-        <f>(O77+Q77+V77+X77+Y77+L77)/(1-(M77++(1-H77)*++Z77+AB77))</f>
+        <f>(O77+Q77+V77+X77+Y77+L77)/(1-(M77+$G$4+(1-H77)*$G$3+$G$8+Z77+AB77))</f>
         <v/>
       </c>
     </row>
@@ -6026,7 +6000,7 @@
       <c r="E78" s="27" t="n"/>
       <c r="F78" s="27" t="n"/>
       <c r="G78" s="27">
-        <f>(1.25*L78+O78+Q78+V78+X78+Y78)/(1-M78---(1-H78)*-Z78-AB78)</f>
+        <f>(1.25*L78+O78+Q78+V78+X78+Y78)/(1-M78-$G$8-$G$4-(1-H78)*$G$3-Z78-AB78)</f>
         <v/>
       </c>
       <c r="H78" s="28" t="n">
@@ -6039,10 +6013,9 @@
       <c r="J78" s="30" t="n">
         <v>431.05</v>
       </c>
-      <c r="K78" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K78" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L78" s="32">
         <f>J78+K78</f>
@@ -6059,18 +6032,18 @@
         <v>67</v>
       </c>
       <c r="P78" s="34">
-        <f>G78*</f>
+        <f>G78*$G$8</f>
         <v/>
       </c>
       <c r="Q78" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R78" s="34">
-        <f>G78*</f>
+        <f>G78*$G$4</f>
         <v/>
       </c>
       <c r="S78" s="34">
-        <f>I78*</f>
+        <f>I78*$G$3</f>
         <v/>
       </c>
       <c r="T78" s="36" t="n">
@@ -6087,11 +6060,11 @@
         <v>0.73</v>
       </c>
       <c r="X78" s="34">
-        <f>**W78</f>
+        <f>$G$6*$G$7*W78</f>
         <v/>
       </c>
       <c r="Y78" s="32">
-        <f>W78*(+0)</f>
+        <f>W78*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z78" s="33" t="n">
@@ -6133,7 +6106,7 @@
         <v/>
       </c>
       <c r="AJ78" s="34">
-        <f>(O78+Q78+V78+X78+Y78+L78)/(1-(M78++(1-H78)*++Z78+AB78))</f>
+        <f>(O78+Q78+V78+X78+Y78+L78)/(1-(M78+$G$4+(1-H78)*$G$3+$G$8+Z78+AB78))</f>
         <v/>
       </c>
     </row>
@@ -6171,10 +6144,9 @@
       <c r="J79" s="30" t="n">
         <v>313.84</v>
       </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K79" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L79" s="32">
         <f>J79+K79</f>
@@ -6191,18 +6163,18 @@
         <v>67</v>
       </c>
       <c r="P79" s="34">
-        <f>G79*</f>
+        <f>G79*$G$8</f>
         <v/>
       </c>
       <c r="Q79" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R79" s="34">
-        <f>G79*</f>
+        <f>G79*$G$4</f>
         <v/>
       </c>
       <c r="S79" s="34">
-        <f>I79*</f>
+        <f>I79*$G$3</f>
         <v/>
       </c>
       <c r="T79" s="36" t="n">
@@ -6219,11 +6191,11 @@
         <v>0.86</v>
       </c>
       <c r="X79" s="34">
-        <f>**W79</f>
+        <f>$G$6*$G$7*W79</f>
         <v/>
       </c>
       <c r="Y79" s="32">
-        <f>W79*(+0)</f>
+        <f>W79*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z79" s="33" t="n">
@@ -6265,7 +6237,7 @@
         <v/>
       </c>
       <c r="AJ79" s="34">
-        <f>(O79+Q79+V79+X79+Y79+L79)/(1-(M79++(1-H79)*++Z79+AB79))</f>
+        <f>(O79+Q79+V79+X79+Y79+L79)/(1-(M79+$G$4+(1-H79)*$G$3+$G$8+Z79+AB79))</f>
         <v/>
       </c>
     </row>
@@ -6287,7 +6259,7 @@
         <v>7</v>
       </c>
       <c r="G80" s="27">
-        <f>(1.25*L80+O80+Q80+V80+X80+Y80)/(1-M80---(1-H80)*-Z80-AB80)</f>
+        <f>(1.25*L80+O80+Q80+V80+X80+Y80)/(1-M80-$G$8-$G$4-(1-H80)*$G$3-Z80-AB80)</f>
         <v/>
       </c>
       <c r="H80" s="28" t="n">
@@ -6300,10 +6272,9 @@
       <c r="J80" s="30" t="n">
         <v>390.46</v>
       </c>
-      <c r="K80" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K80" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L80" s="32">
         <f>J80+K80</f>
@@ -6320,18 +6291,18 @@
         <v>67</v>
       </c>
       <c r="P80" s="34">
-        <f>G80*</f>
+        <f>G80*$G$8</f>
         <v/>
       </c>
       <c r="Q80" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R80" s="34">
-        <f>G80*</f>
+        <f>G80*$G$4</f>
         <v/>
       </c>
       <c r="S80" s="34">
-        <f>I80*</f>
+        <f>I80*$G$3</f>
         <v/>
       </c>
       <c r="T80" s="36" t="n">
@@ -6348,11 +6319,11 @@
         <v>0.86</v>
       </c>
       <c r="X80" s="34">
-        <f>**W80</f>
+        <f>$G$6*$G$7*W80</f>
         <v/>
       </c>
       <c r="Y80" s="32">
-        <f>W80*(+0)</f>
+        <f>W80*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z80" s="33" t="n">
@@ -6394,7 +6365,7 @@
         <v/>
       </c>
       <c r="AJ80" s="34">
-        <f>(O80+Q80+V80+X80+Y80+L80)/(1-(M80++(1-H80)*++Z80+AB80))</f>
+        <f>(O80+Q80+V80+X80+Y80+L80)/(1-(M80+$G$4+(1-H80)*$G$3+$G$8+Z80+AB80))</f>
         <v/>
       </c>
     </row>
@@ -6416,7 +6387,7 @@
         <v>1</v>
       </c>
       <c r="G81" s="27">
-        <f>(1.25*L81+O81+Q81+V81+X81+Y81)/(1-M81---(1-H81)*-Z81-AB81)</f>
+        <f>(1.25*L81+O81+Q81+V81+X81+Y81)/(1-M81-$G$8-$G$4-(1-H81)*$G$3-Z81-AB81)</f>
         <v/>
       </c>
       <c r="H81" s="28" t="n">
@@ -6429,10 +6400,9 @@
       <c r="J81" s="30" t="n">
         <v>400.76</v>
       </c>
-      <c r="K81" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K81" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L81" s="32">
         <f>J81+K81</f>
@@ -6449,18 +6419,18 @@
         <v>75</v>
       </c>
       <c r="P81" s="34">
-        <f>G81*</f>
+        <f>G81*$G$8</f>
         <v/>
       </c>
       <c r="Q81" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R81" s="34">
-        <f>G81*</f>
+        <f>G81*$G$4</f>
         <v/>
       </c>
       <c r="S81" s="34">
-        <f>I81*</f>
+        <f>I81*$G$3</f>
         <v/>
       </c>
       <c r="T81" s="36" t="n">
@@ -6477,11 +6447,11 @@
         <v>1.26</v>
       </c>
       <c r="X81" s="34">
-        <f>**W81</f>
+        <f>$G$6*$G$7*W81</f>
         <v/>
       </c>
       <c r="Y81" s="32">
-        <f>W81*(+0)</f>
+        <f>W81*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z81" s="33" t="n">
@@ -6523,7 +6493,7 @@
         <v/>
       </c>
       <c r="AJ81" s="34">
-        <f>(O81+Q81+V81+X81+Y81+L81)/(1-(M81++(1-H81)*++Z81+AB81))</f>
+        <f>(O81+Q81+V81+X81+Y81+L81)/(1-(M81+$G$4+(1-H81)*$G$3+$G$8+Z81+AB81))</f>
         <v/>
       </c>
     </row>
@@ -6545,7 +6515,7 @@
         <v>7.5</v>
       </c>
       <c r="G82" s="27">
-        <f>(1.25*L82+O82+Q82+V82+X82+Y82)/(1-M82---(1-H82)*-Z82-AB82)</f>
+        <f>(1.25*L82+O82+Q82+V82+X82+Y82)/(1-M82-$G$8-$G$4-(1-H82)*$G$3-Z82-AB82)</f>
         <v/>
       </c>
       <c r="H82" s="28" t="n">
@@ -6558,10 +6528,9 @@
       <c r="J82" s="30" t="n">
         <v>396.72</v>
       </c>
-      <c r="K82" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K82" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L82" s="32">
         <f>J82+K82</f>
@@ -6578,18 +6547,18 @@
         <v>75</v>
       </c>
       <c r="P82" s="34">
-        <f>G82*</f>
+        <f>G82*$G$8</f>
         <v/>
       </c>
       <c r="Q82" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R82" s="34">
-        <f>G82*</f>
+        <f>G82*$G$4</f>
         <v/>
       </c>
       <c r="S82" s="34">
-        <f>I82*</f>
+        <f>I82*$G$3</f>
         <v/>
       </c>
       <c r="T82" s="36" t="n">
@@ -6606,11 +6575,11 @@
         <v>1.26</v>
       </c>
       <c r="X82" s="34">
-        <f>**W82</f>
+        <f>$G$6*$G$7*W82</f>
         <v/>
       </c>
       <c r="Y82" s="32">
-        <f>W82*(+0)</f>
+        <f>W82*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z82" s="33" t="n">
@@ -6652,7 +6621,7 @@
         <v/>
       </c>
       <c r="AJ82" s="34">
-        <f>(O82+Q82+V82+X82+Y82+L82)/(1-(M82++(1-H82)*++Z82+AB82))</f>
+        <f>(O82+Q82+V82+X82+Y82+L82)/(1-(M82+$G$4+(1-H82)*$G$3+$G$8+Z82+AB82))</f>
         <v/>
       </c>
     </row>
@@ -6686,10 +6655,9 @@
       <c r="J83" s="30" t="n">
         <v>231.73</v>
       </c>
-      <c r="K83" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K83" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L83" s="32">
         <f>J83+K83</f>
@@ -6706,18 +6674,18 @@
         <v>63</v>
       </c>
       <c r="P83" s="34">
-        <f>G83*</f>
+        <f>G83*$G$8</f>
         <v/>
       </c>
       <c r="Q83" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R83" s="34">
-        <f>G83*</f>
+        <f>G83*$G$4</f>
         <v/>
       </c>
       <c r="S83" s="34">
-        <f>I83*</f>
+        <f>I83*$G$3</f>
         <v/>
       </c>
       <c r="T83" s="36" t="n">
@@ -6734,11 +6702,11 @@
         <v>0.22</v>
       </c>
       <c r="X83" s="34">
-        <f>**W83</f>
+        <f>$G$6*$G$7*W83</f>
         <v/>
       </c>
       <c r="Y83" s="32">
-        <f>W83*(+0)</f>
+        <f>W83*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z83" s="33" t="n">
@@ -6780,7 +6748,7 @@
         <v/>
       </c>
       <c r="AJ83" s="34">
-        <f>(O83+Q83+V83+X83+Y83+L83)/(1-(M83++(1-H83)*++Z83+AB83))</f>
+        <f>(O83+Q83+V83+X83+Y83+L83)/(1-(M83+$G$4+(1-H83)*$G$3+$G$8+Z83+AB83))</f>
         <v/>
       </c>
     </row>
@@ -6802,7 +6770,7 @@
         <v>7</v>
       </c>
       <c r="G84" s="27">
-        <f>(1.25*L84+O84+Q84+V84+X84+Y84)/(1-M84---(1-H84)*-Z84-AB84)</f>
+        <f>(1.25*L84+O84+Q84+V84+X84+Y84)/(1-M84-$G$8-$G$4-(1-H84)*$G$3-Z84-AB84)</f>
         <v/>
       </c>
       <c r="H84" s="28" t="n">
@@ -6815,10 +6783,9 @@
       <c r="J84" s="30" t="n">
         <v>484.42</v>
       </c>
-      <c r="K84" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K84" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L84" s="32">
         <f>J84+K84</f>
@@ -6835,18 +6802,18 @@
         <v>67</v>
       </c>
       <c r="P84" s="34">
-        <f>G84*</f>
+        <f>G84*$G$8</f>
         <v/>
       </c>
       <c r="Q84" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R84" s="34">
-        <f>G84*</f>
+        <f>G84*$G$4</f>
         <v/>
       </c>
       <c r="S84" s="34">
-        <f>I84*</f>
+        <f>I84*$G$3</f>
         <v/>
       </c>
       <c r="T84" s="36" t="n">
@@ -6863,11 +6830,11 @@
         <v>0.57</v>
       </c>
       <c r="X84" s="34">
-        <f>**W84</f>
+        <f>$G$6*$G$7*W84</f>
         <v/>
       </c>
       <c r="Y84" s="32">
-        <f>W84*(+0)</f>
+        <f>W84*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z84" s="33" t="n">
@@ -6909,7 +6876,7 @@
         <v/>
       </c>
       <c r="AJ84" s="34">
-        <f>(O84+Q84+V84+X84+Y84+L84)/(1-(M84++(1-H84)*++Z84+AB84))</f>
+        <f>(O84+Q84+V84+X84+Y84+L84)/(1-(M84+$G$4+(1-H84)*$G$3+$G$8+Z84+AB84))</f>
         <v/>
       </c>
     </row>
@@ -6931,7 +6898,7 @@
         <v>4.5</v>
       </c>
       <c r="G85" s="27">
-        <f>(1.25*L85+O85+Q85+V85+X85+Y85)/(1-M85---(1-H85)*-Z85-AB85)</f>
+        <f>(1.25*L85+O85+Q85+V85+X85+Y85)/(1-M85-$G$8-$G$4-(1-H85)*$G$3-Z85-AB85)</f>
         <v/>
       </c>
       <c r="H85" s="28" t="n">
@@ -6944,10 +6911,9 @@
       <c r="J85" s="30" t="n">
         <v>161.47</v>
       </c>
-      <c r="K85" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K85" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L85" s="32">
         <f>J85+K85</f>
@@ -6964,18 +6930,18 @@
         <v>67</v>
       </c>
       <c r="P85" s="34">
-        <f>G85*</f>
+        <f>G85*$G$8</f>
         <v/>
       </c>
       <c r="Q85" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R85" s="34">
-        <f>G85*</f>
+        <f>G85*$G$4</f>
         <v/>
       </c>
       <c r="S85" s="34">
-        <f>I85*</f>
+        <f>I85*$G$3</f>
         <v/>
       </c>
       <c r="T85" s="36" t="n">
@@ -6992,11 +6958,11 @@
         <v>0.57</v>
       </c>
       <c r="X85" s="34">
-        <f>**W85</f>
+        <f>$G$6*$G$7*W85</f>
         <v/>
       </c>
       <c r="Y85" s="32">
-        <f>W85*(+0)</f>
+        <f>W85*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z85" s="33" t="n">
@@ -7038,7 +7004,7 @@
         <v/>
       </c>
       <c r="AJ85" s="34">
-        <f>(O85+Q85+V85+X85+Y85+L85)/(1-(M85++(1-H85)*++Z85+AB85))</f>
+        <f>(O85+Q85+V85+X85+Y85+L85)/(1-(M85+$G$4+(1-H85)*$G$3+$G$8+Z85+AB85))</f>
         <v/>
       </c>
     </row>
@@ -7072,10 +7038,9 @@
       <c r="J86" s="30" t="n">
         <v>770.48</v>
       </c>
-      <c r="K86" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K86" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L86" s="32">
         <f>J86+K86</f>
@@ -7092,18 +7057,18 @@
         <v>56</v>
       </c>
       <c r="P86" s="34">
-        <f>G86*</f>
+        <f>G86*$G$8</f>
         <v/>
       </c>
       <c r="Q86" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R86" s="34">
-        <f>G86*</f>
+        <f>G86*$G$4</f>
         <v/>
       </c>
       <c r="S86" s="34">
-        <f>I86*</f>
+        <f>I86*$G$3</f>
         <v/>
       </c>
       <c r="T86" s="36" t="n">
@@ -7120,11 +7085,11 @@
         <v>0.14</v>
       </c>
       <c r="X86" s="34">
-        <f>**W86</f>
+        <f>$G$6*$G$7*W86</f>
         <v/>
       </c>
       <c r="Y86" s="32">
-        <f>W86*(+0)</f>
+        <f>W86*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z86" s="33" t="n">
@@ -7166,7 +7131,7 @@
         <v/>
       </c>
       <c r="AJ86" s="34">
-        <f>(O86+Q86+V86+X86+Y86+L86)/(1-(M86++(1-H86)*++Z86+AB86))</f>
+        <f>(O86+Q86+V86+X86+Y86+L86)/(1-(M86+$G$4+(1-H86)*$G$3+$G$8+Z86+AB86))</f>
         <v/>
       </c>
     </row>
@@ -7620,10 +7585,9 @@
       <c r="J97" s="30" t="n">
         <v>202.27</v>
       </c>
-      <c r="K97" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K97" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L97" s="32">
         <f>J97+K97</f>
@@ -7640,18 +7604,18 @@
         <v>67</v>
       </c>
       <c r="P97" s="34">
-        <f>G97*</f>
+        <f>G97*$G$8</f>
         <v/>
       </c>
       <c r="Q97" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R97" s="34">
-        <f>G97*</f>
+        <f>G97*$G$4</f>
         <v/>
       </c>
       <c r="S97" s="34">
-        <f>I97*</f>
+        <f>I97*$G$3</f>
         <v/>
       </c>
       <c r="T97" s="36" t="n">
@@ -7668,11 +7632,11 @@
         <v>0.42</v>
       </c>
       <c r="X97" s="34">
-        <f>**W97</f>
+        <f>$G$6*$G$7*W97</f>
         <v/>
       </c>
       <c r="Y97" s="32">
-        <f>W97*(+0)</f>
+        <f>W97*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z97" s="33" t="n">
@@ -7714,7 +7678,7 @@
         <v/>
       </c>
       <c r="AJ97" s="34">
-        <f>(O97+Q97+V97+X97+Y97+L97)/(1-(M97++(1-H97)*++Z97+AB97))</f>
+        <f>(O97+Q97+V97+X97+Y97+L97)/(1-(M97+$G$4+(1-H97)*$G$3+$G$8+Z97+AB97))</f>
         <v/>
       </c>
     </row>
@@ -7748,10 +7712,9 @@
       <c r="J98" s="30" t="n">
         <v>185.86</v>
       </c>
-      <c r="K98" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K98" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L98" s="32">
         <f>J98+K98</f>
@@ -7768,18 +7731,18 @@
         <v>67</v>
       </c>
       <c r="P98" s="34">
-        <f>G98*</f>
+        <f>G98*$G$8</f>
         <v/>
       </c>
       <c r="Q98" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R98" s="34">
-        <f>G98*</f>
+        <f>G98*$G$4</f>
         <v/>
       </c>
       <c r="S98" s="34">
-        <f>I98*</f>
+        <f>I98*$G$3</f>
         <v/>
       </c>
       <c r="T98" s="36" t="n">
@@ -7796,11 +7759,11 @@
         <v>0.57</v>
       </c>
       <c r="X98" s="34">
-        <f>**W98</f>
+        <f>$G$6*$G$7*W98</f>
         <v/>
       </c>
       <c r="Y98" s="32">
-        <f>W98*(+0)</f>
+        <f>W98*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z98" s="33" t="n">
@@ -7842,7 +7805,7 @@
         <v/>
       </c>
       <c r="AJ98" s="34">
-        <f>(O98+Q98+V98+X98+Y98+L98)/(1-(M98++(1-H98)*++Z98+AB98))</f>
+        <f>(O98+Q98+V98+X98+Y98+L98)/(1-(M98+$G$4+(1-H98)*$G$3+$G$8+Z98+AB98))</f>
         <v/>
       </c>
     </row>
@@ -7876,10 +7839,9 @@
       <c r="J99" s="30" t="n">
         <v>202.27</v>
       </c>
-      <c r="K99" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K99" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L99" s="32">
         <f>J99+K99</f>
@@ -7896,18 +7858,18 @@
         <v>67</v>
       </c>
       <c r="P99" s="34">
-        <f>G99*</f>
+        <f>G99*$G$8</f>
         <v/>
       </c>
       <c r="Q99" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R99" s="34">
-        <f>G99*</f>
+        <f>G99*$G$4</f>
         <v/>
       </c>
       <c r="S99" s="34">
-        <f>I99*</f>
+        <f>I99*$G$3</f>
         <v/>
       </c>
       <c r="T99" s="36" t="n">
@@ -7924,11 +7886,11 @@
         <v>0.42</v>
       </c>
       <c r="X99" s="34">
-        <f>**W99</f>
+        <f>$G$6*$G$7*W99</f>
         <v/>
       </c>
       <c r="Y99" s="32">
-        <f>W99*(+0)</f>
+        <f>W99*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z99" s="33" t="n">
@@ -7970,7 +7932,7 @@
         <v/>
       </c>
       <c r="AJ99" s="34">
-        <f>(O99+Q99+V99+X99+Y99+L99)/(1-(M99++(1-H99)*++Z99+AB99))</f>
+        <f>(O99+Q99+V99+X99+Y99+L99)/(1-(M99+$G$4+(1-H99)*$G$3+$G$8+Z99+AB99))</f>
         <v/>
       </c>
     </row>
@@ -8760,10 +8722,9 @@
       <c r="J118" s="30" t="n">
         <v>265.36</v>
       </c>
-      <c r="K118" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K118" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L118" s="32">
         <f>J118+K118</f>
@@ -8780,18 +8741,18 @@
         <v>67</v>
       </c>
       <c r="P118" s="34">
-        <f>G118*</f>
+        <f>G118*$G$8</f>
         <v/>
       </c>
       <c r="Q118" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R118" s="34">
-        <f>G118*</f>
+        <f>G118*$G$4</f>
         <v/>
       </c>
       <c r="S118" s="34">
-        <f>I118*</f>
+        <f>I118*$G$3</f>
         <v/>
       </c>
       <c r="T118" s="36" t="n">
@@ -8808,11 +8769,11 @@
         <v>0.93</v>
       </c>
       <c r="X118" s="34">
-        <f>**W118</f>
+        <f>$G$6*$G$7*W118</f>
         <v/>
       </c>
       <c r="Y118" s="32">
-        <f>W118*(+0)</f>
+        <f>W118*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z118" s="33" t="n">
@@ -8854,7 +8815,7 @@
         <v/>
       </c>
       <c r="AJ118" s="34">
-        <f>(O118+Q118+V118+X118+Y118+L118)/(1-(M118++(1-H118)*++Z118+AB118))</f>
+        <f>(O118+Q118+V118+X118+Y118+L118)/(1-(M118+$G$4+(1-H118)*$G$3+$G$8+Z118+AB118))</f>
         <v/>
       </c>
     </row>
@@ -8888,10 +8849,9 @@
       <c r="J119" s="30" t="n">
         <v>265.36</v>
       </c>
-      <c r="K119" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K119" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L119" s="32">
         <f>J119+K119</f>
@@ -8908,18 +8868,18 @@
         <v>67</v>
       </c>
       <c r="P119" s="34">
-        <f>G119*</f>
+        <f>G119*$G$8</f>
         <v/>
       </c>
       <c r="Q119" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R119" s="34">
-        <f>G119*</f>
+        <f>G119*$G$4</f>
         <v/>
       </c>
       <c r="S119" s="34">
-        <f>I119*</f>
+        <f>I119*$G$3</f>
         <v/>
       </c>
       <c r="T119" s="36" t="n">
@@ -8936,11 +8896,11 @@
         <v>0.93</v>
       </c>
       <c r="X119" s="34">
-        <f>**W119</f>
+        <f>$G$6*$G$7*W119</f>
         <v/>
       </c>
       <c r="Y119" s="32">
-        <f>W119*(+0)</f>
+        <f>W119*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z119" s="33" t="n">
@@ -8982,7 +8942,7 @@
         <v/>
       </c>
       <c r="AJ119" s="34">
-        <f>(O119+Q119+V119+X119+Y119+L119)/(1-(M119++(1-H119)*++Z119+AB119))</f>
+        <f>(O119+Q119+V119+X119+Y119+L119)/(1-(M119+$G$4+(1-H119)*$G$3+$G$8+Z119+AB119))</f>
         <v/>
       </c>
     </row>
@@ -9016,10 +8976,9 @@
       <c r="J120" s="30" t="n">
         <v>265.36</v>
       </c>
-      <c r="K120" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K120" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L120" s="32">
         <f>J120+K120</f>
@@ -9036,18 +8995,18 @@
         <v>67</v>
       </c>
       <c r="P120" s="34">
-        <f>G120*</f>
+        <f>G120*$G$8</f>
         <v/>
       </c>
       <c r="Q120" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R120" s="34">
-        <f>G120*</f>
+        <f>G120*$G$4</f>
         <v/>
       </c>
       <c r="S120" s="34">
-        <f>I120*</f>
+        <f>I120*$G$3</f>
         <v/>
       </c>
       <c r="T120" s="36" t="n">
@@ -9064,11 +9023,11 @@
         <v>0.93</v>
       </c>
       <c r="X120" s="34">
-        <f>**W120</f>
+        <f>$G$6*$G$7*W120</f>
         <v/>
       </c>
       <c r="Y120" s="32">
-        <f>W120*(+0)</f>
+        <f>W120*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z120" s="33" t="n">
@@ -9110,7 +9069,7 @@
         <v/>
       </c>
       <c r="AJ120" s="34">
-        <f>(O120+Q120+V120+X120+Y120+L120)/(1-(M120++(1-H120)*++Z120+AB120))</f>
+        <f>(O120+Q120+V120+X120+Y120+L120)/(1-(M120+$G$4+(1-H120)*$G$3+$G$8+Z120+AB120))</f>
         <v/>
       </c>
     </row>
@@ -9144,10 +9103,9 @@
       <c r="J121" s="30" t="n">
         <v>265.36</v>
       </c>
-      <c r="K121" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K121" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L121" s="32">
         <f>J121+K121</f>
@@ -9164,18 +9122,18 @@
         <v>67</v>
       </c>
       <c r="P121" s="34">
-        <f>G121*</f>
+        <f>G121*$G$8</f>
         <v/>
       </c>
       <c r="Q121" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R121" s="34">
-        <f>G121*</f>
+        <f>G121*$G$4</f>
         <v/>
       </c>
       <c r="S121" s="34">
-        <f>I121*</f>
+        <f>I121*$G$3</f>
         <v/>
       </c>
       <c r="T121" s="36" t="n">
@@ -9192,11 +9150,11 @@
         <v>0.93</v>
       </c>
       <c r="X121" s="34">
-        <f>**W121</f>
+        <f>$G$6*$G$7*W121</f>
         <v/>
       </c>
       <c r="Y121" s="32">
-        <f>W121*(+0)</f>
+        <f>W121*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z121" s="33" t="n">
@@ -9238,7 +9196,7 @@
         <v/>
       </c>
       <c r="AJ121" s="34">
-        <f>(O121+Q121+V121+X121+Y121+L121)/(1-(M121++(1-H121)*++Z121+AB121))</f>
+        <f>(O121+Q121+V121+X121+Y121+L121)/(1-(M121+$G$4+(1-H121)*$G$3+$G$8+Z121+AB121))</f>
         <v/>
       </c>
     </row>
@@ -9274,10 +9232,9 @@
       <c r="J122" s="30" t="n">
         <v>463.2</v>
       </c>
-      <c r="K122" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K122" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L122" s="32">
         <f>J122+K122</f>
@@ -9294,18 +9251,18 @@
         <v>72</v>
       </c>
       <c r="P122" s="34">
-        <f>G122*</f>
+        <f>G122*$G$8</f>
         <v/>
       </c>
       <c r="Q122" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R122" s="34">
-        <f>G122*</f>
+        <f>G122*$G$4</f>
         <v/>
       </c>
       <c r="S122" s="34">
-        <f>I122*</f>
+        <f>I122*$G$3</f>
         <v/>
       </c>
       <c r="T122" s="36" t="n">
@@ -9322,11 +9279,11 @@
         <v>1.25</v>
       </c>
       <c r="X122" s="34">
-        <f>**W122</f>
+        <f>$G$6*$G$7*W122</f>
         <v/>
       </c>
       <c r="Y122" s="32">
-        <f>W122*(+0)</f>
+        <f>W122*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z122" s="33" t="n">
@@ -9368,7 +9325,7 @@
         <v/>
       </c>
       <c r="AJ122" s="34">
-        <f>(O122+Q122+V122+X122+Y122+L122)/(1-(M122++(1-H122)*++Z122+AB122))</f>
+        <f>(O122+Q122+V122+X122+Y122+L122)/(1-(M122+$G$4+(1-H122)*$G$3+$G$8+Z122+AB122))</f>
         <v/>
       </c>
     </row>
@@ -10324,10 +10281,9 @@
       <c r="J145" s="30" t="n">
         <v>463.2</v>
       </c>
-      <c r="K145" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K145" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L145" s="32">
         <f>J145+K145</f>
@@ -10344,18 +10300,18 @@
         <v>72</v>
       </c>
       <c r="P145" s="34">
-        <f>G145*</f>
+        <f>G145*$G$8</f>
         <v/>
       </c>
       <c r="Q145" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R145" s="34">
-        <f>G145*</f>
+        <f>G145*$G$4</f>
         <v/>
       </c>
       <c r="S145" s="34">
-        <f>I145*</f>
+        <f>I145*$G$3</f>
         <v/>
       </c>
       <c r="T145" s="36" t="n">
@@ -10372,11 +10328,11 @@
         <v>1.25</v>
       </c>
       <c r="X145" s="34">
-        <f>**W145</f>
+        <f>$G$6*$G$7*W145</f>
         <v/>
       </c>
       <c r="Y145" s="32">
-        <f>W145*(+0)</f>
+        <f>W145*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z145" s="33" t="n">
@@ -10418,7 +10374,7 @@
         <v/>
       </c>
       <c r="AJ145" s="34">
-        <f>(O145+Q145+V145+X145+Y145+L145)/(1-(M145++(1-H145)*++Z145+AB145))</f>
+        <f>(O145+Q145+V145+X145+Y145+L145)/(1-(M145+$G$4+(1-H145)*$G$3+$G$8+Z145+AB145))</f>
         <v/>
       </c>
     </row>
@@ -11208,10 +11164,9 @@
       <c r="J164" s="30" t="n">
         <v>108.15</v>
       </c>
-      <c r="K164" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K164" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L164" s="32">
         <f>J164+K164</f>
@@ -11228,18 +11183,18 @@
         <v>63</v>
       </c>
       <c r="P164" s="34">
-        <f>G164*</f>
+        <f>G164*$G$8</f>
         <v/>
       </c>
       <c r="Q164" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R164" s="34">
-        <f>G164*</f>
+        <f>G164*$G$4</f>
         <v/>
       </c>
       <c r="S164" s="34">
-        <f>I164*</f>
+        <f>I164*$G$3</f>
         <v/>
       </c>
       <c r="T164" s="36" t="n">
@@ -11256,11 +11211,11 @@
         <v>0.27</v>
       </c>
       <c r="X164" s="34">
-        <f>**W164</f>
+        <f>$G$6*$G$7*W164</f>
         <v/>
       </c>
       <c r="Y164" s="32">
-        <f>W164*(+0)</f>
+        <f>W164*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z164" s="33" t="n">
@@ -11302,7 +11257,7 @@
         <v/>
       </c>
       <c r="AJ164" s="34">
-        <f>(O164+Q164+V164+X164+Y164+L164)/(1-(M164++(1-H164)*++Z164+AB164))</f>
+        <f>(O164+Q164+V164+X164+Y164+L164)/(1-(M164+$G$4+(1-H164)*$G$3+$G$8+Z164+AB164))</f>
         <v/>
       </c>
     </row>
@@ -11366,7 +11321,7 @@
         <v>10</v>
       </c>
       <c r="G166" s="27">
-        <f>(1.25*L166+O166+Q166+V166+X166+Y166)/(1-M166---(1-H166)*-Z166-AB166)</f>
+        <f>(1.25*L166+O166+Q166+V166+X166+Y166)/(1-M166-$G$8-$G$4-(1-H166)*$G$3-Z166-AB166)</f>
         <v/>
       </c>
       <c r="H166" s="28" t="n">
@@ -11379,10 +11334,9 @@
       <c r="J166" s="30" t="n">
         <v>130.86</v>
       </c>
-      <c r="K166" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K166" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L166" s="32">
         <f>J166+K166</f>
@@ -11399,18 +11353,18 @@
         <v>56</v>
       </c>
       <c r="P166" s="34">
-        <f>G166*</f>
+        <f>G166*$G$8</f>
         <v/>
       </c>
       <c r="Q166" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R166" s="34">
-        <f>G166*</f>
+        <f>G166*$G$4</f>
         <v/>
       </c>
       <c r="S166" s="34">
-        <f>I166*</f>
+        <f>I166*$G$3</f>
         <v/>
       </c>
       <c r="T166" s="36" t="n">
@@ -11427,11 +11381,11 @@
         <v>0.2</v>
       </c>
       <c r="X166" s="34">
-        <f>**W166</f>
+        <f>$G$6*$G$7*W166</f>
         <v/>
       </c>
       <c r="Y166" s="32">
-        <f>W166*(+0)</f>
+        <f>W166*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z166" s="33" t="n">
@@ -11473,7 +11427,7 @@
         <v/>
       </c>
       <c r="AJ166" s="34">
-        <f>(O166+Q166+V166+X166+Y166+L166)/(1-(M166++(1-H166)*++Z166+AB166))</f>
+        <f>(O166+Q166+V166+X166+Y166+L166)/(1-(M166+$G$4+(1-H166)*$G$3+$G$8+Z166+AB166))</f>
         <v/>
       </c>
     </row>
@@ -11549,10 +11503,9 @@
       <c r="J168" s="30" t="n">
         <v>899.78</v>
       </c>
-      <c r="K168" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K168" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L168" s="32">
         <f>J168+K168</f>
@@ -11569,18 +11522,18 @@
         <v>63</v>
       </c>
       <c r="P168" s="34">
-        <f>G168*</f>
+        <f>G168*$G$8</f>
         <v/>
       </c>
       <c r="Q168" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R168" s="34">
-        <f>G168*</f>
+        <f>G168*$G$4</f>
         <v/>
       </c>
       <c r="S168" s="34">
-        <f>I168*</f>
+        <f>I168*$G$3</f>
         <v/>
       </c>
       <c r="T168" s="36" t="n">
@@ -11597,11 +11550,11 @@
         <v>0.3</v>
       </c>
       <c r="X168" s="34">
-        <f>**W168</f>
+        <f>$G$6*$G$7*W168</f>
         <v/>
       </c>
       <c r="Y168" s="32">
-        <f>W168*(+0)</f>
+        <f>W168*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z168" s="33" t="n">
@@ -11643,7 +11596,7 @@
         <v/>
       </c>
       <c r="AJ168" s="34">
-        <f>(O168+Q168+V168+X168+Y168+L168)/(1-(M168++(1-H168)*++Z168+AB168))</f>
+        <f>(O168+Q168+V168+X168+Y168+L168)/(1-(M168+$G$4+(1-H168)*$G$3+$G$8+Z168+AB168))</f>
         <v/>
       </c>
     </row>
@@ -11681,10 +11634,9 @@
       <c r="J169" s="30" t="n">
         <v>646.83</v>
       </c>
-      <c r="K169" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K169" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L169" s="32">
         <f>J169+K169</f>
@@ -11701,18 +11653,18 @@
         <v>56</v>
       </c>
       <c r="P169" s="34">
-        <f>G169*</f>
+        <f>G169*$G$8</f>
         <v/>
       </c>
       <c r="Q169" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R169" s="34">
-        <f>G169*</f>
+        <f>G169*$G$4</f>
         <v/>
       </c>
       <c r="S169" s="34">
-        <f>I169*</f>
+        <f>I169*$G$3</f>
         <v/>
       </c>
       <c r="T169" s="36" t="n">
@@ -11729,11 +11681,11 @@
         <v>0.19</v>
       </c>
       <c r="X169" s="34">
-        <f>**W169</f>
+        <f>$G$6*$G$7*W169</f>
         <v/>
       </c>
       <c r="Y169" s="32">
-        <f>W169*(+0)</f>
+        <f>W169*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z169" s="33" t="n">
@@ -11775,7 +11727,7 @@
         <v/>
       </c>
       <c r="AJ169" s="34">
-        <f>(O169+Q169+V169+X169+Y169+L169)/(1-(M169++(1-H169)*++Z169+AB169))</f>
+        <f>(O169+Q169+V169+X169+Y169+L169)/(1-(M169+$G$4+(1-H169)*$G$3+$G$8+Z169+AB169))</f>
         <v/>
       </c>
     </row>
@@ -11855,10 +11807,9 @@
       <c r="J171" s="30" t="n">
         <v>735.34</v>
       </c>
-      <c r="K171" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K171" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L171" s="32">
         <f>J171+K171</f>
@@ -11875,18 +11826,18 @@
         <v>67</v>
       </c>
       <c r="P171" s="34">
-        <f>G171*</f>
+        <f>G171*$G$8</f>
         <v/>
       </c>
       <c r="Q171" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R171" s="34">
-        <f>G171*</f>
+        <f>G171*$G$4</f>
         <v/>
       </c>
       <c r="S171" s="34">
-        <f>I171*</f>
+        <f>I171*$G$3</f>
         <v/>
       </c>
       <c r="T171" s="36" t="n">
@@ -11903,11 +11854,11 @@
         <v>0.61</v>
       </c>
       <c r="X171" s="34">
-        <f>**W171</f>
+        <f>$G$6*$G$7*W171</f>
         <v/>
       </c>
       <c r="Y171" s="32">
-        <f>W171*(+0)</f>
+        <f>W171*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z171" s="33" t="n">
@@ -11949,7 +11900,7 @@
         <v/>
       </c>
       <c r="AJ171" s="34">
-        <f>(O171+Q171+V171+X171+Y171+L171)/(1-(M171++(1-H171)*++Z171+AB171))</f>
+        <f>(O171+Q171+V171+X171+Y171+L171)/(1-(M171+$G$4+(1-H171)*$G$3+$G$8+Z171+AB171))</f>
         <v/>
       </c>
     </row>
@@ -11987,10 +11938,9 @@
       <c r="J172" s="30" t="n">
         <v>853</v>
       </c>
-      <c r="K172" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K172" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L172" s="32">
         <f>J172+K172</f>
@@ -12007,18 +11957,18 @@
         <v>67</v>
       </c>
       <c r="P172" s="34">
-        <f>G172*</f>
+        <f>G172*$G$8</f>
         <v/>
       </c>
       <c r="Q172" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R172" s="34">
-        <f>G172*</f>
+        <f>G172*$G$4</f>
         <v/>
       </c>
       <c r="S172" s="34">
-        <f>I172*</f>
+        <f>I172*$G$3</f>
         <v/>
       </c>
       <c r="T172" s="36" t="n">
@@ -12035,11 +11985,11 @@
         <v>0.5</v>
       </c>
       <c r="X172" s="34">
-        <f>**W172</f>
+        <f>$G$6*$G$7*W172</f>
         <v/>
       </c>
       <c r="Y172" s="32">
-        <f>W172*(+0)</f>
+        <f>W172*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z172" s="33" t="n">
@@ -12081,7 +12031,7 @@
         <v/>
       </c>
       <c r="AJ172" s="34">
-        <f>(O172+Q172+V172+X172+Y172+L172)/(1-(M172++(1-H172)*++Z172+AB172))</f>
+        <f>(O172+Q172+V172+X172+Y172+L172)/(1-(M172+$G$4+(1-H172)*$G$3+$G$8+Z172+AB172))</f>
         <v/>
       </c>
     </row>
@@ -12161,10 +12111,9 @@
       <c r="J174" s="30" t="n">
         <v>650</v>
       </c>
-      <c r="K174" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K174" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L174" s="32">
         <f>J174+K174</f>
@@ -12181,18 +12130,18 @@
         <v>75</v>
       </c>
       <c r="P174" s="34">
-        <f>G174*</f>
+        <f>G174*$G$8</f>
         <v/>
       </c>
       <c r="Q174" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R174" s="34">
-        <f>G174*</f>
+        <f>G174*$G$4</f>
         <v/>
       </c>
       <c r="S174" s="34">
-        <f>I174*</f>
+        <f>I174*$G$3</f>
         <v/>
       </c>
       <c r="T174" s="36" t="n">
@@ -12209,11 +12158,11 @@
         <v>0.931</v>
       </c>
       <c r="X174" s="34">
-        <f>**W174</f>
+        <f>$G$6*$G$7*W174</f>
         <v/>
       </c>
       <c r="Y174" s="32">
-        <f>W174*(+0)</f>
+        <f>W174*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z174" s="33" t="n">
@@ -12255,7 +12204,7 @@
         <v/>
       </c>
       <c r="AJ174" s="34">
-        <f>(O174+Q174+V174+X174+Y174+L174)/(1-(M174++(1-H174)*++Z174+AB174))</f>
+        <f>(O174+Q174+V174+X174+Y174+L174)/(1-(M174+$G$4+(1-H174)*$G$3+$G$8+Z174+AB174))</f>
         <v/>
       </c>
     </row>
@@ -12289,10 +12238,9 @@
       <c r="J175" s="30" t="n">
         <v>899.78</v>
       </c>
-      <c r="K175" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K175" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L175" s="32">
         <f>J175+K175</f>
@@ -12309,18 +12257,18 @@
         <v>63</v>
       </c>
       <c r="P175" s="34">
-        <f>G175*</f>
+        <f>G175*$G$8</f>
         <v/>
       </c>
       <c r="Q175" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R175" s="34">
-        <f>G175*</f>
+        <f>G175*$G$4</f>
         <v/>
       </c>
       <c r="S175" s="34">
-        <f>I175*</f>
+        <f>I175*$G$3</f>
         <v/>
       </c>
       <c r="T175" s="36" t="n">
@@ -12337,11 +12285,11 @@
         <v>0.3</v>
       </c>
       <c r="X175" s="34">
-        <f>**W175</f>
+        <f>$G$6*$G$7*W175</f>
         <v/>
       </c>
       <c r="Y175" s="32">
-        <f>W175*(+0)</f>
+        <f>W175*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z175" s="33" t="n">
@@ -12383,7 +12331,7 @@
         <v/>
       </c>
       <c r="AJ175" s="34">
-        <f>(O175+Q175+V175+X175+Y175+L175)/(1-(M175++(1-H175)*++Z175+AB175))</f>
+        <f>(O175+Q175+V175+X175+Y175+L175)/(1-(M175+$G$4+(1-H175)*$G$3+$G$8+Z175+AB175))</f>
         <v/>
       </c>
     </row>
@@ -12501,10 +12449,9 @@
       <c r="J178" s="30" t="n">
         <v>385.05</v>
       </c>
-      <c r="K178" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K178" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L178" s="32">
         <f>J178+K178</f>
@@ -12521,18 +12468,18 @@
         <v>67</v>
       </c>
       <c r="P178" s="34">
-        <f>G178*</f>
+        <f>G178*$G$8</f>
         <v/>
       </c>
       <c r="Q178" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R178" s="34">
-        <f>G178*</f>
+        <f>G178*$G$4</f>
         <v/>
       </c>
       <c r="S178" s="34">
-        <f>I178*</f>
+        <f>I178*$G$3</f>
         <v/>
       </c>
       <c r="T178" s="36" t="n">
@@ -12549,11 +12496,11 @@
         <v>0.6</v>
       </c>
       <c r="X178" s="34">
-        <f>**W178</f>
+        <f>$G$6*$G$7*W178</f>
         <v/>
       </c>
       <c r="Y178" s="32">
-        <f>W178*(+0)</f>
+        <f>W178*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z178" s="33" t="n">
@@ -12595,7 +12542,7 @@
         <v/>
       </c>
       <c r="AJ178" s="34">
-        <f>(O178+Q178+V178+X178+Y178+L178)/(1-(M178++(1-H178)*++Z178+AB178))</f>
+        <f>(O178+Q178+V178+X178+Y178+L178)/(1-(M178+$G$4+(1-H178)*$G$3+$G$8+Z178+AB178))</f>
         <v/>
       </c>
     </row>
@@ -12611,7 +12558,7 @@
       <c r="E179" s="27" t="n"/>
       <c r="F179" s="27" t="n"/>
       <c r="G179" s="27">
-        <f>(1.25*L179+O179+Q179+V179+X179+Y179)/(1-M179---(1-H179)*-Z179-AB179)</f>
+        <f>(1.25*L179+O179+Q179+V179+X179+Y179)/(1-M179-$G$8-$G$4-(1-H179)*$G$3-Z179-AB179)</f>
         <v/>
       </c>
       <c r="H179" s="28" t="n">
@@ -12624,10 +12571,9 @@
       <c r="J179" s="30" t="n">
         <v>486.69</v>
       </c>
-      <c r="K179" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K179" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L179" s="32">
         <f>J179+K179</f>
@@ -12644,18 +12590,18 @@
         <v>67</v>
       </c>
       <c r="P179" s="34">
-        <f>G179*</f>
+        <f>G179*$G$8</f>
         <v/>
       </c>
       <c r="Q179" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R179" s="34">
-        <f>G179*</f>
+        <f>G179*$G$4</f>
         <v/>
       </c>
       <c r="S179" s="34">
-        <f>I179*</f>
+        <f>I179*$G$3</f>
         <v/>
       </c>
       <c r="T179" s="36" t="n">
@@ -12672,11 +12618,11 @@
         <v>0.93</v>
       </c>
       <c r="X179" s="34">
-        <f>**W179</f>
+        <f>$G$6*$G$7*W179</f>
         <v/>
       </c>
       <c r="Y179" s="32">
-        <f>W179*(+0)</f>
+        <f>W179*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z179" s="33" t="n">
@@ -12718,7 +12664,7 @@
         <v/>
       </c>
       <c r="AJ179" s="34">
-        <f>(O179+Q179+V179+X179+Y179+L179)/(1-(M179++(1-H179)*++Z179+AB179))</f>
+        <f>(O179+Q179+V179+X179+Y179+L179)/(1-(M179+$G$4+(1-H179)*$G$3+$G$8+Z179+AB179))</f>
         <v/>
       </c>
     </row>
@@ -12734,7 +12680,7 @@
       <c r="E180" s="27" t="n"/>
       <c r="F180" s="27" t="n"/>
       <c r="G180" s="27">
-        <f>(1.25*L180+O180+Q180+V180+X180+Y180)/(1-M180---(1-H180)*-Z180-AB180)</f>
+        <f>(1.25*L180+O180+Q180+V180+X180+Y180)/(1-M180-$G$8-$G$4-(1-H180)*$G$3-Z180-AB180)</f>
         <v/>
       </c>
       <c r="H180" s="28" t="n">
@@ -12747,10 +12693,9 @@
       <c r="J180" s="30" t="n">
         <v>415.46</v>
       </c>
-      <c r="K180" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K180" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L180" s="32">
         <f>J180+K180</f>
@@ -12767,18 +12712,18 @@
         <v>67</v>
       </c>
       <c r="P180" s="34">
-        <f>G180*</f>
+        <f>G180*$G$8</f>
         <v/>
       </c>
       <c r="Q180" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R180" s="34">
-        <f>G180*</f>
+        <f>G180*$G$4</f>
         <v/>
       </c>
       <c r="S180" s="34">
-        <f>I180*</f>
+        <f>I180*$G$3</f>
         <v/>
       </c>
       <c r="T180" s="36" t="n">
@@ -12795,11 +12740,11 @@
         <v>0.6</v>
       </c>
       <c r="X180" s="34">
-        <f>**W180</f>
+        <f>$G$6*$G$7*W180</f>
         <v/>
       </c>
       <c r="Y180" s="32">
-        <f>W180*(+0)</f>
+        <f>W180*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z180" s="33" t="n">
@@ -12841,7 +12786,7 @@
         <v/>
       </c>
       <c r="AJ180" s="34">
-        <f>(O180+Q180+V180+X180+Y180+L180)/(1-(M180++(1-H180)*++Z180+AB180))</f>
+        <f>(O180+Q180+V180+X180+Y180+L180)/(1-(M180+$G$4+(1-H180)*$G$3+$G$8+Z180+AB180))</f>
         <v/>
       </c>
     </row>
@@ -12857,7 +12802,7 @@
       <c r="E181" s="27" t="n"/>
       <c r="F181" s="27" t="n"/>
       <c r="G181" s="27">
-        <f>(1.25*L181+O181+Q181+V181+X181+Y181)/(1-M181---(1-H181)*-Z181-AB181)</f>
+        <f>(1.25*L181+O181+Q181+V181+X181+Y181)/(1-M181-$G$8-$G$4-(1-H181)*$G$3-Z181-AB181)</f>
         <v/>
       </c>
       <c r="H181" s="28" t="n">
@@ -12870,10 +12815,9 @@
       <c r="J181" s="30" t="n">
         <v>591.29</v>
       </c>
-      <c r="K181" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K181" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L181" s="32">
         <f>J181+K181</f>
@@ -12890,18 +12834,18 @@
         <v>67</v>
       </c>
       <c r="P181" s="34">
-        <f>G181*</f>
+        <f>G181*$G$8</f>
         <v/>
       </c>
       <c r="Q181" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R181" s="34">
-        <f>G181*</f>
+        <f>G181*$G$4</f>
         <v/>
       </c>
       <c r="S181" s="34">
-        <f>I181*</f>
+        <f>I181*$G$3</f>
         <v/>
       </c>
       <c r="T181" s="36" t="n">
@@ -12918,11 +12862,11 @@
         <v>0.93</v>
       </c>
       <c r="X181" s="34">
-        <f>**W181</f>
+        <f>$G$6*$G$7*W181</f>
         <v/>
       </c>
       <c r="Y181" s="32">
-        <f>W181*(+0)</f>
+        <f>W181*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z181" s="33" t="n">
@@ -12964,7 +12908,7 @@
         <v/>
       </c>
       <c r="AJ181" s="34">
-        <f>(O181+Q181+V181+X181+Y181+L181)/(1-(M181++(1-H181)*++Z181+AB181))</f>
+        <f>(O181+Q181+V181+X181+Y181+L181)/(1-(M181+$G$4+(1-H181)*$G$3+$G$8+Z181+AB181))</f>
         <v/>
       </c>
     </row>
@@ -12980,7 +12924,7 @@
       <c r="E182" s="27" t="n"/>
       <c r="F182" s="27" t="n"/>
       <c r="G182" s="27">
-        <f>(1.25*L182+O182+Q182+V182+X182+Y182)/(1-M182---(1-H182)*-Z182-AB182)</f>
+        <f>(1.25*L182+O182+Q182+V182+X182+Y182)/(1-M182-$G$8-$G$4-(1-H182)*$G$3-Z182-AB182)</f>
         <v/>
       </c>
       <c r="H182" s="28" t="n">
@@ -12993,10 +12937,9 @@
       <c r="J182" s="30" t="n">
         <v>415.46</v>
       </c>
-      <c r="K182" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K182" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L182" s="32">
         <f>J182+K182</f>
@@ -13013,18 +12956,18 @@
         <v>67</v>
       </c>
       <c r="P182" s="34">
-        <f>G182*</f>
+        <f>G182*$G$8</f>
         <v/>
       </c>
       <c r="Q182" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R182" s="34">
-        <f>G182*</f>
+        <f>G182*$G$4</f>
         <v/>
       </c>
       <c r="S182" s="34">
-        <f>I182*</f>
+        <f>I182*$G$3</f>
         <v/>
       </c>
       <c r="T182" s="36" t="n">
@@ -13041,11 +12984,11 @@
         <v>0.6</v>
       </c>
       <c r="X182" s="34">
-        <f>**W182</f>
+        <f>$G$6*$G$7*W182</f>
         <v/>
       </c>
       <c r="Y182" s="32">
-        <f>W182*(+0)</f>
+        <f>W182*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z182" s="33" t="n">
@@ -13087,7 +13030,7 @@
         <v/>
       </c>
       <c r="AJ182" s="34">
-        <f>(O182+Q182+V182+X182+Y182+L182)/(1-(M182++(1-H182)*++Z182+AB182))</f>
+        <f>(O182+Q182+V182+X182+Y182+L182)/(1-(M182+$G$4+(1-H182)*$G$3+$G$8+Z182+AB182))</f>
         <v/>
       </c>
     </row>
@@ -13103,7 +13046,7 @@
       <c r="E183" s="27" t="n"/>
       <c r="F183" s="27" t="n"/>
       <c r="G183" s="27">
-        <f>(1.25*L183+O183+Q183+V183+X183+Y183)/(1-M183---(1-H183)*-Z183-AB183)</f>
+        <f>(1.25*L183+O183+Q183+V183+X183+Y183)/(1-M183-$G$8-$G$4-(1-H183)*$G$3-Z183-AB183)</f>
         <v/>
       </c>
       <c r="H183" s="28" t="n">
@@ -13116,10 +13059,9 @@
       <c r="J183" s="30" t="n">
         <v>415.46</v>
       </c>
-      <c r="K183" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K183" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L183" s="32">
         <f>J183+K183</f>
@@ -13136,18 +13078,18 @@
         <v>67</v>
       </c>
       <c r="P183" s="34">
-        <f>G183*</f>
+        <f>G183*$G$8</f>
         <v/>
       </c>
       <c r="Q183" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R183" s="34">
-        <f>G183*</f>
+        <f>G183*$G$4</f>
         <v/>
       </c>
       <c r="S183" s="34">
-        <f>I183*</f>
+        <f>I183*$G$3</f>
         <v/>
       </c>
       <c r="T183" s="36" t="n">
@@ -13164,11 +13106,11 @@
         <v>0.6</v>
       </c>
       <c r="X183" s="34">
-        <f>**W183</f>
+        <f>$G$6*$G$7*W183</f>
         <v/>
       </c>
       <c r="Y183" s="32">
-        <f>W183*(+0)</f>
+        <f>W183*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z183" s="33" t="n">
@@ -13210,7 +13152,7 @@
         <v/>
       </c>
       <c r="AJ183" s="34">
-        <f>(O183+Q183+V183+X183+Y183+L183)/(1-(M183++(1-H183)*++Z183+AB183))</f>
+        <f>(O183+Q183+V183+X183+Y183+L183)/(1-(M183+$G$4+(1-H183)*$G$3+$G$8+Z183+AB183))</f>
         <v/>
       </c>
     </row>
@@ -13226,7 +13168,7 @@
       <c r="E184" s="27" t="n"/>
       <c r="F184" s="27" t="n"/>
       <c r="G184" s="27">
-        <f>(1.25*L184+O184+Q184+V184+X184+Y184)/(1-M184---(1-H184)*-Z184-AB184)</f>
+        <f>(1.25*L184+O184+Q184+V184+X184+Y184)/(1-M184-$G$8-$G$4-(1-H184)*$G$3-Z184-AB184)</f>
         <v/>
       </c>
       <c r="H184" s="28" t="n">
@@ -13239,10 +13181,9 @@
       <c r="J184" s="30" t="n">
         <v>385.05</v>
       </c>
-      <c r="K184" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K184" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L184" s="32">
         <f>J184+K184</f>
@@ -13259,18 +13200,18 @@
         <v>67</v>
       </c>
       <c r="P184" s="34">
-        <f>G184*</f>
+        <f>G184*$G$8</f>
         <v/>
       </c>
       <c r="Q184" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R184" s="34">
-        <f>G184*</f>
+        <f>G184*$G$4</f>
         <v/>
       </c>
       <c r="S184" s="34">
-        <f>I184*</f>
+        <f>I184*$G$3</f>
         <v/>
       </c>
       <c r="T184" s="36" t="n">
@@ -13287,11 +13228,11 @@
         <v>0.6</v>
       </c>
       <c r="X184" s="34">
-        <f>**W184</f>
+        <f>$G$6*$G$7*W184</f>
         <v/>
       </c>
       <c r="Y184" s="32">
-        <f>W184*(+0)</f>
+        <f>W184*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z184" s="33" t="n">
@@ -13333,7 +13274,7 @@
         <v/>
       </c>
       <c r="AJ184" s="34">
-        <f>(O184+Q184+V184+X184+Y184+L184)/(1-(M184++(1-H184)*++Z184+AB184))</f>
+        <f>(O184+Q184+V184+X184+Y184+L184)/(1-(M184+$G$4+(1-H184)*$G$3+$G$8+Z184+AB184))</f>
         <v/>
       </c>
     </row>
@@ -13392,7 +13333,7 @@
       <c r="E186" s="27" t="n"/>
       <c r="F186" s="27" t="n"/>
       <c r="G186" s="27">
-        <f>(1.25*L186+O186+Q186+V186+X186+Y186)/(1-M186---(1-H186)*-Z186-AB186)</f>
+        <f>(1.25*L186+O186+Q186+V186+X186+Y186)/(1-M186-$G$8-$G$4-(1-H186)*$G$3-Z186-AB186)</f>
         <v/>
       </c>
       <c r="H186" s="28" t="n">
@@ -13405,10 +13346,9 @@
       <c r="J186" s="30" t="n">
         <v>486.69</v>
       </c>
-      <c r="K186" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K186" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L186" s="32">
         <f>J186+K186</f>
@@ -13425,18 +13365,18 @@
         <v>67</v>
       </c>
       <c r="P186" s="34">
-        <f>G186*</f>
+        <f>G186*$G$8</f>
         <v/>
       </c>
       <c r="Q186" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R186" s="34">
-        <f>G186*</f>
+        <f>G186*$G$4</f>
         <v/>
       </c>
       <c r="S186" s="34">
-        <f>I186*</f>
+        <f>I186*$G$3</f>
         <v/>
       </c>
       <c r="T186" s="36" t="n">
@@ -13453,11 +13393,11 @@
         <v>0.93</v>
       </c>
       <c r="X186" s="34">
-        <f>**W186</f>
+        <f>$G$6*$G$7*W186</f>
         <v/>
       </c>
       <c r="Y186" s="32">
-        <f>W186*(+0)</f>
+        <f>W186*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z186" s="33" t="n">
@@ -13499,7 +13439,7 @@
         <v/>
       </c>
       <c r="AJ186" s="34">
-        <f>(O186+Q186+V186+X186+Y186+L186)/(1-(M186++(1-H186)*++Z186+AB186))</f>
+        <f>(O186+Q186+V186+X186+Y186+L186)/(1-(M186+$G$4+(1-H186)*$G$3+$G$8+Z186+AB186))</f>
         <v/>
       </c>
     </row>
@@ -13533,10 +13473,9 @@
       <c r="J187" s="30" t="n">
         <v>387.67</v>
       </c>
-      <c r="K187" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K187" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L187" s="32">
         <f>J187+K187</f>
@@ -13553,18 +13492,18 @@
         <v>67</v>
       </c>
       <c r="P187" s="34">
-        <f>G187*</f>
+        <f>G187*$G$8</f>
         <v/>
       </c>
       <c r="Q187" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R187" s="34">
-        <f>G187*</f>
+        <f>G187*$G$4</f>
         <v/>
       </c>
       <c r="S187" s="34">
-        <f>I187*</f>
+        <f>I187*$G$3</f>
         <v/>
       </c>
       <c r="T187" s="36" t="n">
@@ -13581,11 +13520,11 @@
         <v>0.6</v>
       </c>
       <c r="X187" s="34">
-        <f>**W187</f>
+        <f>$G$6*$G$7*W187</f>
         <v/>
       </c>
       <c r="Y187" s="32">
-        <f>W187*(+0)</f>
+        <f>W187*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z187" s="33" t="n">
@@ -13627,7 +13566,7 @@
         <v/>
       </c>
       <c r="AJ187" s="34">
-        <f>(O187+Q187+V187+X187+Y187+L187)/(1-(M187++(1-H187)*++Z187+AB187))</f>
+        <f>(O187+Q187+V187+X187+Y187+L187)/(1-(M187+$G$4+(1-H187)*$G$3+$G$8+Z187+AB187))</f>
         <v/>
       </c>
     </row>
@@ -13661,10 +13600,9 @@
       <c r="J188" s="30" t="n">
         <v>415.46</v>
       </c>
-      <c r="K188" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K188" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L188" s="32">
         <f>J188+K188</f>
@@ -13681,18 +13619,18 @@
         <v>67</v>
       </c>
       <c r="P188" s="34">
-        <f>G188*</f>
+        <f>G188*$G$8</f>
         <v/>
       </c>
       <c r="Q188" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R188" s="34">
-        <f>G188*</f>
+        <f>G188*$G$4</f>
         <v/>
       </c>
       <c r="S188" s="34">
-        <f>I188*</f>
+        <f>I188*$G$3</f>
         <v/>
       </c>
       <c r="T188" s="36" t="n">
@@ -13709,11 +13647,11 @@
         <v>0.6</v>
       </c>
       <c r="X188" s="34">
-        <f>**W188</f>
+        <f>$G$6*$G$7*W188</f>
         <v/>
       </c>
       <c r="Y188" s="32">
-        <f>W188*(+0)</f>
+        <f>W188*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z188" s="33" t="n">
@@ -13755,7 +13693,7 @@
         <v/>
       </c>
       <c r="AJ188" s="34">
-        <f>(O188+Q188+V188+X188+Y188+L188)/(1-(M188++(1-H188)*++Z188+AB188))</f>
+        <f>(O188+Q188+V188+X188+Y188+L188)/(1-(M188+$G$4+(1-H188)*$G$3+$G$8+Z188+AB188))</f>
         <v/>
       </c>
     </row>
@@ -13789,10 +13727,9 @@
       <c r="J189" s="30" t="n">
         <v>415.46</v>
       </c>
-      <c r="K189" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K189" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L189" s="32">
         <f>J189+K189</f>
@@ -13809,18 +13746,18 @@
         <v>67</v>
       </c>
       <c r="P189" s="34">
-        <f>G189*</f>
+        <f>G189*$G$8</f>
         <v/>
       </c>
       <c r="Q189" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R189" s="34">
-        <f>G189*</f>
+        <f>G189*$G$4</f>
         <v/>
       </c>
       <c r="S189" s="34">
-        <f>I189*</f>
+        <f>I189*$G$3</f>
         <v/>
       </c>
       <c r="T189" s="36" t="n">
@@ -13837,11 +13774,11 @@
         <v>0.6</v>
       </c>
       <c r="X189" s="34">
-        <f>**W189</f>
+        <f>$G$6*$G$7*W189</f>
         <v/>
       </c>
       <c r="Y189" s="32">
-        <f>W189*(+0)</f>
+        <f>W189*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z189" s="33" t="n">
@@ -13883,7 +13820,7 @@
         <v/>
       </c>
       <c r="AJ189" s="34">
-        <f>(O189+Q189+V189+X189+Y189+L189)/(1-(M189++(1-H189)*++Z189+AB189))</f>
+        <f>(O189+Q189+V189+X189+Y189+L189)/(1-(M189+$G$4+(1-H189)*$G$3+$G$8+Z189+AB189))</f>
         <v/>
       </c>
     </row>
@@ -13917,10 +13854,9 @@
       <c r="J190" s="30" t="n">
         <v>415.46</v>
       </c>
-      <c r="K190" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K190" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L190" s="32">
         <f>J190+K190</f>
@@ -13937,18 +13873,18 @@
         <v>67</v>
       </c>
       <c r="P190" s="34">
-        <f>G190*</f>
+        <f>G190*$G$8</f>
         <v/>
       </c>
       <c r="Q190" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R190" s="34">
-        <f>G190*</f>
+        <f>G190*$G$4</f>
         <v/>
       </c>
       <c r="S190" s="34">
-        <f>I190*</f>
+        <f>I190*$G$3</f>
         <v/>
       </c>
       <c r="T190" s="36" t="n">
@@ -13965,11 +13901,11 @@
         <v>0.6</v>
       </c>
       <c r="X190" s="34">
-        <f>**W190</f>
+        <f>$G$6*$G$7*W190</f>
         <v/>
       </c>
       <c r="Y190" s="32">
-        <f>W190*(+0)</f>
+        <f>W190*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z190" s="33" t="n">
@@ -14011,7 +13947,7 @@
         <v/>
       </c>
       <c r="AJ190" s="34">
-        <f>(O190+Q190+V190+X190+Y190+L190)/(1-(M190++(1-H190)*++Z190+AB190))</f>
+        <f>(O190+Q190+V190+X190+Y190+L190)/(1-(M190+$G$4+(1-H190)*$G$3+$G$8+Z190+AB190))</f>
         <v/>
       </c>
     </row>
@@ -14129,10 +14065,9 @@
       <c r="J193" s="30" t="n">
         <v>486.41</v>
       </c>
-      <c r="K193" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K193" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L193" s="32">
         <f>J193+K193</f>
@@ -14149,18 +14084,18 @@
         <v>72</v>
       </c>
       <c r="P193" s="34">
-        <f>G193*</f>
+        <f>G193*$G$8</f>
         <v/>
       </c>
       <c r="Q193" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R193" s="34">
-        <f>G193*</f>
+        <f>G193*$G$4</f>
         <v/>
       </c>
       <c r="S193" s="34">
-        <f>I193*</f>
+        <f>I193*$G$3</f>
         <v/>
       </c>
       <c r="T193" s="36" t="n">
@@ -14177,11 +14112,11 @@
         <v>1.1</v>
       </c>
       <c r="X193" s="34">
-        <f>**W193</f>
+        <f>$G$6*$G$7*W193</f>
         <v/>
       </c>
       <c r="Y193" s="32">
-        <f>W193*(+0)</f>
+        <f>W193*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z193" s="33" t="n">
@@ -14223,7 +14158,7 @@
         <v/>
       </c>
       <c r="AJ193" s="34">
-        <f>(O193+Q193+V193+X193+Y193+L193)/(1-(M193++(1-H193)*++Z193+AB193))</f>
+        <f>(O193+Q193+V193+X193+Y193+L193)/(1-(M193+$G$4+(1-H193)*$G$3+$G$8+Z193+AB193))</f>
         <v/>
       </c>
     </row>
@@ -14257,10 +14192,9 @@
       <c r="J194" s="30" t="n">
         <v>507.16</v>
       </c>
-      <c r="K194" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K194" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L194" s="32">
         <f>J194+K194</f>
@@ -14277,18 +14211,18 @@
         <v>72</v>
       </c>
       <c r="P194" s="34">
-        <f>G194*</f>
+        <f>G194*$G$8</f>
         <v/>
       </c>
       <c r="Q194" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R194" s="34">
-        <f>G194*</f>
+        <f>G194*$G$4</f>
         <v/>
       </c>
       <c r="S194" s="34">
-        <f>I194*</f>
+        <f>I194*$G$3</f>
         <v/>
       </c>
       <c r="T194" s="36" t="n">
@@ -14305,11 +14239,11 @@
         <v>1.1</v>
       </c>
       <c r="X194" s="34">
-        <f>**W194</f>
+        <f>$G$6*$G$7*W194</f>
         <v/>
       </c>
       <c r="Y194" s="32">
-        <f>W194*(+0)</f>
+        <f>W194*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z194" s="33" t="n">
@@ -14351,7 +14285,7 @@
         <v/>
       </c>
       <c r="AJ194" s="34">
-        <f>(O194+Q194+V194+X194+Y194+L194)/(1-(M194++(1-H194)*++Z194+AB194))</f>
+        <f>(O194+Q194+V194+X194+Y194+L194)/(1-(M194+$G$4+(1-H194)*$G$3+$G$8+Z194+AB194))</f>
         <v/>
       </c>
     </row>
@@ -14385,10 +14319,9 @@
       <c r="J195" s="30" t="n">
         <v>496.86</v>
       </c>
-      <c r="K195" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K195" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L195" s="32">
         <f>J195+K195</f>
@@ -14405,18 +14338,18 @@
         <v>72</v>
       </c>
       <c r="P195" s="34">
-        <f>G195*</f>
+        <f>G195*$G$8</f>
         <v/>
       </c>
       <c r="Q195" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R195" s="34">
-        <f>G195*</f>
+        <f>G195*$G$4</f>
         <v/>
       </c>
       <c r="S195" s="34">
-        <f>I195*</f>
+        <f>I195*$G$3</f>
         <v/>
       </c>
       <c r="T195" s="36" t="n">
@@ -14433,11 +14366,11 @@
         <v>1.1</v>
       </c>
       <c r="X195" s="34">
-        <f>**W195</f>
+        <f>$G$6*$G$7*W195</f>
         <v/>
       </c>
       <c r="Y195" s="32">
-        <f>W195*(+0)</f>
+        <f>W195*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z195" s="33" t="n">
@@ -14479,7 +14412,7 @@
         <v/>
       </c>
       <c r="AJ195" s="34">
-        <f>(O195+Q195+V195+X195+Y195+L195)/(1-(M195++(1-H195)*++Z195+AB195))</f>
+        <f>(O195+Q195+V195+X195+Y195+L195)/(1-(M195+$G$4+(1-H195)*$G$3+$G$8+Z195+AB195))</f>
         <v/>
       </c>
     </row>
@@ -14513,10 +14446,9 @@
       <c r="J196" s="30" t="n">
         <v>498.54</v>
       </c>
-      <c r="K196" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K196" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L196" s="32">
         <f>J196+K196</f>
@@ -14533,18 +14465,18 @@
         <v>72</v>
       </c>
       <c r="P196" s="34">
-        <f>G196*</f>
+        <f>G196*$G$8</f>
         <v/>
       </c>
       <c r="Q196" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R196" s="34">
-        <f>G196*</f>
+        <f>G196*$G$4</f>
         <v/>
       </c>
       <c r="S196" s="34">
-        <f>I196*</f>
+        <f>I196*$G$3</f>
         <v/>
       </c>
       <c r="T196" s="36" t="n">
@@ -14561,11 +14493,11 @@
         <v>1.1</v>
       </c>
       <c r="X196" s="34">
-        <f>**W196</f>
+        <f>$G$6*$G$7*W196</f>
         <v/>
       </c>
       <c r="Y196" s="32">
-        <f>W196*(+0)</f>
+        <f>W196*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z196" s="33" t="n">
@@ -14607,7 +14539,7 @@
         <v/>
       </c>
       <c r="AJ196" s="34">
-        <f>(O196+Q196+V196+X196+Y196+L196)/(1-(M196++(1-H196)*++Z196+AB196))</f>
+        <f>(O196+Q196+V196+X196+Y196+L196)/(1-(M196+$G$4+(1-H196)*$G$3+$G$8+Z196+AB196))</f>
         <v/>
       </c>
     </row>
@@ -14641,10 +14573,9 @@
       <c r="J197" s="30" t="n">
         <v>478.17</v>
       </c>
-      <c r="K197" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K197" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L197" s="32">
         <f>J197+K197</f>
@@ -14661,18 +14592,18 @@
         <v>72</v>
       </c>
       <c r="P197" s="34">
-        <f>G197*</f>
+        <f>G197*$G$8</f>
         <v/>
       </c>
       <c r="Q197" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R197" s="34">
-        <f>G197*</f>
+        <f>G197*$G$4</f>
         <v/>
       </c>
       <c r="S197" s="34">
-        <f>I197*</f>
+        <f>I197*$G$3</f>
         <v/>
       </c>
       <c r="T197" s="36" t="n">
@@ -14689,11 +14620,11 @@
         <v>1.1</v>
       </c>
       <c r="X197" s="34">
-        <f>**W197</f>
+        <f>$G$6*$G$7*W197</f>
         <v/>
       </c>
       <c r="Y197" s="32">
-        <f>W197*(+0)</f>
+        <f>W197*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z197" s="33" t="n">
@@ -14735,7 +14666,7 @@
         <v/>
       </c>
       <c r="AJ197" s="34">
-        <f>(O197+Q197+V197+X197+Y197+L197)/(1-(M197++(1-H197)*++Z197+AB197))</f>
+        <f>(O197+Q197+V197+X197+Y197+L197)/(1-(M197+$G$4+(1-H197)*$G$3+$G$8+Z197+AB197))</f>
         <v/>
       </c>
     </row>
@@ -14769,10 +14700,9 @@
       <c r="J198" s="30" t="n">
         <v>478.05</v>
       </c>
-      <c r="K198" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K198" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L198" s="32">
         <f>J198+K198</f>
@@ -14789,18 +14719,18 @@
         <v>72</v>
       </c>
       <c r="P198" s="34">
-        <f>G198*</f>
+        <f>G198*$G$8</f>
         <v/>
       </c>
       <c r="Q198" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R198" s="34">
-        <f>G198*</f>
+        <f>G198*$G$4</f>
         <v/>
       </c>
       <c r="S198" s="34">
-        <f>I198*</f>
+        <f>I198*$G$3</f>
         <v/>
       </c>
       <c r="T198" s="36" t="n">
@@ -14817,11 +14747,11 @@
         <v>1.1</v>
       </c>
       <c r="X198" s="34">
-        <f>**W198</f>
+        <f>$G$6*$G$7*W198</f>
         <v/>
       </c>
       <c r="Y198" s="32">
-        <f>W198*(+0)</f>
+        <f>W198*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z198" s="33" t="n">
@@ -14863,7 +14793,7 @@
         <v/>
       </c>
       <c r="AJ198" s="34">
-        <f>(O198+Q198+V198+X198+Y198+L198)/(1-(M198++(1-H198)*++Z198+AB198))</f>
+        <f>(O198+Q198+V198+X198+Y198+L198)/(1-(M198+$G$4+(1-H198)*$G$3+$G$8+Z198+AB198))</f>
         <v/>
       </c>
     </row>
@@ -15065,10 +14995,9 @@
       <c r="J203" s="30" t="n">
         <v>463.19</v>
       </c>
-      <c r="K203" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K203" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L203" s="32">
         <f>J203+K203</f>
@@ -15085,18 +15014,18 @@
         <v>74</v>
       </c>
       <c r="P203" s="34">
-        <f>G203*</f>
+        <f>G203*$G$8</f>
         <v/>
       </c>
       <c r="Q203" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R203" s="34">
-        <f>G203*</f>
+        <f>G203*$G$4</f>
         <v/>
       </c>
       <c r="S203" s="34">
-        <f>I203*</f>
+        <f>I203*$G$3</f>
         <v/>
       </c>
       <c r="T203" s="36" t="n">
@@ -15113,11 +15042,11 @@
         <v>1.28</v>
       </c>
       <c r="X203" s="34">
-        <f>**W203</f>
+        <f>$G$6*$G$7*W203</f>
         <v/>
       </c>
       <c r="Y203" s="32">
-        <f>W203*(+0)</f>
+        <f>W203*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z203" s="33" t="n">
@@ -15159,7 +15088,7 @@
         <v/>
       </c>
       <c r="AJ203" s="34">
-        <f>(O203+Q203+V203+X203+Y203+L203)/(1-(M203++(1-H203)*++Z203+AB203))</f>
+        <f>(O203+Q203+V203+X203+Y203+L203)/(1-(M203+$G$4+(1-H203)*$G$3+$G$8+Z203+AB203))</f>
         <v/>
       </c>
     </row>
@@ -15259,7 +15188,7 @@
       <c r="E206" s="27" t="n"/>
       <c r="F206" s="27" t="n"/>
       <c r="G206" s="27">
-        <f>(1.25*L206+O206+Q206+V206+X206+Y206)/(1-M206---(1-H206)*-Z206-AB206)</f>
+        <f>(1.25*L206+O206+Q206+V206+X206+Y206)/(1-M206-$G$8-$G$4-(1-H206)*$G$3-Z206-AB206)</f>
         <v/>
       </c>
       <c r="H206" s="28" t="n">
@@ -15272,10 +15201,9 @@
       <c r="J206" s="30" t="n">
         <v>512.3200000000001</v>
       </c>
-      <c r="K206" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K206" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L206" s="32">
         <f>J206+K206</f>
@@ -15292,18 +15220,18 @@
         <v>67</v>
       </c>
       <c r="P206" s="34">
-        <f>G206*</f>
+        <f>G206*$G$8</f>
         <v/>
       </c>
       <c r="Q206" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R206" s="34">
-        <f>G206*</f>
+        <f>G206*$G$4</f>
         <v/>
       </c>
       <c r="S206" s="34">
-        <f>I206*</f>
+        <f>I206*$G$3</f>
         <v/>
       </c>
       <c r="T206" s="36" t="n">
@@ -15320,11 +15248,11 @@
         <v>0.8</v>
       </c>
       <c r="X206" s="34">
-        <f>**W206</f>
+        <f>$G$6*$G$7*W206</f>
         <v/>
       </c>
       <c r="Y206" s="32">
-        <f>W206*(+0)</f>
+        <f>W206*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z206" s="33" t="n">
@@ -15366,7 +15294,7 @@
         <v/>
       </c>
       <c r="AJ206" s="34">
-        <f>(O206+Q206+V206+X206+Y206+L206)/(1-(M206++(1-H206)*++Z206+AB206))</f>
+        <f>(O206+Q206+V206+X206+Y206+L206)/(1-(M206+$G$4+(1-H206)*$G$3+$G$8+Z206+AB206))</f>
         <v/>
       </c>
     </row>
@@ -15736,10 +15664,9 @@
       <c r="J215" s="30" t="n">
         <v>463.19</v>
       </c>
-      <c r="K215" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K215" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L215" s="32">
         <f>J215+K215</f>
@@ -15756,18 +15683,18 @@
         <v>74</v>
       </c>
       <c r="P215" s="34">
-        <f>G215*</f>
+        <f>G215*$G$8</f>
         <v/>
       </c>
       <c r="Q215" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R215" s="34">
-        <f>G215*</f>
+        <f>G215*$G$4</f>
         <v/>
       </c>
       <c r="S215" s="34">
-        <f>I215*</f>
+        <f>I215*$G$3</f>
         <v/>
       </c>
       <c r="T215" s="36" t="n">
@@ -15784,11 +15711,11 @@
         <v>1.28</v>
       </c>
       <c r="X215" s="34">
-        <f>**W215</f>
+        <f>$G$6*$G$7*W215</f>
         <v/>
       </c>
       <c r="Y215" s="32">
-        <f>W215*(+0)</f>
+        <f>W215*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z215" s="33" t="n">
@@ -15830,7 +15757,7 @@
         <v/>
       </c>
       <c r="AJ215" s="34">
-        <f>(O215+Q215+V215+X215+Y215+L215)/(1-(M215++(1-H215)*++Z215+AB215))</f>
+        <f>(O215+Q215+V215+X215+Y215+L215)/(1-(M215+$G$4+(1-H215)*$G$3+$G$8+Z215+AB215))</f>
         <v/>
       </c>
     </row>
@@ -15908,10 +15835,9 @@
       <c r="J217" s="30" t="n">
         <v>406</v>
       </c>
-      <c r="K217" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K217" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L217" s="32">
         <f>J217+K217</f>
@@ -15928,18 +15854,18 @@
         <v>74</v>
       </c>
       <c r="P217" s="34">
-        <f>G217*</f>
+        <f>G217*$G$8</f>
         <v/>
       </c>
       <c r="Q217" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R217" s="34">
-        <f>G217*</f>
+        <f>G217*$G$4</f>
         <v/>
       </c>
       <c r="S217" s="34">
-        <f>I217*</f>
+        <f>I217*$G$3</f>
         <v/>
       </c>
       <c r="T217" s="36" t="n">
@@ -15956,11 +15882,11 @@
         <v>1.28</v>
       </c>
       <c r="X217" s="34">
-        <f>**W217</f>
+        <f>$G$6*$G$7*W217</f>
         <v/>
       </c>
       <c r="Y217" s="32">
-        <f>W217*(+0)</f>
+        <f>W217*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z217" s="33" t="n">
@@ -16002,7 +15928,7 @@
         <v/>
       </c>
       <c r="AJ217" s="34">
-        <f>(O217+Q217+V217+X217+Y217+L217)/(1-(M217++(1-H217)*++Z217+AB217))</f>
+        <f>(O217+Q217+V217+X217+Y217+L217)/(1-(M217+$G$4+(1-H217)*$G$3+$G$8+Z217+AB217))</f>
         <v/>
       </c>
     </row>
@@ -16038,10 +15964,9 @@
       <c r="J218" s="30" t="n">
         <v>483</v>
       </c>
-      <c r="K218" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K218" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L218" s="32">
         <f>J218+K218</f>
@@ -16058,18 +15983,18 @@
         <v>74</v>
       </c>
       <c r="P218" s="34">
-        <f>G218*</f>
+        <f>G218*$G$8</f>
         <v/>
       </c>
       <c r="Q218" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R218" s="34">
-        <f>G218*</f>
+        <f>G218*$G$4</f>
         <v/>
       </c>
       <c r="S218" s="34">
-        <f>I218*</f>
+        <f>I218*$G$3</f>
         <v/>
       </c>
       <c r="T218" s="36" t="n">
@@ -16086,11 +16011,11 @@
         <v>1.28</v>
       </c>
       <c r="X218" s="34">
-        <f>**W218</f>
+        <f>$G$6*$G$7*W218</f>
         <v/>
       </c>
       <c r="Y218" s="32">
-        <f>W218*(+0)</f>
+        <f>W218*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z218" s="33" t="n">
@@ -16132,7 +16057,7 @@
         <v/>
       </c>
       <c r="AJ218" s="34">
-        <f>(O218+Q218+V218+X218+Y218+L218)/(1-(M218++(1-H218)*++Z218+AB218))</f>
+        <f>(O218+Q218+V218+X218+Y218+L218)/(1-(M218+$G$4+(1-H218)*$G$3+$G$8+Z218+AB218))</f>
         <v/>
       </c>
     </row>
@@ -16168,10 +16093,9 @@
       <c r="J219" s="30" t="n">
         <v>712</v>
       </c>
-      <c r="K219" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K219" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L219" s="32">
         <f>J219+K219</f>
@@ -16188,18 +16112,18 @@
         <v>74</v>
       </c>
       <c r="P219" s="34">
-        <f>G219*</f>
+        <f>G219*$G$8</f>
         <v/>
       </c>
       <c r="Q219" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R219" s="34">
-        <f>G219*</f>
+        <f>G219*$G$4</f>
         <v/>
       </c>
       <c r="S219" s="34">
-        <f>I219*</f>
+        <f>I219*$G$3</f>
         <v/>
       </c>
       <c r="T219" s="36" t="n">
@@ -16216,11 +16140,11 @@
         <v>1.28</v>
       </c>
       <c r="X219" s="34">
-        <f>**W219</f>
+        <f>$G$6*$G$7*W219</f>
         <v/>
       </c>
       <c r="Y219" s="32">
-        <f>W219*(+0)</f>
+        <f>W219*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z219" s="33" t="n">
@@ -16262,7 +16186,7 @@
         <v/>
       </c>
       <c r="AJ219" s="34">
-        <f>(O219+Q219+V219+X219+Y219+L219)/(1-(M219++(1-H219)*++Z219+AB219))</f>
+        <f>(O219+Q219+V219+X219+Y219+L219)/(1-(M219+$G$4+(1-H219)*$G$3+$G$8+Z219+AB219))</f>
         <v/>
       </c>
     </row>
@@ -16298,10 +16222,9 @@
       <c r="J220" s="30" t="n">
         <v>761</v>
       </c>
-      <c r="K220" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K220" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L220" s="32">
         <f>J220+K220</f>
@@ -16318,18 +16241,18 @@
         <v>74</v>
       </c>
       <c r="P220" s="34">
-        <f>G220*</f>
+        <f>G220*$G$8</f>
         <v/>
       </c>
       <c r="Q220" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R220" s="34">
-        <f>G220*</f>
+        <f>G220*$G$4</f>
         <v/>
       </c>
       <c r="S220" s="34">
-        <f>I220*</f>
+        <f>I220*$G$3</f>
         <v/>
       </c>
       <c r="T220" s="36" t="n">
@@ -16346,11 +16269,11 @@
         <v>1.28</v>
       </c>
       <c r="X220" s="34">
-        <f>**W220</f>
+        <f>$G$6*$G$7*W220</f>
         <v/>
       </c>
       <c r="Y220" s="32">
-        <f>W220*(+0)</f>
+        <f>W220*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z220" s="33" t="n">
@@ -16392,7 +16315,7 @@
         <v/>
       </c>
       <c r="AJ220" s="34">
-        <f>(O220+Q220+V220+X220+Y220+L220)/(1-(M220++(1-H220)*++Z220+AB220))</f>
+        <f>(O220+Q220+V220+X220+Y220+L220)/(1-(M220+$G$4+(1-H220)*$G$3+$G$8+Z220+AB220))</f>
         <v/>
       </c>
     </row>
@@ -16428,10 +16351,9 @@
       <c r="J221" s="30" t="n">
         <v>636</v>
       </c>
-      <c r="K221" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K221" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L221" s="32">
         <f>J221+K221</f>
@@ -16448,18 +16370,18 @@
         <v>74</v>
       </c>
       <c r="P221" s="34">
-        <f>G221*</f>
+        <f>G221*$G$8</f>
         <v/>
       </c>
       <c r="Q221" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R221" s="34">
-        <f>G221*</f>
+        <f>G221*$G$4</f>
         <v/>
       </c>
       <c r="S221" s="34">
-        <f>I221*</f>
+        <f>I221*$G$3</f>
         <v/>
       </c>
       <c r="T221" s="36" t="n">
@@ -16476,11 +16398,11 @@
         <v>1.28</v>
       </c>
       <c r="X221" s="34">
-        <f>**W221</f>
+        <f>$G$6*$G$7*W221</f>
         <v/>
       </c>
       <c r="Y221" s="32">
-        <f>W221*(+0)</f>
+        <f>W221*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z221" s="33" t="n">
@@ -16522,7 +16444,7 @@
         <v/>
       </c>
       <c r="AJ221" s="34">
-        <f>(O221+Q221+V221+X221+Y221+L221)/(1-(M221++(1-H221)*++Z221+AB221))</f>
+        <f>(O221+Q221+V221+X221+Y221+L221)/(1-(M221+$G$4+(1-H221)*$G$3+$G$8+Z221+AB221))</f>
         <v/>
       </c>
     </row>
@@ -16558,10 +16480,9 @@
       <c r="J222" s="30" t="n">
         <v>668</v>
       </c>
-      <c r="K222" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K222" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L222" s="32">
         <f>J222+K222</f>
@@ -16578,18 +16499,18 @@
         <v>74</v>
       </c>
       <c r="P222" s="34">
-        <f>G222*</f>
+        <f>G222*$G$8</f>
         <v/>
       </c>
       <c r="Q222" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R222" s="34">
-        <f>G222*</f>
+        <f>G222*$G$4</f>
         <v/>
       </c>
       <c r="S222" s="34">
-        <f>I222*</f>
+        <f>I222*$G$3</f>
         <v/>
       </c>
       <c r="T222" s="36" t="n">
@@ -16606,11 +16527,11 @@
         <v>1.28</v>
       </c>
       <c r="X222" s="34">
-        <f>**W222</f>
+        <f>$G$6*$G$7*W222</f>
         <v/>
       </c>
       <c r="Y222" s="32">
-        <f>W222*(+0)</f>
+        <f>W222*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z222" s="33" t="n">
@@ -16652,7 +16573,7 @@
         <v/>
       </c>
       <c r="AJ222" s="34">
-        <f>(O222+Q222+V222+X222+Y222+L222)/(1-(M222++(1-H222)*++Z222+AB222))</f>
+        <f>(O222+Q222+V222+X222+Y222+L222)/(1-(M222+$G$4+(1-H222)*$G$3+$G$8+Z222+AB222))</f>
         <v/>
       </c>
     </row>
@@ -16688,10 +16609,9 @@
       <c r="J223" s="30" t="n">
         <v>378</v>
       </c>
-      <c r="K223" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K223" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L223" s="32">
         <f>J223+K223</f>
@@ -16708,18 +16628,18 @@
         <v>74</v>
       </c>
       <c r="P223" s="34">
-        <f>G223*</f>
+        <f>G223*$G$8</f>
         <v/>
       </c>
       <c r="Q223" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R223" s="34">
-        <f>G223*</f>
+        <f>G223*$G$4</f>
         <v/>
       </c>
       <c r="S223" s="34">
-        <f>I223*</f>
+        <f>I223*$G$3</f>
         <v/>
       </c>
       <c r="T223" s="36" t="n">
@@ -16736,11 +16656,11 @@
         <v>1.28</v>
       </c>
       <c r="X223" s="34">
-        <f>**W223</f>
+        <f>$G$6*$G$7*W223</f>
         <v/>
       </c>
       <c r="Y223" s="32">
-        <f>W223*(+0)</f>
+        <f>W223*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z223" s="33" t="n">
@@ -16782,7 +16702,7 @@
         <v/>
       </c>
       <c r="AJ223" s="34">
-        <f>(O223+Q223+V223+X223+Y223+L223)/(1-(M223++(1-H223)*++Z223+AB223))</f>
+        <f>(O223+Q223+V223+X223+Y223+L223)/(1-(M223+$G$4+(1-H223)*$G$3+$G$8+Z223+AB223))</f>
         <v/>
       </c>
     </row>
@@ -17280,10 +17200,9 @@
       <c r="J235" s="30" t="n">
         <v>663.86</v>
       </c>
-      <c r="K235" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K235" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L235" s="32">
         <f>J235+K235</f>
@@ -17300,18 +17219,18 @@
         <v>67</v>
       </c>
       <c r="P235" s="34">
-        <f>G235*</f>
+        <f>G235*$G$8</f>
         <v/>
       </c>
       <c r="Q235" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R235" s="34">
-        <f>G235*</f>
+        <f>G235*$G$4</f>
         <v/>
       </c>
       <c r="S235" s="34">
-        <f>I235*</f>
+        <f>I235*$G$3</f>
         <v/>
       </c>
       <c r="T235" s="36" t="n">
@@ -17328,11 +17247,11 @@
         <v>0.735</v>
       </c>
       <c r="X235" s="34">
-        <f>**W235</f>
+        <f>$G$6*$G$7*W235</f>
         <v/>
       </c>
       <c r="Y235" s="32">
-        <f>W235*(+0)</f>
+        <f>W235*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z235" s="33" t="n">
@@ -17374,7 +17293,7 @@
         <v/>
       </c>
       <c r="AJ235" s="34">
-        <f>(O235+Q235+V235+X235+Y235+L235)/(1-(M235++(1-H235)*++Z235+AB235))</f>
+        <f>(O235+Q235+V235+X235+Y235+L235)/(1-(M235+$G$4+(1-H235)*$G$3+$G$8+Z235+AB235))</f>
         <v/>
       </c>
     </row>
@@ -17408,10 +17327,9 @@
       <c r="J236" s="30" t="n">
         <v>512.1799999999999</v>
       </c>
-      <c r="K236" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K236" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L236" s="32">
         <f>J236+K236</f>
@@ -17428,18 +17346,18 @@
         <v>56</v>
       </c>
       <c r="P236" s="34">
-        <f>G236*</f>
+        <f>G236*$G$8</f>
         <v/>
       </c>
       <c r="Q236" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R236" s="34">
-        <f>G236*</f>
+        <f>G236*$G$4</f>
         <v/>
       </c>
       <c r="S236" s="34">
-        <f>I236*</f>
+        <f>I236*$G$3</f>
         <v/>
       </c>
       <c r="T236" s="36" t="n">
@@ -17456,11 +17374,11 @@
         <v>0.18</v>
       </c>
       <c r="X236" s="34">
-        <f>**W236</f>
+        <f>$G$6*$G$7*W236</f>
         <v/>
       </c>
       <c r="Y236" s="32">
-        <f>W236*(+0)</f>
+        <f>W236*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z236" s="33" t="n">
@@ -17502,7 +17420,7 @@
         <v/>
       </c>
       <c r="AJ236" s="34">
-        <f>(O236+Q236+V236+X236+Y236+L236)/(1-(M236++(1-H236)*++Z236+AB236))</f>
+        <f>(O236+Q236+V236+X236+Y236+L236)/(1-(M236+$G$4+(1-H236)*$G$3+$G$8+Z236+AB236))</f>
         <v/>
       </c>
     </row>
@@ -17540,10 +17458,9 @@
       <c r="J237" s="30" t="n">
         <v>532.1</v>
       </c>
-      <c r="K237" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K237" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L237" s="32">
         <f>J237+K237</f>
@@ -17560,18 +17477,18 @@
         <v>63</v>
       </c>
       <c r="P237" s="34">
-        <f>G237*</f>
+        <f>G237*$G$8</f>
         <v/>
       </c>
       <c r="Q237" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R237" s="34">
-        <f>G237*</f>
+        <f>G237*$G$4</f>
         <v/>
       </c>
       <c r="S237" s="34">
-        <f>I237*</f>
+        <f>I237*$G$3</f>
         <v/>
       </c>
       <c r="T237" s="36" t="n">
@@ -17588,11 +17505,11 @@
         <v>0.38</v>
       </c>
       <c r="X237" s="34">
-        <f>**W237</f>
+        <f>$G$6*$G$7*W237</f>
         <v/>
       </c>
       <c r="Y237" s="32">
-        <f>W237*(+0)</f>
+        <f>W237*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z237" s="33" t="n">
@@ -17634,7 +17551,7 @@
         <v/>
       </c>
       <c r="AJ237" s="34">
-        <f>(O237+Q237+V237+X237+Y237+L237)/(1-(M237++(1-H237)*++Z237+AB237))</f>
+        <f>(O237+Q237+V237+X237+Y237+L237)/(1-(M237+$G$4+(1-H237)*$G$3+$G$8+Z237+AB237))</f>
         <v/>
       </c>
     </row>
@@ -17670,10 +17587,9 @@
       <c r="J238" s="30" t="n">
         <v>343</v>
       </c>
-      <c r="K238" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K238" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L238" s="32">
         <f>J238+K238</f>
@@ -17690,18 +17606,18 @@
         <v>67</v>
       </c>
       <c r="P238" s="34">
-        <f>G238*</f>
+        <f>G238*$G$8</f>
         <v/>
       </c>
       <c r="Q238" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R238" s="34">
-        <f>G238*</f>
+        <f>G238*$G$4</f>
         <v/>
       </c>
       <c r="S238" s="34">
-        <f>I238*</f>
+        <f>I238*$G$3</f>
         <v/>
       </c>
       <c r="T238" s="36" t="n">
@@ -17718,11 +17634,11 @@
         <v>0.96</v>
       </c>
       <c r="X238" s="34">
-        <f>**W238</f>
+        <f>$G$6*$G$7*W238</f>
         <v/>
       </c>
       <c r="Y238" s="32">
-        <f>W238*(+0)</f>
+        <f>W238*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z238" s="33" t="n">
@@ -17764,7 +17680,7 @@
         <v/>
       </c>
       <c r="AJ238" s="34">
-        <f>(O238+Q238+V238+X238+Y238+L238)/(1-(M238++(1-H238)*++Z238+AB238))</f>
+        <f>(O238+Q238+V238+X238+Y238+L238)/(1-(M238+$G$4+(1-H238)*$G$3+$G$8+Z238+AB238))</f>
         <v/>
       </c>
     </row>
@@ -17800,10 +17716,9 @@
       <c r="J239" s="30" t="n">
         <v>483</v>
       </c>
-      <c r="K239" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K239" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L239" s="32">
         <f>J239+K239</f>
@@ -17820,18 +17735,18 @@
         <v>67</v>
       </c>
       <c r="P239" s="34">
-        <f>G239*</f>
+        <f>G239*$G$8</f>
         <v/>
       </c>
       <c r="Q239" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R239" s="34">
-        <f>G239*</f>
+        <f>G239*$G$4</f>
         <v/>
       </c>
       <c r="S239" s="34">
-        <f>I239*</f>
+        <f>I239*$G$3</f>
         <v/>
       </c>
       <c r="T239" s="36" t="n">
@@ -17848,11 +17763,11 @@
         <v>0.96</v>
       </c>
       <c r="X239" s="34">
-        <f>**W239</f>
+        <f>$G$6*$G$7*W239</f>
         <v/>
       </c>
       <c r="Y239" s="32">
-        <f>W239*(+0)</f>
+        <f>W239*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z239" s="33" t="n">
@@ -17894,7 +17809,7 @@
         <v/>
       </c>
       <c r="AJ239" s="34">
-        <f>(O239+Q239+V239+X239+Y239+L239)/(1-(M239++(1-H239)*++Z239+AB239))</f>
+        <f>(O239+Q239+V239+X239+Y239+L239)/(1-(M239+$G$4+(1-H239)*$G$3+$G$8+Z239+AB239))</f>
         <v/>
       </c>
     </row>
@@ -17930,10 +17845,9 @@
       <c r="J240" s="30" t="n">
         <v>96.94</v>
       </c>
-      <c r="K240" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K240" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L240" s="32">
         <f>J240+K240</f>
@@ -17950,18 +17864,18 @@
         <v>56</v>
       </c>
       <c r="P240" s="34">
-        <f>G240*</f>
+        <f>G240*$G$8</f>
         <v/>
       </c>
       <c r="Q240" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R240" s="34">
-        <f>G240*</f>
+        <f>G240*$G$4</f>
         <v/>
       </c>
       <c r="S240" s="34">
-        <f>I240*</f>
+        <f>I240*$G$3</f>
         <v/>
       </c>
       <c r="T240" s="36" t="n">
@@ -17978,11 +17892,11 @@
         <v>0.14</v>
       </c>
       <c r="X240" s="34">
-        <f>**W240</f>
+        <f>$G$6*$G$7*W240</f>
         <v/>
       </c>
       <c r="Y240" s="32">
-        <f>W240*(+0)</f>
+        <f>W240*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z240" s="33" t="n">
@@ -18024,7 +17938,7 @@
         <v/>
       </c>
       <c r="AJ240" s="34">
-        <f>(O240+Q240+V240+X240+Y240+L240)/(1-(M240++(1-H240)*++Z240+AB240))</f>
+        <f>(O240+Q240+V240+X240+Y240+L240)/(1-(M240+$G$4+(1-H240)*$G$3+$G$8+Z240+AB240))</f>
         <v/>
       </c>
     </row>
@@ -18186,10 +18100,9 @@
       <c r="J244" s="30" t="n">
         <v>707.88</v>
       </c>
-      <c r="K244" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K244" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L244" s="32">
         <f>J244+K244</f>
@@ -18206,18 +18119,18 @@
         <v>67</v>
       </c>
       <c r="P244" s="34">
-        <f>G244*</f>
+        <f>G244*$G$8</f>
         <v/>
       </c>
       <c r="Q244" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R244" s="34">
-        <f>G244*</f>
+        <f>G244*$G$4</f>
         <v/>
       </c>
       <c r="S244" s="34">
-        <f>I244*</f>
+        <f>I244*$G$3</f>
         <v/>
       </c>
       <c r="T244" s="36" t="n">
@@ -18234,11 +18147,11 @@
         <v>0.96</v>
       </c>
       <c r="X244" s="34">
-        <f>**W244</f>
+        <f>$G$6*$G$7*W244</f>
         <v/>
       </c>
       <c r="Y244" s="32">
-        <f>W244*(+0)</f>
+        <f>W244*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z244" s="33" t="n">
@@ -18280,7 +18193,7 @@
         <v/>
       </c>
       <c r="AJ244" s="34">
-        <f>(O244+Q244+V244+X244+Y244+L244)/(1-(M244++(1-H244)*++Z244+AB244))</f>
+        <f>(O244+Q244+V244+X244+Y244+L244)/(1-(M244+$G$4+(1-H244)*$G$3+$G$8+Z244+AB244))</f>
         <v/>
       </c>
     </row>
@@ -18358,10 +18271,9 @@
       <c r="J246" s="30" t="n">
         <v>556.1799999999999</v>
       </c>
-      <c r="K246" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K246" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L246" s="32">
         <f>J246+K246</f>
@@ -18378,18 +18290,18 @@
         <v>67</v>
       </c>
       <c r="P246" s="34">
-        <f>G246*</f>
+        <f>G246*$G$8</f>
         <v/>
       </c>
       <c r="Q246" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R246" s="34">
-        <f>G246*</f>
+        <f>G246*$G$4</f>
         <v/>
       </c>
       <c r="S246" s="34">
-        <f>I246*</f>
+        <f>I246*$G$3</f>
         <v/>
       </c>
       <c r="T246" s="36" t="n">
@@ -18406,11 +18318,11 @@
         <v>0.57</v>
       </c>
       <c r="X246" s="34">
-        <f>**W246</f>
+        <f>$G$6*$G$7*W246</f>
         <v/>
       </c>
       <c r="Y246" s="32">
-        <f>W246*(+0)</f>
+        <f>W246*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z246" s="33" t="n">
@@ -18452,7 +18364,7 @@
         <v/>
       </c>
       <c r="AJ246" s="34">
-        <f>(O246+Q246+V246+X246+Y246+L246)/(1-(M246++(1-H246)*++Z246+AB246))</f>
+        <f>(O246+Q246+V246+X246+Y246+L246)/(1-(M246+$G$4+(1-H246)*$G$3+$G$8+Z246+AB246))</f>
         <v/>
       </c>
     </row>
@@ -18572,10 +18484,9 @@
       <c r="J249" s="30" t="n">
         <v>467</v>
       </c>
-      <c r="K249" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K249" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L249" s="32">
         <f>J249+K249</f>
@@ -18592,18 +18503,18 @@
         <v>67</v>
       </c>
       <c r="P249" s="34">
-        <f>G249*</f>
+        <f>G249*$G$8</f>
         <v/>
       </c>
       <c r="Q249" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R249" s="34">
-        <f>G249*</f>
+        <f>G249*$G$4</f>
         <v/>
       </c>
       <c r="S249" s="34">
-        <f>I249*</f>
+        <f>I249*$G$3</f>
         <v/>
       </c>
       <c r="T249" s="36" t="n">
@@ -18620,11 +18531,11 @@
         <v>0.96</v>
       </c>
       <c r="X249" s="34">
-        <f>**W249</f>
+        <f>$G$6*$G$7*W249</f>
         <v/>
       </c>
       <c r="Y249" s="32">
-        <f>W249*(+0)</f>
+        <f>W249*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z249" s="33" t="n">
@@ -18666,7 +18577,7 @@
         <v/>
       </c>
       <c r="AJ249" s="34">
-        <f>(O249+Q249+V249+X249+Y249+L249)/(1-(M249++(1-H249)*++Z249+AB249))</f>
+        <f>(O249+Q249+V249+X249+Y249+L249)/(1-(M249+$G$4+(1-H249)*$G$3+$G$8+Z249+AB249))</f>
         <v/>
       </c>
     </row>
@@ -18702,10 +18613,9 @@
       <c r="J250" s="30" t="n">
         <v>417</v>
       </c>
-      <c r="K250" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K250" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L250" s="32">
         <f>J250+K250</f>
@@ -18722,18 +18632,18 @@
         <v>67</v>
       </c>
       <c r="P250" s="34">
-        <f>G250*</f>
+        <f>G250*$G$8</f>
         <v/>
       </c>
       <c r="Q250" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R250" s="34">
-        <f>G250*</f>
+        <f>G250*$G$4</f>
         <v/>
       </c>
       <c r="S250" s="34">
-        <f>I250*</f>
+        <f>I250*$G$3</f>
         <v/>
       </c>
       <c r="T250" s="36" t="n">
@@ -18750,11 +18660,11 @@
         <v>0.96</v>
       </c>
       <c r="X250" s="34">
-        <f>**W250</f>
+        <f>$G$6*$G$7*W250</f>
         <v/>
       </c>
       <c r="Y250" s="32">
-        <f>W250*(+0)</f>
+        <f>W250*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z250" s="33" t="n">
@@ -18796,7 +18706,7 @@
         <v/>
       </c>
       <c r="AJ250" s="34">
-        <f>(O250+Q250+V250+X250+Y250+L250)/(1-(M250++(1-H250)*++Z250+AB250))</f>
+        <f>(O250+Q250+V250+X250+Y250+L250)/(1-(M250+$G$4+(1-H250)*$G$3+$G$8+Z250+AB250))</f>
         <v/>
       </c>
     </row>
@@ -18832,10 +18742,9 @@
       <c r="J251" s="30" t="n">
         <v>452</v>
       </c>
-      <c r="K251" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K251" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L251" s="32">
         <f>J251+K251</f>
@@ -18852,18 +18761,18 @@
         <v>67</v>
       </c>
       <c r="P251" s="34">
-        <f>G251*</f>
+        <f>G251*$G$8</f>
         <v/>
       </c>
       <c r="Q251" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R251" s="34">
-        <f>G251*</f>
+        <f>G251*$G$4</f>
         <v/>
       </c>
       <c r="S251" s="34">
-        <f>I251*</f>
+        <f>I251*$G$3</f>
         <v/>
       </c>
       <c r="T251" s="36" t="n">
@@ -18880,11 +18789,11 @@
         <v>0.96</v>
       </c>
       <c r="X251" s="34">
-        <f>**W251</f>
+        <f>$G$6*$G$7*W251</f>
         <v/>
       </c>
       <c r="Y251" s="32">
-        <f>W251*(+0)</f>
+        <f>W251*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z251" s="33" t="n">
@@ -18926,7 +18835,7 @@
         <v/>
       </c>
       <c r="AJ251" s="34">
-        <f>(O251+Q251+V251+X251+Y251+L251)/(1-(M251++(1-H251)*++Z251+AB251))</f>
+        <f>(O251+Q251+V251+X251+Y251+L251)/(1-(M251+$G$4+(1-H251)*$G$3+$G$8+Z251+AB251))</f>
         <v/>
       </c>
     </row>
@@ -18962,10 +18871,9 @@
       <c r="J252" s="30" t="n">
         <v>544</v>
       </c>
-      <c r="K252" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K252" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L252" s="32">
         <f>J252+K252</f>
@@ -18982,18 +18890,18 @@
         <v>67</v>
       </c>
       <c r="P252" s="34">
-        <f>G252*</f>
+        <f>G252*$G$8</f>
         <v/>
       </c>
       <c r="Q252" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R252" s="34">
-        <f>G252*</f>
+        <f>G252*$G$4</f>
         <v/>
       </c>
       <c r="S252" s="34">
-        <f>I252*</f>
+        <f>I252*$G$3</f>
         <v/>
       </c>
       <c r="T252" s="36" t="n">
@@ -19010,11 +18918,11 @@
         <v>0.96</v>
       </c>
       <c r="X252" s="34">
-        <f>**W252</f>
+        <f>$G$6*$G$7*W252</f>
         <v/>
       </c>
       <c r="Y252" s="32">
-        <f>W252*(+0)</f>
+        <f>W252*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z252" s="33" t="n">
@@ -19056,7 +18964,7 @@
         <v/>
       </c>
       <c r="AJ252" s="34">
-        <f>(O252+Q252+V252+X252+Y252+L252)/(1-(M252++(1-H252)*++Z252+AB252))</f>
+        <f>(O252+Q252+V252+X252+Y252+L252)/(1-(M252+$G$4+(1-H252)*$G$3+$G$8+Z252+AB252))</f>
         <v/>
       </c>
     </row>
@@ -19092,10 +19000,9 @@
       <c r="J253" s="30" t="n">
         <v>514</v>
       </c>
-      <c r="K253" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K253" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L253" s="32">
         <f>J253+K253</f>
@@ -19112,18 +19019,18 @@
         <v>67</v>
       </c>
       <c r="P253" s="34">
-        <f>G253*</f>
+        <f>G253*$G$8</f>
         <v/>
       </c>
       <c r="Q253" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R253" s="34">
-        <f>G253*</f>
+        <f>G253*$G$4</f>
         <v/>
       </c>
       <c r="S253" s="34">
-        <f>I253*</f>
+        <f>I253*$G$3</f>
         <v/>
       </c>
       <c r="T253" s="36" t="n">
@@ -19140,11 +19047,11 @@
         <v>0.96</v>
       </c>
       <c r="X253" s="34">
-        <f>**W253</f>
+        <f>$G$6*$G$7*W253</f>
         <v/>
       </c>
       <c r="Y253" s="32">
-        <f>W253*(+0)</f>
+        <f>W253*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z253" s="33" t="n">
@@ -19186,7 +19093,7 @@
         <v/>
       </c>
       <c r="AJ253" s="34">
-        <f>(O253+Q253+V253+X253+Y253+L253)/(1-(M253++(1-H253)*++Z253+AB253))</f>
+        <f>(O253+Q253+V253+X253+Y253+L253)/(1-(M253+$G$4+(1-H253)*$G$3+$G$8+Z253+AB253))</f>
         <v/>
       </c>
     </row>
@@ -19222,10 +19129,9 @@
       <c r="J254" s="30" t="n">
         <v>632</v>
       </c>
-      <c r="K254" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K254" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L254" s="32">
         <f>J254+K254</f>
@@ -19242,18 +19148,18 @@
         <v>67</v>
       </c>
       <c r="P254" s="34">
-        <f>G254*</f>
+        <f>G254*$G$8</f>
         <v/>
       </c>
       <c r="Q254" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R254" s="34">
-        <f>G254*</f>
+        <f>G254*$G$4</f>
         <v/>
       </c>
       <c r="S254" s="34">
-        <f>I254*</f>
+        <f>I254*$G$3</f>
         <v/>
       </c>
       <c r="T254" s="36" t="n">
@@ -19270,11 +19176,11 @@
         <v>0.96</v>
       </c>
       <c r="X254" s="34">
-        <f>**W254</f>
+        <f>$G$6*$G$7*W254</f>
         <v/>
       </c>
       <c r="Y254" s="32">
-        <f>W254*(+0)</f>
+        <f>W254*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z254" s="33" t="n">
@@ -19316,7 +19222,7 @@
         <v/>
       </c>
       <c r="AJ254" s="34">
-        <f>(O254+Q254+V254+X254+Y254+L254)/(1-(M254++(1-H254)*++Z254+AB254))</f>
+        <f>(O254+Q254+V254+X254+Y254+L254)/(1-(M254+$G$4+(1-H254)*$G$3+$G$8+Z254+AB254))</f>
         <v/>
       </c>
     </row>
@@ -19352,10 +19258,9 @@
       <c r="J255" s="30" t="n">
         <v>734</v>
       </c>
-      <c r="K255" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K255" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L255" s="32">
         <f>J255+K255</f>
@@ -19372,18 +19277,18 @@
         <v>67</v>
       </c>
       <c r="P255" s="34">
-        <f>G255*</f>
+        <f>G255*$G$8</f>
         <v/>
       </c>
       <c r="Q255" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R255" s="34">
-        <f>G255*</f>
+        <f>G255*$G$4</f>
         <v/>
       </c>
       <c r="S255" s="34">
-        <f>I255*</f>
+        <f>I255*$G$3</f>
         <v/>
       </c>
       <c r="T255" s="36" t="n">
@@ -19400,11 +19305,11 @@
         <v>0.96</v>
       </c>
       <c r="X255" s="34">
-        <f>**W255</f>
+        <f>$G$6*$G$7*W255</f>
         <v/>
       </c>
       <c r="Y255" s="32">
-        <f>W255*(+0)</f>
+        <f>W255*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z255" s="33" t="n">
@@ -19446,7 +19351,7 @@
         <v/>
       </c>
       <c r="AJ255" s="34">
-        <f>(O255+Q255+V255+X255+Y255+L255)/(1-(M255++(1-H255)*++Z255+AB255))</f>
+        <f>(O255+Q255+V255+X255+Y255+L255)/(1-(M255+$G$4+(1-H255)*$G$3+$G$8+Z255+AB255))</f>
         <v/>
       </c>
     </row>
@@ -19482,10 +19387,9 @@
       <c r="J256" s="30" t="n">
         <v>602</v>
       </c>
-      <c r="K256" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K256" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L256" s="32">
         <f>J256+K256</f>
@@ -19502,18 +19406,18 @@
         <v>67</v>
       </c>
       <c r="P256" s="34">
-        <f>G256*</f>
+        <f>G256*$G$8</f>
         <v/>
       </c>
       <c r="Q256" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R256" s="34">
-        <f>G256*</f>
+        <f>G256*$G$4</f>
         <v/>
       </c>
       <c r="S256" s="34">
-        <f>I256*</f>
+        <f>I256*$G$3</f>
         <v/>
       </c>
       <c r="T256" s="36" t="n">
@@ -19530,11 +19434,11 @@
         <v>0.96</v>
       </c>
       <c r="X256" s="34">
-        <f>**W256</f>
+        <f>$G$6*$G$7*W256</f>
         <v/>
       </c>
       <c r="Y256" s="32">
-        <f>W256*(+0)</f>
+        <f>W256*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z256" s="33" t="n">
@@ -19576,7 +19480,7 @@
         <v/>
       </c>
       <c r="AJ256" s="34">
-        <f>(O256+Q256+V256+X256+Y256+L256)/(1-(M256++(1-H256)*++Z256+AB256))</f>
+        <f>(O256+Q256+V256+X256+Y256+L256)/(1-(M256+$G$4+(1-H256)*$G$3+$G$8+Z256+AB256))</f>
         <v/>
       </c>
     </row>
@@ -19612,10 +19516,9 @@
       <c r="J257" s="30" t="n">
         <v>405</v>
       </c>
-      <c r="K257" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K257" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L257" s="32">
         <f>J257+K257</f>
@@ -19632,18 +19535,18 @@
         <v>67</v>
       </c>
       <c r="P257" s="34">
-        <f>G257*</f>
+        <f>G257*$G$8</f>
         <v/>
       </c>
       <c r="Q257" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R257" s="34">
-        <f>G257*</f>
+        <f>G257*$G$4</f>
         <v/>
       </c>
       <c r="S257" s="34">
-        <f>I257*</f>
+        <f>I257*$G$3</f>
         <v/>
       </c>
       <c r="T257" s="36" t="n">
@@ -19660,11 +19563,11 @@
         <v>0.96</v>
       </c>
       <c r="X257" s="34">
-        <f>**W257</f>
+        <f>$G$6*$G$7*W257</f>
         <v/>
       </c>
       <c r="Y257" s="32">
-        <f>W257*(+0)</f>
+        <f>W257*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z257" s="33" t="n">
@@ -19706,7 +19609,7 @@
         <v/>
       </c>
       <c r="AJ257" s="34">
-        <f>(O257+Q257+V257+X257+Y257+L257)/(1-(M257++(1-H257)*++Z257+AB257))</f>
+        <f>(O257+Q257+V257+X257+Y257+L257)/(1-(M257+$G$4+(1-H257)*$G$3+$G$8+Z257+AB257))</f>
         <v/>
       </c>
     </row>
@@ -19742,10 +19645,9 @@
       <c r="J258" s="30" t="n">
         <v>387</v>
       </c>
-      <c r="K258" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K258" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L258" s="32">
         <f>J258+K258</f>
@@ -19762,18 +19664,18 @@
         <v>67</v>
       </c>
       <c r="P258" s="34">
-        <f>G258*</f>
+        <f>G258*$G$8</f>
         <v/>
       </c>
       <c r="Q258" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R258" s="34">
-        <f>G258*</f>
+        <f>G258*$G$4</f>
         <v/>
       </c>
       <c r="S258" s="34">
-        <f>I258*</f>
+        <f>I258*$G$3</f>
         <v/>
       </c>
       <c r="T258" s="36" t="n">
@@ -19790,11 +19692,11 @@
         <v>0.96</v>
       </c>
       <c r="X258" s="34">
-        <f>**W258</f>
+        <f>$G$6*$G$7*W258</f>
         <v/>
       </c>
       <c r="Y258" s="32">
-        <f>W258*(+0)</f>
+        <f>W258*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z258" s="33" t="n">
@@ -19836,7 +19738,7 @@
         <v/>
       </c>
       <c r="AJ258" s="34">
-        <f>(O258+Q258+V258+X258+Y258+L258)/(1-(M258++(1-H258)*++Z258+AB258))</f>
+        <f>(O258+Q258+V258+X258+Y258+L258)/(1-(M258+$G$4+(1-H258)*$G$3+$G$8+Z258+AB258))</f>
         <v/>
       </c>
     </row>
@@ -19956,10 +19858,9 @@
       <c r="J261" s="30" t="n">
         <v>387</v>
       </c>
-      <c r="K261" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K261" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L261" s="32">
         <f>J261+K261</f>
@@ -19976,18 +19877,18 @@
         <v>67</v>
       </c>
       <c r="P261" s="34">
-        <f>G261*</f>
+        <f>G261*$G$8</f>
         <v/>
       </c>
       <c r="Q261" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R261" s="34">
-        <f>G261*</f>
+        <f>G261*$G$4</f>
         <v/>
       </c>
       <c r="S261" s="34">
-        <f>I261*</f>
+        <f>I261*$G$3</f>
         <v/>
       </c>
       <c r="T261" s="36" t="n">
@@ -20004,11 +19905,11 @@
         <v>0.96</v>
       </c>
       <c r="X261" s="34">
-        <f>**W261</f>
+        <f>$G$6*$G$7*W261</f>
         <v/>
       </c>
       <c r="Y261" s="32">
-        <f>W261*(+0)</f>
+        <f>W261*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z261" s="33" t="n">
@@ -20050,7 +19951,7 @@
         <v/>
       </c>
       <c r="AJ261" s="34">
-        <f>(O261+Q261+V261+X261+Y261+L261)/(1-(M261++(1-H261)*++Z261+AB261))</f>
+        <f>(O261+Q261+V261+X261+Y261+L261)/(1-(M261+$G$4+(1-H261)*$G$3+$G$8+Z261+AB261))</f>
         <v/>
       </c>
     </row>
@@ -20086,10 +19987,9 @@
       <c r="J262" s="30" t="n">
         <v>510</v>
       </c>
-      <c r="K262" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K262" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L262" s="32">
         <f>J262+K262</f>
@@ -20106,18 +20006,18 @@
         <v>67</v>
       </c>
       <c r="P262" s="34">
-        <f>G262*</f>
+        <f>G262*$G$8</f>
         <v/>
       </c>
       <c r="Q262" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R262" s="34">
-        <f>G262*</f>
+        <f>G262*$G$4</f>
         <v/>
       </c>
       <c r="S262" s="34">
-        <f>I262*</f>
+        <f>I262*$G$3</f>
         <v/>
       </c>
       <c r="T262" s="36" t="n">
@@ -20134,11 +20034,11 @@
         <v>0.96</v>
       </c>
       <c r="X262" s="34">
-        <f>**W262</f>
+        <f>$G$6*$G$7*W262</f>
         <v/>
       </c>
       <c r="Y262" s="32">
-        <f>W262*(+0)</f>
+        <f>W262*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z262" s="33" t="n">
@@ -20180,7 +20080,7 @@
         <v/>
       </c>
       <c r="AJ262" s="34">
-        <f>(O262+Q262+V262+X262+Y262+L262)/(1-(M262++(1-H262)*++Z262+AB262))</f>
+        <f>(O262+Q262+V262+X262+Y262+L262)/(1-(M262+$G$4+(1-H262)*$G$3+$G$8+Z262+AB262))</f>
         <v/>
       </c>
     </row>
@@ -20216,10 +20116,9 @@
       <c r="J263" s="30" t="n">
         <v>420</v>
       </c>
-      <c r="K263" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K263" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L263" s="32">
         <f>J263+K263</f>
@@ -20236,18 +20135,18 @@
         <v>67</v>
       </c>
       <c r="P263" s="34">
-        <f>G263*</f>
+        <f>G263*$G$8</f>
         <v/>
       </c>
       <c r="Q263" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R263" s="34">
-        <f>G263*</f>
+        <f>G263*$G$4</f>
         <v/>
       </c>
       <c r="S263" s="34">
-        <f>I263*</f>
+        <f>I263*$G$3</f>
         <v/>
       </c>
       <c r="T263" s="36" t="n">
@@ -20264,11 +20163,11 @@
         <v>0.96</v>
       </c>
       <c r="X263" s="34">
-        <f>**W263</f>
+        <f>$G$6*$G$7*W263</f>
         <v/>
       </c>
       <c r="Y263" s="32">
-        <f>W263*(+0)</f>
+        <f>W263*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z263" s="33" t="n">
@@ -20310,7 +20209,7 @@
         <v/>
       </c>
       <c r="AJ263" s="34">
-        <f>(O263+Q263+V263+X263+Y263+L263)/(1-(M263++(1-H263)*++Z263+AB263))</f>
+        <f>(O263+Q263+V263+X263+Y263+L263)/(1-(M263+$G$4+(1-H263)*$G$3+$G$8+Z263+AB263))</f>
         <v/>
       </c>
     </row>
@@ -20346,10 +20245,9 @@
       <c r="J264" s="30" t="n">
         <v>406</v>
       </c>
-      <c r="K264" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K264" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L264" s="32">
         <f>J264+K264</f>
@@ -20366,18 +20264,18 @@
         <v>67</v>
       </c>
       <c r="P264" s="34">
-        <f>G264*</f>
+        <f>G264*$G$8</f>
         <v/>
       </c>
       <c r="Q264" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R264" s="34">
-        <f>G264*</f>
+        <f>G264*$G$4</f>
         <v/>
       </c>
       <c r="S264" s="34">
-        <f>I264*</f>
+        <f>I264*$G$3</f>
         <v/>
       </c>
       <c r="T264" s="36" t="n">
@@ -20394,11 +20292,11 @@
         <v>0.96</v>
       </c>
       <c r="X264" s="34">
-        <f>**W264</f>
+        <f>$G$6*$G$7*W264</f>
         <v/>
       </c>
       <c r="Y264" s="32">
-        <f>W264*(+0)</f>
+        <f>W264*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z264" s="33" t="n">
@@ -20440,7 +20338,7 @@
         <v/>
       </c>
       <c r="AJ264" s="34">
-        <f>(O264+Q264+V264+X264+Y264+L264)/(1-(M264++(1-H264)*++Z264+AB264))</f>
+        <f>(O264+Q264+V264+X264+Y264+L264)/(1-(M264+$G$4+(1-H264)*$G$3+$G$8+Z264+AB264))</f>
         <v/>
       </c>
     </row>
@@ -20476,10 +20374,9 @@
       <c r="J265" s="30" t="n">
         <v>327</v>
       </c>
-      <c r="K265" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K265" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L265" s="32">
         <f>J265+K265</f>
@@ -20496,18 +20393,18 @@
         <v>67</v>
       </c>
       <c r="P265" s="34">
-        <f>G265*</f>
+        <f>G265*$G$8</f>
         <v/>
       </c>
       <c r="Q265" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R265" s="34">
-        <f>G265*</f>
+        <f>G265*$G$4</f>
         <v/>
       </c>
       <c r="S265" s="34">
-        <f>I265*</f>
+        <f>I265*$G$3</f>
         <v/>
       </c>
       <c r="T265" s="36" t="n">
@@ -20524,11 +20421,11 @@
         <v>0.96</v>
       </c>
       <c r="X265" s="34">
-        <f>**W265</f>
+        <f>$G$6*$G$7*W265</f>
         <v/>
       </c>
       <c r="Y265" s="32">
-        <f>W265*(+0)</f>
+        <f>W265*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z265" s="33" t="n">
@@ -20570,7 +20467,7 @@
         <v/>
       </c>
       <c r="AJ265" s="34">
-        <f>(O265+Q265+V265+X265+Y265+L265)/(1-(M265++(1-H265)*++Z265+AB265))</f>
+        <f>(O265+Q265+V265+X265+Y265+L265)/(1-(M265+$G$4+(1-H265)*$G$3+$G$8+Z265+AB265))</f>
         <v/>
       </c>
     </row>
@@ -20646,10 +20543,9 @@
       <c r="J267" s="30" t="n">
         <v>1335.95</v>
       </c>
-      <c r="K267" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K267" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L267" s="32">
         <f>J267+K267</f>
@@ -20666,18 +20562,18 @@
         <v>63</v>
       </c>
       <c r="P267" s="34">
-        <f>G267*</f>
+        <f>G267*$G$8</f>
         <v/>
       </c>
       <c r="Q267" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R267" s="34">
-        <f>G267*</f>
+        <f>G267*$G$4</f>
         <v/>
       </c>
       <c r="S267" s="34">
-        <f>I267*</f>
+        <f>I267*$G$3</f>
         <v/>
       </c>
       <c r="T267" s="36" t="n">
@@ -20694,11 +20590,11 @@
         <v>0.3</v>
       </c>
       <c r="X267" s="34">
-        <f>**W267</f>
+        <f>$G$6*$G$7*W267</f>
         <v/>
       </c>
       <c r="Y267" s="32">
-        <f>W267*(+0)</f>
+        <f>W267*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z267" s="33" t="n">
@@ -20740,7 +20636,7 @@
         <v/>
       </c>
       <c r="AJ267" s="34">
-        <f>(O267+Q267+V267+X267+Y267+L267)/(1-(M267++(1-H267)*++Z267+AB267))</f>
+        <f>(O267+Q267+V267+X267+Y267+L267)/(1-(M267+$G$4+(1-H267)*$G$3+$G$8+Z267+AB267))</f>
         <v/>
       </c>
     </row>
@@ -20774,10 +20670,9 @@
       <c r="J268" s="30" t="n">
         <v>974.04</v>
       </c>
-      <c r="K268" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K268" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L268" s="32">
         <f>J268+K268</f>
@@ -20794,18 +20689,18 @@
         <v>63</v>
       </c>
       <c r="P268" s="34">
-        <f>G268*</f>
+        <f>G268*$G$8</f>
         <v/>
       </c>
       <c r="Q268" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R268" s="34">
-        <f>G268*</f>
+        <f>G268*$G$4</f>
         <v/>
       </c>
       <c r="S268" s="34">
-        <f>I268*</f>
+        <f>I268*$G$3</f>
         <v/>
       </c>
       <c r="T268" s="36" t="n">
@@ -20822,11 +20717,11 @@
         <v>0.4</v>
       </c>
       <c r="X268" s="34">
-        <f>**W268</f>
+        <f>$G$6*$G$7*W268</f>
         <v/>
       </c>
       <c r="Y268" s="32">
-        <f>W268*(+0)</f>
+        <f>W268*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z268" s="33" t="n">
@@ -20868,7 +20763,7 @@
         <v/>
       </c>
       <c r="AJ268" s="34">
-        <f>(O268+Q268+V268+X268+Y268+L268)/(1-(M268++(1-H268)*++Z268+AB268))</f>
+        <f>(O268+Q268+V268+X268+Y268+L268)/(1-(M268+$G$4+(1-H268)*$G$3+$G$8+Z268+AB268))</f>
         <v/>
       </c>
     </row>
@@ -21282,10 +21177,9 @@
       <c r="J278" s="30" t="n">
         <v>261</v>
       </c>
-      <c r="K278" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K278" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L278" s="32">
         <f>J278+K278</f>
@@ -21302,18 +21196,18 @@
         <v>63</v>
       </c>
       <c r="P278" s="34">
-        <f>G278*</f>
+        <f>G278*$G$8</f>
         <v/>
       </c>
       <c r="Q278" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R278" s="34">
-        <f>G278*</f>
+        <f>G278*$G$4</f>
         <v/>
       </c>
       <c r="S278" s="34">
-        <f>I278*</f>
+        <f>I278*$G$3</f>
         <v/>
       </c>
       <c r="T278" s="36" t="n">
@@ -21330,11 +21224,11 @@
         <v>0.4</v>
       </c>
       <c r="X278" s="34">
-        <f>**W278</f>
+        <f>$G$6*$G$7*W278</f>
         <v/>
       </c>
       <c r="Y278" s="32">
-        <f>W278*(+0)</f>
+        <f>W278*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z278" s="33" t="n">
@@ -21376,7 +21270,7 @@
         <v/>
       </c>
       <c r="AJ278" s="34">
-        <f>(O278+Q278+V278+X278+Y278+L278)/(1-(M278++(1-H278)*++Z278+AB278))</f>
+        <f>(O278+Q278+V278+X278+Y278+L278)/(1-(M278+$G$4+(1-H278)*$G$3+$G$8+Z278+AB278))</f>
         <v/>
       </c>
     </row>
@@ -21412,10 +21306,9 @@
       <c r="J279" s="30" t="n">
         <v>293</v>
       </c>
-      <c r="K279" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K279" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L279" s="32">
         <f>J279+K279</f>
@@ -21432,18 +21325,18 @@
         <v>63</v>
       </c>
       <c r="P279" s="34">
-        <f>G279*</f>
+        <f>G279*$G$8</f>
         <v/>
       </c>
       <c r="Q279" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R279" s="34">
-        <f>G279*</f>
+        <f>G279*$G$4</f>
         <v/>
       </c>
       <c r="S279" s="34">
-        <f>I279*</f>
+        <f>I279*$G$3</f>
         <v/>
       </c>
       <c r="T279" s="36" t="n">
@@ -21460,11 +21353,11 @@
         <v>0.4</v>
       </c>
       <c r="X279" s="34">
-        <f>**W279</f>
+        <f>$G$6*$G$7*W279</f>
         <v/>
       </c>
       <c r="Y279" s="32">
-        <f>W279*(+0)</f>
+        <f>W279*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z279" s="33" t="n">
@@ -21506,7 +21399,7 @@
         <v/>
       </c>
       <c r="AJ279" s="34">
-        <f>(O279+Q279+V279+X279+Y279+L279)/(1-(M279++(1-H279)*++Z279+AB279))</f>
+        <f>(O279+Q279+V279+X279+Y279+L279)/(1-(M279+$G$4+(1-H279)*$G$3+$G$8+Z279+AB279))</f>
         <v/>
       </c>
     </row>
@@ -21584,10 +21477,9 @@
       <c r="J281" s="30" t="n">
         <v>175</v>
       </c>
-      <c r="K281" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K281" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L281" s="32">
         <f>J281+K281</f>
@@ -21604,18 +21496,18 @@
         <v>63</v>
       </c>
       <c r="P281" s="34">
-        <f>G281*</f>
+        <f>G281*$G$8</f>
         <v/>
       </c>
       <c r="Q281" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R281" s="34">
-        <f>G281*</f>
+        <f>G281*$G$4</f>
         <v/>
       </c>
       <c r="S281" s="34">
-        <f>I281*</f>
+        <f>I281*$G$3</f>
         <v/>
       </c>
       <c r="T281" s="36" t="n">
@@ -21632,11 +21524,11 @@
         <v>0.4</v>
       </c>
       <c r="X281" s="34">
-        <f>**W281</f>
+        <f>$G$6*$G$7*W281</f>
         <v/>
       </c>
       <c r="Y281" s="32">
-        <f>W281*(+0)</f>
+        <f>W281*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z281" s="33" t="n">
@@ -21678,7 +21570,7 @@
         <v/>
       </c>
       <c r="AJ281" s="34">
-        <f>(O281+Q281+V281+X281+Y281+L281)/(1-(M281++(1-H281)*++Z281+AB281))</f>
+        <f>(O281+Q281+V281+X281+Y281+L281)/(1-(M281+$G$4+(1-H281)*$G$3+$G$8+Z281+AB281))</f>
         <v/>
       </c>
     </row>
@@ -21714,10 +21606,9 @@
       <c r="J282" s="30" t="n">
         <v>363</v>
       </c>
-      <c r="K282" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K282" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L282" s="32">
         <f>J282+K282</f>
@@ -21734,18 +21625,18 @@
         <v>63</v>
       </c>
       <c r="P282" s="34">
-        <f>G282*</f>
+        <f>G282*$G$8</f>
         <v/>
       </c>
       <c r="Q282" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R282" s="34">
-        <f>G282*</f>
+        <f>G282*$G$4</f>
         <v/>
       </c>
       <c r="S282" s="34">
-        <f>I282*</f>
+        <f>I282*$G$3</f>
         <v/>
       </c>
       <c r="T282" s="36" t="n">
@@ -21762,11 +21653,11 @@
         <v>0.4</v>
       </c>
       <c r="X282" s="34">
-        <f>**W282</f>
+        <f>$G$6*$G$7*W282</f>
         <v/>
       </c>
       <c r="Y282" s="32">
-        <f>W282*(+0)</f>
+        <f>W282*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z282" s="33" t="n">
@@ -21808,7 +21699,7 @@
         <v/>
       </c>
       <c r="AJ282" s="34">
-        <f>(O282+Q282+V282+X282+Y282+L282)/(1-(M282++(1-H282)*++Z282+AB282))</f>
+        <f>(O282+Q282+V282+X282+Y282+L282)/(1-(M282+$G$4+(1-H282)*$G$3+$G$8+Z282+AB282))</f>
         <v/>
       </c>
     </row>
@@ -21844,10 +21735,9 @@
       <c r="J283" s="30" t="n">
         <v>302</v>
       </c>
-      <c r="K283" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K283" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L283" s="32">
         <f>J283+K283</f>
@@ -21864,18 +21754,18 @@
         <v>63</v>
       </c>
       <c r="P283" s="34">
-        <f>G283*</f>
+        <f>G283*$G$8</f>
         <v/>
       </c>
       <c r="Q283" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R283" s="34">
-        <f>G283*</f>
+        <f>G283*$G$4</f>
         <v/>
       </c>
       <c r="S283" s="34">
-        <f>I283*</f>
+        <f>I283*$G$3</f>
         <v/>
       </c>
       <c r="T283" s="36" t="n">
@@ -21892,11 +21782,11 @@
         <v>0.4</v>
       </c>
       <c r="X283" s="34">
-        <f>**W283</f>
+        <f>$G$6*$G$7*W283</f>
         <v/>
       </c>
       <c r="Y283" s="32">
-        <f>W283*(+0)</f>
+        <f>W283*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z283" s="33" t="n">
@@ -21938,7 +21828,7 @@
         <v/>
       </c>
       <c r="AJ283" s="34">
-        <f>(O283+Q283+V283+X283+Y283+L283)/(1-(M283++(1-H283)*++Z283+AB283))</f>
+        <f>(O283+Q283+V283+X283+Y283+L283)/(1-(M283+$G$4+(1-H283)*$G$3+$G$8+Z283+AB283))</f>
         <v/>
       </c>
     </row>
@@ -22016,10 +21906,9 @@
       <c r="J285" s="30" t="n">
         <v>477</v>
       </c>
-      <c r="K285" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K285" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L285" s="32">
         <f>J285+K285</f>
@@ -22036,18 +21925,18 @@
         <v>63</v>
       </c>
       <c r="P285" s="34">
-        <f>G285*</f>
+        <f>G285*$G$8</f>
         <v/>
       </c>
       <c r="Q285" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R285" s="34">
-        <f>G285*</f>
+        <f>G285*$G$4</f>
         <v/>
       </c>
       <c r="S285" s="34">
-        <f>I285*</f>
+        <f>I285*$G$3</f>
         <v/>
       </c>
       <c r="T285" s="36" t="n">
@@ -22064,11 +21953,11 @@
         <v>0.4</v>
       </c>
       <c r="X285" s="34">
-        <f>**W285</f>
+        <f>$G$6*$G$7*W285</f>
         <v/>
       </c>
       <c r="Y285" s="32">
-        <f>W285*(+0)</f>
+        <f>W285*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z285" s="33" t="n">
@@ -22110,7 +21999,7 @@
         <v/>
       </c>
       <c r="AJ285" s="34">
-        <f>(O285+Q285+V285+X285+Y285+L285)/(1-(M285++(1-H285)*++Z285+AB285))</f>
+        <f>(O285+Q285+V285+X285+Y285+L285)/(1-(M285+$G$4+(1-H285)*$G$3+$G$8+Z285+AB285))</f>
         <v/>
       </c>
     </row>
@@ -22188,10 +22077,9 @@
       <c r="J287" s="30" t="n">
         <v>455</v>
       </c>
-      <c r="K287" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K287" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L287" s="32">
         <f>J287+K287</f>
@@ -22208,18 +22096,18 @@
         <v>74</v>
       </c>
       <c r="P287" s="34">
-        <f>G287*</f>
+        <f>G287*$G$8</f>
         <v/>
       </c>
       <c r="Q287" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R287" s="34">
-        <f>G287*</f>
+        <f>G287*$G$4</f>
         <v/>
       </c>
       <c r="S287" s="34">
-        <f>I287*</f>
+        <f>I287*$G$3</f>
         <v/>
       </c>
       <c r="T287" s="36" t="n">
@@ -22236,11 +22124,11 @@
         <v>1.28</v>
       </c>
       <c r="X287" s="34">
-        <f>**W287</f>
+        <f>$G$6*$G$7*W287</f>
         <v/>
       </c>
       <c r="Y287" s="32">
-        <f>W287*(+0)</f>
+        <f>W287*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z287" s="33" t="n">
@@ -22282,7 +22170,7 @@
         <v/>
       </c>
       <c r="AJ287" s="34">
-        <f>(O287+Q287+V287+X287+Y287+L287)/(1-(M287++(1-H287)*++Z287+AB287))</f>
+        <f>(O287+Q287+V287+X287+Y287+L287)/(1-(M287+$G$4+(1-H287)*$G$3+$G$8+Z287+AB287))</f>
         <v/>
       </c>
     </row>
@@ -22318,10 +22206,9 @@
       <c r="J288" s="30" t="n">
         <v>674</v>
       </c>
-      <c r="K288" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K288" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L288" s="32">
         <f>J288+K288</f>
@@ -22338,18 +22225,18 @@
         <v>63</v>
       </c>
       <c r="P288" s="34">
-        <f>G288*</f>
+        <f>G288*$G$8</f>
         <v/>
       </c>
       <c r="Q288" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R288" s="34">
-        <f>G288*</f>
+        <f>G288*$G$4</f>
         <v/>
       </c>
       <c r="S288" s="34">
-        <f>I288*</f>
+        <f>I288*$G$3</f>
         <v/>
       </c>
       <c r="T288" s="36" t="n">
@@ -22366,11 +22253,11 @@
         <v>0.4</v>
       </c>
       <c r="X288" s="34">
-        <f>**W288</f>
+        <f>$G$6*$G$7*W288</f>
         <v/>
       </c>
       <c r="Y288" s="32">
-        <f>W288*(+0)</f>
+        <f>W288*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z288" s="33" t="n">
@@ -22412,7 +22299,7 @@
         <v/>
       </c>
       <c r="AJ288" s="34">
-        <f>(O288+Q288+V288+X288+Y288+L288)/(1-(M288++(1-H288)*++Z288+AB288))</f>
+        <f>(O288+Q288+V288+X288+Y288+L288)/(1-(M288+$G$4+(1-H288)*$G$3+$G$8+Z288+AB288))</f>
         <v/>
       </c>
     </row>
@@ -22448,10 +22335,9 @@
       <c r="J289" s="30" t="n">
         <v>833</v>
       </c>
-      <c r="K289" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K289" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L289" s="32">
         <f>J289+K289</f>
@@ -22468,18 +22354,18 @@
         <v>63</v>
       </c>
       <c r="P289" s="34">
-        <f>G289*</f>
+        <f>G289*$G$8</f>
         <v/>
       </c>
       <c r="Q289" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R289" s="34">
-        <f>G289*</f>
+        <f>G289*$G$4</f>
         <v/>
       </c>
       <c r="S289" s="34">
-        <f>I289*</f>
+        <f>I289*$G$3</f>
         <v/>
       </c>
       <c r="T289" s="36" t="n">
@@ -22496,11 +22382,11 @@
         <v>0.4</v>
       </c>
       <c r="X289" s="34">
-        <f>**W289</f>
+        <f>$G$6*$G$7*W289</f>
         <v/>
       </c>
       <c r="Y289" s="32">
-        <f>W289*(+0)</f>
+        <f>W289*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z289" s="33" t="n">
@@ -22542,7 +22428,7 @@
         <v/>
       </c>
       <c r="AJ289" s="34">
-        <f>(O289+Q289+V289+X289+Y289+L289)/(1-(M289++(1-H289)*++Z289+AB289))</f>
+        <f>(O289+Q289+V289+X289+Y289+L289)/(1-(M289+$G$4+(1-H289)*$G$3+$G$8+Z289+AB289))</f>
         <v/>
       </c>
     </row>
@@ -22578,10 +22464,9 @@
       <c r="J290" s="30" t="n">
         <v>757</v>
       </c>
-      <c r="K290" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K290" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L290" s="32">
         <f>J290+K290</f>
@@ -22598,18 +22483,18 @@
         <v>63</v>
       </c>
       <c r="P290" s="34">
-        <f>G290*</f>
+        <f>G290*$G$8</f>
         <v/>
       </c>
       <c r="Q290" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R290" s="34">
-        <f>G290*</f>
+        <f>G290*$G$4</f>
         <v/>
       </c>
       <c r="S290" s="34">
-        <f>I290*</f>
+        <f>I290*$G$3</f>
         <v/>
       </c>
       <c r="T290" s="36" t="n">
@@ -22626,11 +22511,11 @@
         <v>0.4</v>
       </c>
       <c r="X290" s="34">
-        <f>**W290</f>
+        <f>$G$6*$G$7*W290</f>
         <v/>
       </c>
       <c r="Y290" s="32">
-        <f>W290*(+0)</f>
+        <f>W290*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z290" s="33" t="n">
@@ -22672,7 +22557,7 @@
         <v/>
       </c>
       <c r="AJ290" s="34">
-        <f>(O290+Q290+V290+X290+Y290+L290)/(1-(M290++(1-H290)*++Z290+AB290))</f>
+        <f>(O290+Q290+V290+X290+Y290+L290)/(1-(M290+$G$4+(1-H290)*$G$3+$G$8+Z290+AB290))</f>
         <v/>
       </c>
     </row>
@@ -22708,10 +22593,9 @@
       <c r="J291" s="30" t="n">
         <v>922</v>
       </c>
-      <c r="K291" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K291" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L291" s="32">
         <f>J291+K291</f>
@@ -22728,18 +22612,18 @@
         <v>63</v>
       </c>
       <c r="P291" s="34">
-        <f>G291*</f>
+        <f>G291*$G$8</f>
         <v/>
       </c>
       <c r="Q291" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R291" s="34">
-        <f>G291*</f>
+        <f>G291*$G$4</f>
         <v/>
       </c>
       <c r="S291" s="34">
-        <f>I291*</f>
+        <f>I291*$G$3</f>
         <v/>
       </c>
       <c r="T291" s="36" t="n">
@@ -22756,11 +22640,11 @@
         <v>0.4</v>
       </c>
       <c r="X291" s="34">
-        <f>**W291</f>
+        <f>$G$6*$G$7*W291</f>
         <v/>
       </c>
       <c r="Y291" s="32">
-        <f>W291*(+0)</f>
+        <f>W291*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z291" s="33" t="n">
@@ -22802,7 +22686,7 @@
         <v/>
       </c>
       <c r="AJ291" s="34">
-        <f>(O291+Q291+V291+X291+Y291+L291)/(1-(M291++(1-H291)*++Z291+AB291))</f>
+        <f>(O291+Q291+V291+X291+Y291+L291)/(1-(M291+$G$4+(1-H291)*$G$3+$G$8+Z291+AB291))</f>
         <v/>
       </c>
     </row>
@@ -22838,10 +22722,9 @@
       <c r="J292" s="30" t="n">
         <v>1019</v>
       </c>
-      <c r="K292" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K292" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L292" s="32">
         <f>J292+K292</f>
@@ -22858,18 +22741,18 @@
         <v>63</v>
       </c>
       <c r="P292" s="34">
-        <f>G292*</f>
+        <f>G292*$G$8</f>
         <v/>
       </c>
       <c r="Q292" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R292" s="34">
-        <f>G292*</f>
+        <f>G292*$G$4</f>
         <v/>
       </c>
       <c r="S292" s="34">
-        <f>I292*</f>
+        <f>I292*$G$3</f>
         <v/>
       </c>
       <c r="T292" s="36" t="n">
@@ -22886,11 +22769,11 @@
         <v>0.4</v>
       </c>
       <c r="X292" s="34">
-        <f>**W292</f>
+        <f>$G$6*$G$7*W292</f>
         <v/>
       </c>
       <c r="Y292" s="32">
-        <f>W292*(+0)</f>
+        <f>W292*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z292" s="33" t="n">
@@ -22932,7 +22815,7 @@
         <v/>
       </c>
       <c r="AJ292" s="34">
-        <f>(O292+Q292+V292+X292+Y292+L292)/(1-(M292++(1-H292)*++Z292+AB292))</f>
+        <f>(O292+Q292+V292+X292+Y292+L292)/(1-(M292+$G$4+(1-H292)*$G$3+$G$8+Z292+AB292))</f>
         <v/>
       </c>
     </row>
@@ -22968,10 +22851,9 @@
       <c r="J293" s="30" t="n">
         <v>670</v>
       </c>
-      <c r="K293" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K293" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L293" s="32">
         <f>J293+K293</f>
@@ -22988,18 +22870,18 @@
         <v>63</v>
       </c>
       <c r="P293" s="34">
-        <f>G293*</f>
+        <f>G293*$G$8</f>
         <v/>
       </c>
       <c r="Q293" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R293" s="34">
-        <f>G293*</f>
+        <f>G293*$G$4</f>
         <v/>
       </c>
       <c r="S293" s="34">
-        <f>I293*</f>
+        <f>I293*$G$3</f>
         <v/>
       </c>
       <c r="T293" s="36" t="n">
@@ -23016,11 +22898,11 @@
         <v>0.4</v>
       </c>
       <c r="X293" s="34">
-        <f>**W293</f>
+        <f>$G$6*$G$7*W293</f>
         <v/>
       </c>
       <c r="Y293" s="32">
-        <f>W293*(+0)</f>
+        <f>W293*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z293" s="33" t="n">
@@ -23062,7 +22944,7 @@
         <v/>
       </c>
       <c r="AJ293" s="34">
-        <f>(O293+Q293+V293+X293+Y293+L293)/(1-(M293++(1-H293)*++Z293+AB293))</f>
+        <f>(O293+Q293+V293+X293+Y293+L293)/(1-(M293+$G$4+(1-H293)*$G$3+$G$8+Z293+AB293))</f>
         <v/>
       </c>
     </row>
@@ -23098,10 +22980,9 @@
       <c r="J294" s="30" t="n">
         <v>407</v>
       </c>
-      <c r="K294" s="31" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
+      <c r="K294" s="31">
+        <f>$G$5</f>
+        <v/>
       </c>
       <c r="L294" s="32">
         <f>J294+K294</f>
@@ -23118,18 +22999,18 @@
         <v>63</v>
       </c>
       <c r="P294" s="34">
-        <f>G294*</f>
+        <f>G294*$G$8</f>
         <v/>
       </c>
       <c r="Q294" s="35" t="n">
         <v>25</v>
       </c>
       <c r="R294" s="34">
-        <f>G294*</f>
+        <f>G294*$G$4</f>
         <v/>
       </c>
       <c r="S294" s="34">
-        <f>I294*</f>
+        <f>I294*$G$3</f>
         <v/>
       </c>
       <c r="T294" s="36" t="n">
@@ -23146,11 +23027,11 @@
         <v>0.4</v>
       </c>
       <c r="X294" s="34">
-        <f>**W294</f>
+        <f>$G$6*$G$7*W294</f>
         <v/>
       </c>
       <c r="Y294" s="32">
-        <f>W294*(+0)</f>
+        <f>W294*($G$9+$G$10)</f>
         <v/>
       </c>
       <c r="Z294" s="33" t="n">
@@ -23192,7 +23073,7 @@
         <v/>
       </c>
       <c r="AJ294" s="34">
-        <f>(O294+Q294+V294+X294+Y294+L294)/(1-(M294++(1-H294)*++Z294+AB294))</f>
+        <f>(O294+Q294+V294+X294+Y294+L294)/(1-(M294+$G$4+(1-H294)*$G$3+$G$8+Z294+AB294))</f>
         <v/>
       </c>
     </row>

--- a/outputs/ozon/ozon_unitka_po_ostatkam_2026-08-05.xlsx
+++ b/outputs/ozon/ozon_unitka_po_ostatkam_2026-08-05.xlsx
@@ -1131,8 +1131,9 @@
       <c r="F14" s="17" t="n">
         <v>22.3</v>
       </c>
-      <c r="G14" s="17" t="n">
-        <v>1630</v>
+      <c r="G14" s="17">
+        <f>(2.0*L14+O14+Q14+V14+X14+Y14)/(1-M14-$G$8-$G$4-(1-H14)*$G$3-Z14-AB14)</f>
+        <v/>
       </c>
       <c r="H14" s="18" t="n">
         <v>0.45</v>
@@ -1384,8 +1385,9 @@
       <c r="F18" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="17" t="n">
-        <v>900</v>
+      <c r="G18" s="17">
+        <f>(2.0*L18+O18+Q18+V18+X18+Y18)/(1-M18-$G$8-$G$4-(1-H18)*$G$3-Z18-AB18)</f>
+        <v/>
       </c>
       <c r="H18" s="18" t="n">
         <v>0.45</v>
@@ -1638,7 +1640,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G22" s="17">
-        <f>(1.25*L22+O22+Q22+V22+X22+Y22)/(1-M22-$G$8-$G$4-(1-H22)*$G$3-Z22-AB22)</f>
+        <f>(2.0*L22+O22+Q22+V22+X22+Y22)/(1-M22-$G$8-$G$4-(1-H22)*$G$3-Z22-AB22)</f>
         <v/>
       </c>
       <c r="H22" s="18" t="n">
@@ -1808,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="17">
-        <f>(1.25*L24+O24+Q24+V24+X24+Y24)/(1-M24-$G$8-$G$4-(1-H24)*$G$3-Z24-AB24)</f>
+        <f>(2.0*L24+O24+Q24+V24+X24+Y24)/(1-M24-$G$8-$G$4-(1-H24)*$G$3-Z24-AB24)</f>
         <v/>
       </c>
       <c r="H24" s="18" t="n">
@@ -1978,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="17">
-        <f>(1.25*L26+O26+Q26+V26+X26+Y26)/(1-M26-$G$8-$G$4-(1-H26)*$G$3-Z26-AB26)</f>
+        <f>(2.0*L26+O26+Q26+V26+X26+Y26)/(1-M26-$G$8-$G$4-(1-H26)*$G$3-Z26-AB26)</f>
         <v/>
       </c>
       <c r="H26" s="18" t="n">
@@ -2104,7 +2106,7 @@
       <c r="E27" s="17" t="n"/>
       <c r="F27" s="17" t="n"/>
       <c r="G27" s="17">
-        <f>(1.25*L27+O27+Q27+V27+X27+Y27)/(1-M27-$G$8-$G$4-(1-H27)*$G$3-Z27-AB27)</f>
+        <f>(2.0*L27+O27+Q27+V27+X27+Y27)/(1-M27-$G$8-$G$4-(1-H27)*$G$3-Z27-AB27)</f>
         <v/>
       </c>
       <c r="H27" s="18" t="n">
@@ -2231,8 +2233,9 @@
       <c r="F28" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="17" t="n">
-        <v>1790</v>
+      <c r="G28" s="17">
+        <f>(2.0*L28+O28+Q28+V28+X28+Y28)/(1-M28-$G$8-$G$4-(1-H28)*$G$3-Z28-AB28)</f>
+        <v/>
       </c>
       <c r="H28" s="18" t="n">
         <v>0.45</v>
@@ -2404,8 +2407,9 @@
       <c r="F30" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="G30" s="17" t="n">
-        <v>750</v>
+      <c r="G30" s="17">
+        <f>(2.0*L30+O30+Q30+V30+X30+Y30)/(1-M30-$G$8-$G$4-(1-H30)*$G$3-Z30-AB30)</f>
+        <v/>
       </c>
       <c r="H30" s="18" t="n">
         <v>0.45</v>
@@ -2532,7 +2536,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="17">
-        <f>(1.25*L31+O31+Q31+V31+X31+Y31)/(1-M31-$G$8-$G$4-(1-H31)*$G$3-Z31-AB31)</f>
+        <f>(2.0*L31+O31+Q31+V31+X31+Y31)/(1-M31-$G$8-$G$4-(1-H31)*$G$3-Z31-AB31)</f>
         <v/>
       </c>
       <c r="H31" s="18" t="n">
@@ -2659,8 +2663,9 @@
       <c r="F32" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="G32" s="17" t="n">
-        <v>1800</v>
+      <c r="G32" s="17">
+        <f>(3.0*L32+O32+Q32+V32+X32+Y32)/(1-M32-$G$8-$G$4-(1-H32)*$G$3-Z32-AB32)</f>
+        <v/>
       </c>
       <c r="H32" s="18" t="n">
         <v>0.45</v>
@@ -2786,8 +2791,9 @@
       <c r="F33" s="17" t="n">
         <v>7.3</v>
       </c>
-      <c r="G33" s="17" t="n">
-        <v>1800</v>
+      <c r="G33" s="17">
+        <f>(2.5*L33+O33+Q33+V33+X33+Y33)/(1-M33-$G$8-$G$4-(1-H33)*$G$3-Z33-AB33)</f>
+        <v/>
       </c>
       <c r="H33" s="18" t="n">
         <v>0.45</v>
@@ -2913,8 +2919,9 @@
       <c r="F34" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="G34" s="17" t="n">
-        <v>1356</v>
+      <c r="G34" s="17">
+        <f>(2.0*L34+O34+Q34+V34+X34+Y34)/(1-M34-$G$8-$G$4-(1-H34)*$G$3-Z34-AB34)</f>
+        <v/>
       </c>
       <c r="H34" s="18" t="n">
         <v>0.45</v>
@@ -3040,8 +3047,9 @@
       <c r="F35" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="17" t="n">
-        <v>1280</v>
+      <c r="G35" s="17">
+        <f>(2.0*L35+O35+Q35+V35+X35+Y35)/(1-M35-$G$8-$G$4-(1-H35)*$G$3-Z35-AB35)</f>
+        <v/>
       </c>
       <c r="H35" s="18" t="n">
         <v>0.45</v>
@@ -3167,8 +3175,9 @@
       <c r="F36" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="G36" s="17" t="n">
-        <v>1600</v>
+      <c r="G36" s="17">
+        <f>(2.5*L36+O36+Q36+V36+X36+Y36)/(1-M36-$G$8-$G$4-(1-H36)*$G$3-Z36-AB36)</f>
+        <v/>
       </c>
       <c r="H36" s="18" t="n">
         <v>0.45</v>
@@ -3294,8 +3303,9 @@
       <c r="F37" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="G37" s="17" t="n">
-        <v>1000</v>
+      <c r="G37" s="17">
+        <f>(2.0*L37+O37+Q37+V37+X37+Y37)/(1-M37-$G$8-$G$4-(1-H37)*$G$3-Z37-AB37)</f>
+        <v/>
       </c>
       <c r="H37" s="18" t="n">
         <v>0.45</v>
@@ -3421,8 +3431,9 @@
       <c r="F38" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="17" t="n">
-        <v>1290</v>
+      <c r="G38" s="17">
+        <f>(2.0*L38+O38+Q38+V38+X38+Y38)/(1-M38-$G$8-$G$4-(1-H38)*$G$3-Z38-AB38)</f>
+        <v/>
       </c>
       <c r="H38" s="18" t="n">
         <v>0.45</v>
@@ -3549,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="17">
-        <f>(1.25*L39+O39+Q39+V39+X39+Y39)/(1-M39-$G$8-$G$4-(1-H39)*$G$3-Z39-AB39)</f>
+        <f>(2.0*L39+O39+Q39+V39+X39+Y39)/(1-M39-$G$8-$G$4-(1-H39)*$G$3-Z39-AB39)</f>
         <v/>
       </c>
       <c r="H39" s="18" t="n">
@@ -3797,7 +3808,7 @@
       <c r="E43" s="17" t="n"/>
       <c r="F43" s="17" t="n"/>
       <c r="G43" s="17">
-        <f>(1.25*L43+O43+Q43+V43+X43+Y43)/(1-M43-$G$8-$G$4-(1-H43)*$G$3-Z43-AB43)</f>
+        <f>(2.0*L43+O43+Q43+V43+X43+Y43)/(1-M43-$G$8-$G$4-(1-H43)*$G$3-Z43-AB43)</f>
         <v/>
       </c>
       <c r="H43" s="18" t="n">
@@ -3966,8 +3977,9 @@
       <c r="F45" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="G45" s="17" t="n">
-        <v>1650</v>
+      <c r="G45" s="17">
+        <f>(2.0*L45+O45+Q45+V45+X45+Y45)/(1-M45-$G$8-$G$4-(1-H45)*$G$3-Z45-AB45)</f>
+        <v/>
       </c>
       <c r="H45" s="18" t="n">
         <v>0.45</v>
@@ -4093,8 +4105,9 @@
       <c r="F46" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="G46" s="17" t="n">
-        <v>1770</v>
+      <c r="G46" s="17">
+        <f>(2.5*L46+O46+Q46+V46+X46+Y46)/(1-M46-$G$8-$G$4-(1-H46)*$G$3-Z46-AB46)</f>
+        <v/>
       </c>
       <c r="H46" s="18" t="n">
         <v>0.45</v>
@@ -4220,8 +4233,9 @@
       <c r="F47" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="G47" s="17" t="n">
-        <v>1835</v>
+      <c r="G47" s="17">
+        <f>(2.0*L47+O47+Q47+V47+X47+Y47)/(1-M47-$G$8-$G$4-(1-H47)*$G$3-Z47-AB47)</f>
+        <v/>
       </c>
       <c r="H47" s="18" t="n">
         <v>0.45</v>
@@ -4393,8 +4407,9 @@
       <c r="F49" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="G49" s="17" t="n">
-        <v>3500</v>
+      <c r="G49" s="17">
+        <f>(3.0*L49+O49+Q49+V49+X49+Y49)/(1-M49-$G$8-$G$4-(1-H49)*$G$3-Z49-AB49)</f>
+        <v/>
       </c>
       <c r="H49" s="18" t="n">
         <v>0.45</v>
@@ -4524,8 +4539,9 @@
       <c r="F50" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="G50" s="17" t="n">
-        <v>1850</v>
+      <c r="G50" s="17">
+        <f>(2.0*L50+O50+Q50+V50+X50+Y50)/(1-M50-$G$8-$G$4-(1-H50)*$G$3-Z50-AB50)</f>
+        <v/>
       </c>
       <c r="H50" s="18" t="n">
         <v>0.45</v>
@@ -4650,7 +4666,7 @@
       <c r="E51" s="17" t="n"/>
       <c r="F51" s="17" t="n"/>
       <c r="G51" s="17">
-        <f>(1.25*L51+O51+Q51+V51+X51+Y51)/(1-M51-$G$8-$G$4-(1-H51)*$G$3-Z51-AB51)</f>
+        <f>(2.0*L51+O51+Q51+V51+X51+Y51)/(1-M51-$G$8-$G$4-(1-H51)*$G$3-Z51-AB51)</f>
         <v/>
       </c>
       <c r="H51" s="18" t="n">
@@ -4781,8 +4797,9 @@
       <c r="F52" s="17" t="n">
         <v>6.6</v>
       </c>
-      <c r="G52" s="17" t="n">
-        <v>2900</v>
+      <c r="G52" s="17">
+        <f>(3.0*L52+O52+Q52+V52+X52+Y52)/(1-M52-$G$8-$G$4-(1-H52)*$G$3-Z52-AB52)</f>
+        <v/>
       </c>
       <c r="H52" s="18" t="n">
         <v>0.45</v>
@@ -4909,7 +4926,7 @@
         <v>7</v>
       </c>
       <c r="G53" s="17">
-        <f>(1.25*L53+O53+Q53+V53+X53+Y53)/(1-M53-$G$8-$G$4-(1-H53)*$G$3-Z53-AB53)</f>
+        <f>(2.0*L53+O53+Q53+V53+X53+Y53)/(1-M53-$G$8-$G$4-(1-H53)*$G$3-Z53-AB53)</f>
         <v/>
       </c>
       <c r="H53" s="18" t="n">
@@ -5037,7 +5054,7 @@
         <v>1</v>
       </c>
       <c r="G54" s="17">
-        <f>(1.25*L54+O54+Q54+V54+X54+Y54)/(1-M54-$G$8-$G$4-(1-H54)*$G$3-Z54-AB54)</f>
+        <f>(2.0*L54+O54+Q54+V54+X54+Y54)/(1-M54-$G$8-$G$4-(1-H54)*$G$3-Z54-AB54)</f>
         <v/>
       </c>
       <c r="H54" s="18" t="n">
@@ -5165,7 +5182,7 @@
         <v>7.5</v>
       </c>
       <c r="G55" s="17">
-        <f>(1.25*L55+O55+Q55+V55+X55+Y55)/(1-M55-$G$8-$G$4-(1-H55)*$G$3-Z55-AB55)</f>
+        <f>(2.0*L55+O55+Q55+V55+X55+Y55)/(1-M55-$G$8-$G$4-(1-H55)*$G$3-Z55-AB55)</f>
         <v/>
       </c>
       <c r="H55" s="18" t="n">
@@ -5292,8 +5309,9 @@
       <c r="F56" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="G56" s="17" t="n">
-        <v>1800</v>
+      <c r="G56" s="17">
+        <f>(2.5*L56+O56+Q56+V56+X56+Y56)/(1-M56-$G$8-$G$4-(1-H56)*$G$3-Z56-AB56)</f>
+        <v/>
       </c>
       <c r="H56" s="18" t="n">
         <v>0.45</v>
@@ -5420,7 +5438,7 @@
         <v>7</v>
       </c>
       <c r="G57" s="17">
-        <f>(1.25*L57+O57+Q57+V57+X57+Y57)/(1-M57-$G$8-$G$4-(1-H57)*$G$3-Z57-AB57)</f>
+        <f>(2.0*L57+O57+Q57+V57+X57+Y57)/(1-M57-$G$8-$G$4-(1-H57)*$G$3-Z57-AB57)</f>
         <v/>
       </c>
       <c r="H57" s="18" t="n">
@@ -5548,7 +5566,7 @@
         <v>4.5</v>
       </c>
       <c r="G58" s="17">
-        <f>(1.25*L58+O58+Q58+V58+X58+Y58)/(1-M58-$G$8-$G$4-(1-H58)*$G$3-Z58-AB58)</f>
+        <f>(2.0*L58+O58+Q58+V58+X58+Y58)/(1-M58-$G$8-$G$4-(1-H58)*$G$3-Z58-AB58)</f>
         <v/>
       </c>
       <c r="H58" s="18" t="n">
@@ -5717,8 +5735,9 @@
       <c r="F60" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G60" s="17" t="n">
-        <v>2750</v>
+      <c r="G60" s="17">
+        <f>(2.0*L60+O60+Q60+V60+X60+Y60)/(1-M60-$G$8-$G$4-(1-H60)*$G$3-Z60-AB60)</f>
+        <v/>
       </c>
       <c r="H60" s="18" t="n">
         <v>0.45</v>
@@ -5928,8 +5947,9 @@
       <c r="F63" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="G63" s="17" t="n">
-        <v>880</v>
+      <c r="G63" s="17">
+        <f>(2.0*L63+O63+Q63+V63+X63+Y63)/(1-M63-$G$8-$G$4-(1-H63)*$G$3-Z63-AB63)</f>
+        <v/>
       </c>
       <c r="H63" s="18" t="n">
         <v>0.45</v>
@@ -6055,8 +6075,9 @@
       <c r="F64" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="G64" s="17" t="n">
-        <v>930</v>
+      <c r="G64" s="17">
+        <f>(2.0*L64+O64+Q64+V64+X64+Y64)/(1-M64-$G$8-$G$4-(1-H64)*$G$3-Z64-AB64)</f>
+        <v/>
       </c>
       <c r="H64" s="18" t="n">
         <v>0.45</v>
@@ -6182,8 +6203,9 @@
       <c r="F65" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="G65" s="17" t="n">
-        <v>960</v>
+      <c r="G65" s="17">
+        <f>(2.0*L65+O65+Q65+V65+X65+Y65)/(1-M65-$G$8-$G$4-(1-H65)*$G$3-Z65-AB65)</f>
+        <v/>
       </c>
       <c r="H65" s="18" t="n">
         <v>0.45</v>
@@ -6435,8 +6457,9 @@
       <c r="F69" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G69" s="17" t="n">
-        <v>960</v>
+      <c r="G69" s="17">
+        <f>(2.0*L69+O69+Q69+V69+X69+Y69)/(1-M69-$G$8-$G$4-(1-H69)*$G$3-Z69-AB69)</f>
+        <v/>
       </c>
       <c r="H69" s="18" t="n">
         <v>0.45</v>
@@ -6562,8 +6585,9 @@
       <c r="F70" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G70" s="17" t="n">
-        <v>960</v>
+      <c r="G70" s="17">
+        <f>(2.0*L70+O70+Q70+V70+X70+Y70)/(1-M70-$G$8-$G$4-(1-H70)*$G$3-Z70-AB70)</f>
+        <v/>
       </c>
       <c r="H70" s="18" t="n">
         <v>0.45</v>
@@ -6689,8 +6713,9 @@
       <c r="F71" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G71" s="17" t="n">
-        <v>900</v>
+      <c r="G71" s="17">
+        <f>(2.0*L71+O71+Q71+V71+X71+Y71)/(1-M71-$G$8-$G$4-(1-H71)*$G$3-Z71-AB71)</f>
+        <v/>
       </c>
       <c r="H71" s="18" t="n">
         <v>0.45</v>
@@ -6816,8 +6841,9 @@
       <c r="F72" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="G72" s="17" t="n">
-        <v>1000</v>
+      <c r="G72" s="17">
+        <f>(2.0*L72+O72+Q72+V72+X72+Y72)/(1-M72-$G$8-$G$4-(1-H72)*$G$3-Z72-AB72)</f>
+        <v/>
       </c>
       <c r="H72" s="18" t="n">
         <v>0.45</v>
@@ -6987,8 +7013,9 @@
       <c r="F74" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="G74" s="17" t="n">
-        <v>2086</v>
+      <c r="G74" s="17">
+        <f>(2.0*L74+O74+Q74+V74+X74+Y74)/(1-M74-$G$8-$G$4-(1-H74)*$G$3-Z74-AB74)</f>
+        <v/>
       </c>
       <c r="H74" s="18" t="n">
         <v>0.45</v>
@@ -7574,8 +7601,9 @@
       <c r="D86" s="17" t="n"/>
       <c r="E86" s="17" t="n"/>
       <c r="F86" s="17" t="n"/>
-      <c r="G86" s="17" t="n">
-        <v>2086</v>
+      <c r="G86" s="17">
+        <f>(2.0*L86+O86+Q86+V86+X86+Y86)/(1-M86-$G$8-$G$4-(1-H86)*$G$3-Z86-AB86)</f>
+        <v/>
       </c>
       <c r="H86" s="18" t="n">
         <v>0.45</v>
@@ -7743,8 +7771,9 @@
       <c r="F88" s="17" t="n">
         <v>22</v>
       </c>
-      <c r="G88" s="17" t="n">
-        <v>600</v>
+      <c r="G88" s="17">
+        <f>(2.0*L88+O88+Q88+V88+X88+Y88)/(1-M88-$G$8-$G$4-(1-H88)*$G$3-Z88-AB88)</f>
+        <v/>
       </c>
       <c r="H88" s="18" t="n">
         <v>0.45</v>
@@ -7913,7 +7942,7 @@
         <v>10</v>
       </c>
       <c r="G90" s="17">
-        <f>(1.25*L90+O90+Q90+V90+X90+Y90)/(1-M90-$G$8-$G$4-(1-H90)*$G$3-Z90-AB90)</f>
+        <f>(2.0*L90+O90+Q90+V90+X90+Y90)/(1-M90-$G$8-$G$4-(1-H90)*$G$3-Z90-AB90)</f>
         <v/>
       </c>
       <c r="H90" s="18" t="n">
@@ -8082,8 +8111,9 @@
       <c r="F92" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G92" s="17" t="n">
-        <v>5500</v>
+      <c r="G92" s="17">
+        <f>(3.0*L92+O92+Q92+V92+X92+Y92)/(1-M92-$G$8-$G$4-(1-H92)*$G$3-Z92-AB92)</f>
+        <v/>
       </c>
       <c r="H92" s="18" t="n">
         <v>0.45</v>
@@ -8213,8 +8243,9 @@
       <c r="F93" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G93" s="17" t="n">
-        <v>3700</v>
+      <c r="G93" s="17">
+        <f>(3.0*L93+O93+Q93+V93+X93+Y93)/(1-M93-$G$8-$G$4-(1-H93)*$G$3-Z93-AB93)</f>
+        <v/>
       </c>
       <c r="H93" s="18" t="n">
         <v>0.45</v>
@@ -8344,8 +8375,9 @@
       <c r="F94" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G94" s="17" t="n">
-        <v>3700</v>
+      <c r="G94" s="17">
+        <f>(3.0*L94+O94+Q94+V94+X94+Y94)/(1-M94-$G$8-$G$4-(1-H94)*$G$3-Z94-AB94)</f>
+        <v/>
       </c>
       <c r="H94" s="18" t="n">
         <v>0.45</v>
@@ -8475,8 +8507,9 @@
       <c r="F95" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G95" s="17" t="n">
-        <v>3700</v>
+      <c r="G95" s="17">
+        <f>(2.5*L95+O95+Q95+V95+X95+Y95)/(1-M95-$G$8-$G$4-(1-H95)*$G$3-Z95-AB95)</f>
+        <v/>
       </c>
       <c r="H95" s="18" t="n">
         <v>0.45</v>
@@ -8606,8 +8639,9 @@
       <c r="F96" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G96" s="17" t="n">
-        <v>4500</v>
+      <c r="G96" s="17">
+        <f>(3.0*L96+O96+Q96+V96+X96+Y96)/(1-M96-$G$8-$G$4-(1-H96)*$G$3-Z96-AB96)</f>
+        <v/>
       </c>
       <c r="H96" s="18" t="n">
         <v>0.45</v>
@@ -8733,8 +8767,9 @@
       <c r="F97" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G97" s="17" t="n">
-        <v>3500</v>
+      <c r="G97" s="17">
+        <f>(2.5*L97+O97+Q97+V97+X97+Y97)/(1-M97-$G$8-$G$4-(1-H97)*$G$3-Z97-AB97)</f>
+        <v/>
       </c>
       <c r="H97" s="18" t="n">
         <v>0.45</v>
@@ -8986,8 +9021,9 @@
       <c r="F101" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="G101" s="17" t="n">
-        <v>1700</v>
+      <c r="G101" s="17">
+        <f>(2.0*L101+O101+Q101+V101+X101+Y101)/(1-M101-$G$8-$G$4-(1-H101)*$G$3-Z101-AB101)</f>
+        <v/>
       </c>
       <c r="H101" s="18" t="n">
         <v>0.45</v>
@@ -9108,7 +9144,7 @@
       <c r="E102" s="17" t="n"/>
       <c r="F102" s="17" t="n"/>
       <c r="G102" s="17">
-        <f>(1.25*L102+O102+Q102+V102+X102+Y102)/(1-M102-$G$8-$G$4-(1-H102)*$G$3-Z102-AB102)</f>
+        <f>(2.0*L102+O102+Q102+V102+X102+Y102)/(1-M102-$G$8-$G$4-(1-H102)*$G$3-Z102-AB102)</f>
         <v/>
       </c>
       <c r="H102" s="18" t="n">
@@ -9230,7 +9266,7 @@
       <c r="E103" s="17" t="n"/>
       <c r="F103" s="17" t="n"/>
       <c r="G103" s="17">
-        <f>(1.25*L103+O103+Q103+V103+X103+Y103)/(1-M103-$G$8-$G$4-(1-H103)*$G$3-Z103-AB103)</f>
+        <f>(2.0*L103+O103+Q103+V103+X103+Y103)/(1-M103-$G$8-$G$4-(1-H103)*$G$3-Z103-AB103)</f>
         <v/>
       </c>
       <c r="H103" s="18" t="n">
@@ -9352,7 +9388,7 @@
       <c r="E104" s="17" t="n"/>
       <c r="F104" s="17" t="n"/>
       <c r="G104" s="17">
-        <f>(1.25*L104+O104+Q104+V104+X104+Y104)/(1-M104-$G$8-$G$4-(1-H104)*$G$3-Z104-AB104)</f>
+        <f>(2.0*L104+O104+Q104+V104+X104+Y104)/(1-M104-$G$8-$G$4-(1-H104)*$G$3-Z104-AB104)</f>
         <v/>
       </c>
       <c r="H104" s="18" t="n">
@@ -9474,7 +9510,7 @@
       <c r="E105" s="17" t="n"/>
       <c r="F105" s="17" t="n"/>
       <c r="G105" s="17">
-        <f>(1.25*L105+O105+Q105+V105+X105+Y105)/(1-M105-$G$8-$G$4-(1-H105)*$G$3-Z105-AB105)</f>
+        <f>(2.0*L105+O105+Q105+V105+X105+Y105)/(1-M105-$G$8-$G$4-(1-H105)*$G$3-Z105-AB105)</f>
         <v/>
       </c>
       <c r="H105" s="18" t="n">
@@ -9596,7 +9632,7 @@
       <c r="E106" s="17" t="n"/>
       <c r="F106" s="17" t="n"/>
       <c r="G106" s="17">
-        <f>(1.25*L106+O106+Q106+V106+X106+Y106)/(1-M106-$G$8-$G$4-(1-H106)*$G$3-Z106-AB106)</f>
+        <f>(2.0*L106+O106+Q106+V106+X106+Y106)/(1-M106-$G$8-$G$4-(1-H106)*$G$3-Z106-AB106)</f>
         <v/>
       </c>
       <c r="H106" s="18" t="n">
@@ -9718,7 +9754,7 @@
       <c r="E107" s="17" t="n"/>
       <c r="F107" s="17" t="n"/>
       <c r="G107" s="17">
-        <f>(1.25*L107+O107+Q107+V107+X107+Y107)/(1-M107-$G$8-$G$4-(1-H107)*$G$3-Z107-AB107)</f>
+        <f>(2.0*L107+O107+Q107+V107+X107+Y107)/(1-M107-$G$8-$G$4-(1-H107)*$G$3-Z107-AB107)</f>
         <v/>
       </c>
       <c r="H107" s="18" t="n">
@@ -9840,7 +9876,7 @@
       <c r="E108" s="17" t="n"/>
       <c r="F108" s="17" t="n"/>
       <c r="G108" s="17">
-        <f>(1.25*L108+O108+Q108+V108+X108+Y108)/(1-M108-$G$8-$G$4-(1-H108)*$G$3-Z108-AB108)</f>
+        <f>(2.0*L108+O108+Q108+V108+X108+Y108)/(1-M108-$G$8-$G$4-(1-H108)*$G$3-Z108-AB108)</f>
         <v/>
       </c>
       <c r="H108" s="18" t="n">
@@ -9967,8 +10003,9 @@
       <c r="F109" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="G109" s="17" t="n">
-        <v>1650</v>
+      <c r="G109" s="17">
+        <f>(2.0*L109+O109+Q109+V109+X109+Y109)/(1-M109-$G$8-$G$4-(1-H109)*$G$3-Z109-AB109)</f>
+        <v/>
       </c>
       <c r="H109" s="18" t="n">
         <v>0.45</v>
@@ -10094,8 +10131,9 @@
       <c r="F110" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="G110" s="17" t="n">
-        <v>1630</v>
+      <c r="G110" s="17">
+        <f>(2.0*L110+O110+Q110+V110+X110+Y110)/(1-M110-$G$8-$G$4-(1-H110)*$G$3-Z110-AB110)</f>
+        <v/>
       </c>
       <c r="H110" s="18" t="n">
         <v>0.45</v>
@@ -10221,8 +10259,9 @@
       <c r="F111" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="G111" s="17" t="n">
-        <v>1630</v>
+      <c r="G111" s="17">
+        <f>(2.0*L111+O111+Q111+V111+X111+Y111)/(1-M111-$G$8-$G$4-(1-H111)*$G$3-Z111-AB111)</f>
+        <v/>
       </c>
       <c r="H111" s="18" t="n">
         <v>0.45</v>
@@ -10348,8 +10387,9 @@
       <c r="F112" s="17" t="n">
         <v>2.2</v>
       </c>
-      <c r="G112" s="17" t="n">
-        <v>1800</v>
+      <c r="G112" s="17">
+        <f>(2.0*L112+O112+Q112+V112+X112+Y112)/(1-M112-$G$8-$G$4-(1-H112)*$G$3-Z112-AB112)</f>
+        <v/>
       </c>
       <c r="H112" s="18" t="n">
         <v>0.45</v>
@@ -10601,8 +10641,9 @@
       <c r="F116" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="G116" s="17" t="n">
-        <v>2200</v>
+      <c r="G116" s="17">
+        <f>(2.0*L116+O116+Q116+V116+X116+Y116)/(1-M116-$G$8-$G$4-(1-H116)*$G$3-Z116-AB116)</f>
+        <v/>
       </c>
       <c r="H116" s="18" t="n">
         <v>0.45</v>
@@ -10728,8 +10769,9 @@
       <c r="F117" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="G117" s="17" t="n">
-        <v>2300</v>
+      <c r="G117" s="17">
+        <f>(2.0*L117+O117+Q117+V117+X117+Y117)/(1-M117-$G$8-$G$4-(1-H117)*$G$3-Z117-AB117)</f>
+        <v/>
       </c>
       <c r="H117" s="18" t="n">
         <v>0.45</v>
@@ -10855,8 +10897,9 @@
       <c r="F118" s="17" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="G118" s="17" t="n">
-        <v>2250</v>
+      <c r="G118" s="17">
+        <f>(2.0*L118+O118+Q118+V118+X118+Y118)/(1-M118-$G$8-$G$4-(1-H118)*$G$3-Z118-AB118)</f>
+        <v/>
       </c>
       <c r="H118" s="18" t="n">
         <v>0.45</v>
@@ -10982,8 +11025,9 @@
       <c r="F119" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="G119" s="17" t="n">
-        <v>2300</v>
+      <c r="G119" s="17">
+        <f>(2.0*L119+O119+Q119+V119+X119+Y119)/(1-M119-$G$8-$G$4-(1-H119)*$G$3-Z119-AB119)</f>
+        <v/>
       </c>
       <c r="H119" s="18" t="n">
         <v>0.45</v>
@@ -11109,8 +11153,9 @@
       <c r="F120" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="G120" s="17" t="n">
-        <v>2135</v>
+      <c r="G120" s="17">
+        <f>(2.0*L120+O120+Q120+V120+X120+Y120)/(1-M120-$G$8-$G$4-(1-H120)*$G$3-Z120-AB120)</f>
+        <v/>
       </c>
       <c r="H120" s="18" t="n">
         <v>0.45</v>
@@ -11236,8 +11281,9 @@
       <c r="F121" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="G121" s="17" t="n">
-        <v>2135</v>
+      <c r="G121" s="17">
+        <f>(2.0*L121+O121+Q121+V121+X121+Y121)/(1-M121-$G$8-$G$4-(1-H121)*$G$3-Z121-AB121)</f>
+        <v/>
       </c>
       <c r="H121" s="18" t="n">
         <v>0.45</v>
@@ -11405,8 +11451,9 @@
       <c r="F123" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="G123" s="17" t="n">
-        <v>2200</v>
+      <c r="G123" s="17">
+        <f>(2.0*L123+O123+Q123+V123+X123+Y123)/(1-M123-$G$8-$G$4-(1-H123)*$G$3-Z123-AB123)</f>
+        <v/>
       </c>
       <c r="H123" s="18" t="n">
         <v>0.45</v>
@@ -11569,7 +11616,7 @@
       <c r="E125" s="17" t="n"/>
       <c r="F125" s="17" t="n"/>
       <c r="G125" s="17">
-        <f>(1.25*L125+O125+Q125+V125+X125+Y125)/(1-M125-$G$8-$G$4-(1-H125)*$G$3-Z125-AB125)</f>
+        <f>(2.0*L125+O125+Q125+V125+X125+Y125)/(1-M125-$G$8-$G$4-(1-H125)*$G$3-Z125-AB125)</f>
         <v/>
       </c>
       <c r="H125" s="18" t="n">
@@ -11780,8 +11827,9 @@
       <c r="F128" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G128" s="17" t="n">
-        <v>3100</v>
+      <c r="G128" s="17">
+        <f>(2.5*L128+O128+Q128+V128+X128+Y128)/(1-M128-$G$8-$G$4-(1-H128)*$G$3-Z128-AB128)</f>
+        <v/>
       </c>
       <c r="H128" s="18" t="n">
         <v>0.45</v>
@@ -12329,8 +12377,9 @@
           <t>10-15</t>
         </is>
       </c>
-      <c r="G139" s="17" t="n">
-        <v>2450</v>
+      <c r="G139" s="17">
+        <f>(2.0*L139+O139+Q139+V139+X139+Y139)/(1-M139-$G$8-$G$4-(1-H139)*$G$3-Z139-AB139)</f>
+        <v/>
       </c>
       <c r="H139" s="18" t="n">
         <v>0.45</v>
@@ -12456,8 +12505,9 @@
       <c r="F140" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="G140" s="17" t="n">
-        <v>2150</v>
+      <c r="G140" s="17">
+        <f>(2.0*L140+O140+Q140+V140+X140+Y140)/(1-M140-$G$8-$G$4-(1-H140)*$G$3-Z140-AB140)</f>
+        <v/>
       </c>
       <c r="H140" s="18" t="n">
         <v>0.45</v>
@@ -12587,8 +12637,9 @@
       <c r="F141" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="G141" s="17" t="n">
-        <v>2350</v>
+      <c r="G141" s="17">
+        <f>(2.0*L141+O141+Q141+V141+X141+Y141)/(1-M141-$G$8-$G$4-(1-H141)*$G$3-Z141-AB141)</f>
+        <v/>
       </c>
       <c r="H141" s="18" t="n">
         <v>0.45</v>
@@ -12716,8 +12767,9 @@
       <c r="F142" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="G142" s="17" t="n">
-        <v>745</v>
+      <c r="G142" s="17">
+        <f>(2.0*L142+O142+Q142+V142+X142+Y142)/(1-M142-$G$8-$G$4-(1-H142)*$G$3-Z142-AB142)</f>
+        <v/>
       </c>
       <c r="H142" s="18" t="n">
         <v>0.45</v>
@@ -12929,8 +12981,9 @@
       <c r="F145" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="G145" s="17" t="n">
-        <v>3150</v>
+      <c r="G145" s="17">
+        <f>(2.0*L145+O145+Q145+V145+X145+Y145)/(1-M145-$G$8-$G$4-(1-H145)*$G$3-Z145-AB145)</f>
+        <v/>
       </c>
       <c r="H145" s="18" t="n">
         <v>0.45</v>
@@ -13100,8 +13153,9 @@
       <c r="F147" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="G147" s="17" t="n">
-        <v>2580</v>
+      <c r="G147" s="17">
+        <f>(2.0*L147+O147+Q147+V147+X147+Y147)/(1-M147-$G$8-$G$4-(1-H147)*$G$3-Z147-AB147)</f>
+        <v/>
       </c>
       <c r="H147" s="18" t="n">
         <v>0.45</v>
@@ -13353,8 +13407,9 @@
       <c r="F151" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="G151" s="17" t="n">
-        <v>5700</v>
+      <c r="G151" s="17">
+        <f>(2.0*L151+O151+Q151+V151+X151+Y151)/(1-M151-$G$8-$G$4-(1-H151)*$G$3-Z151-AB151)</f>
+        <v/>
       </c>
       <c r="H151" s="18" t="n">
         <v>0.45</v>
@@ -13480,8 +13535,9 @@
       <c r="F152" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="G152" s="17" t="n">
-        <v>5600</v>
+      <c r="G152" s="17">
+        <f>(2.5*L152+O152+Q152+V152+X152+Y152)/(1-M152-$G$8-$G$4-(1-H152)*$G$3-Z152-AB152)</f>
+        <v/>
       </c>
       <c r="H152" s="18" t="n">
         <v>0.45</v>
@@ -13693,8 +13749,9 @@
       <c r="F155" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G155" s="17" t="n">
-        <v>2500</v>
+      <c r="G155" s="17">
+        <f>(2.5*L155+O155+Q155+V155+X155+Y155)/(1-M155-$G$8-$G$4-(1-H155)*$G$3-Z155-AB155)</f>
+        <v/>
       </c>
       <c r="H155" s="18" t="n">
         <v>0.45</v>
@@ -13822,8 +13879,9 @@
       <c r="F156" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="G156" s="17" t="n">
-        <v>4580</v>
+      <c r="G156" s="17">
+        <f>(3.0*L156+O156+Q156+V156+X156+Y156)/(1-M156-$G$8-$G$4-(1-H156)*$G$3-Z156-AB156)</f>
+        <v/>
       </c>
       <c r="H156" s="18" t="n">
         <v>0.45</v>
@@ -13951,8 +14009,9 @@
       <c r="F157" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="G157" s="17" t="n">
-        <v>4700</v>
+      <c r="G157" s="17">
+        <f>(2.5*L157+O157+Q157+V157+X157+Y157)/(1-M157-$G$8-$G$4-(1-H157)*$G$3-Z157-AB157)</f>
+        <v/>
       </c>
       <c r="H157" s="18" t="n">
         <v>0.45</v>
@@ -14080,8 +14139,9 @@
       <c r="F158" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="G158" s="17" t="n">
-        <v>4850</v>
+      <c r="G158" s="17">
+        <f>(3.0*L158+O158+Q158+V158+X158+Y158)/(1-M158-$G$8-$G$4-(1-H158)*$G$3-Z158-AB158)</f>
+        <v/>
       </c>
       <c r="H158" s="18" t="n">
         <v>0.45</v>
@@ -14209,8 +14269,9 @@
       <c r="F159" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G159" s="17" t="n">
-        <v>6500</v>
+      <c r="G159" s="17">
+        <f>(3.0*L159+O159+Q159+V159+X159+Y159)/(1-M159-$G$8-$G$4-(1-H159)*$G$3-Z159-AB159)</f>
+        <v/>
       </c>
       <c r="H159" s="18" t="n">
         <v>0.45</v>
@@ -14338,8 +14399,9 @@
       <c r="F160" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="G160" s="17" t="n">
-        <v>5000</v>
+      <c r="G160" s="17">
+        <f>(2.5*L160+O160+Q160+V160+X160+Y160)/(1-M160-$G$8-$G$4-(1-H160)*$G$3-Z160-AB160)</f>
+        <v/>
       </c>
       <c r="H160" s="18" t="n">
         <v>0.45</v>
@@ -14467,8 +14529,9 @@
       <c r="F161" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="G161" s="17" t="n">
-        <v>3150</v>
+      <c r="G161" s="17">
+        <f>(2.0*L161+O161+Q161+V161+X161+Y161)/(1-M161-$G$8-$G$4-(1-H161)*$G$3-Z161-AB161)</f>
+        <v/>
       </c>
       <c r="H161" s="18" t="n">
         <v>0.45</v>
@@ -14596,8 +14659,9 @@
       <c r="F162" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="G162" s="17" t="n">
-        <v>3050</v>
+      <c r="G162" s="17">
+        <f>(3.0*L162+O162+Q162+V162+X162+Y162)/(1-M162-$G$8-$G$4-(1-H162)*$G$3-Z162-AB162)</f>
+        <v/>
       </c>
       <c r="H162" s="18" t="n">
         <v>0.45</v>
